--- a/output/2025-10-03.xlsx
+++ b/output/2025-10-03.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="F14" t="n">
-        <v>7.61</v>
+        <v>7.84</v>
       </c>
       <c r="G14" t="n">
-        <v>119</v>
+        <v>112.7</v>
       </c>
       <c r="H14" t="n">
-        <v>84.5</v>
+        <v>88.3</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>-242.21</v>
+        <v>-1.2</v>
       </c>
       <c r="K14" t="n">
-        <v>3.64</v>
+        <v>130.83</v>
       </c>
       <c r="L14" t="n">
-        <v>242.23</v>
+        <v>130.83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:22:55</t>
+          <t>07:24:29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.68</v>
+        <v>3.03</v>
       </c>
       <c r="F15" t="n">
-        <v>7.05</v>
+        <v>7.67</v>
       </c>
       <c r="G15" t="n">
-        <v>123</v>
+        <v>113.8</v>
       </c>
       <c r="H15" t="n">
-        <v>84.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>-59.55</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>8.68</v>
+        <v>-304.61</v>
       </c>
       <c r="L15" t="n">
-        <v>60.17</v>
+        <v>304.76</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:24:59</t>
+          <t>07:26:17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.67</v>
+        <v>3.04</v>
       </c>
       <c r="F16" t="n">
-        <v>7.61</v>
+        <v>7.7</v>
       </c>
       <c r="G16" t="n">
-        <v>117.7</v>
+        <v>115.8</v>
       </c>
       <c r="H16" t="n">
-        <v>83.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>-72.62</v>
+        <v>11.76</v>
       </c>
       <c r="K16" t="n">
-        <v>156.09</v>
+        <v>122.69</v>
       </c>
       <c r="L16" t="n">
-        <v>172.15</v>
+        <v>123.26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:29:13</t>
+          <t>07:30:26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.91</v>
+        <v>2.37</v>
       </c>
       <c r="F17" t="n">
-        <v>8.220000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="G17" t="n">
-        <v>98.3</v>
+        <v>116.7</v>
       </c>
       <c r="H17" t="n">
-        <v>89.5</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>68.88</v>
+        <v>36.64</v>
       </c>
       <c r="K17" t="n">
-        <v>-108.65</v>
+        <v>-149.67</v>
       </c>
       <c r="L17" t="n">
-        <v>128.65</v>
+        <v>154.09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:30:59</t>
+          <t>07:31:08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.72</v>
+        <v>2.94</v>
       </c>
       <c r="F18" t="n">
-        <v>7.96</v>
+        <v>8.41</v>
       </c>
       <c r="G18" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="H18" t="n">
-        <v>86</v>
+        <v>89.2</v>
       </c>
       <c r="I18" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>44.62</v>
+        <v>10.56</v>
       </c>
       <c r="K18" t="n">
-        <v>-84.13</v>
+        <v>-272.87</v>
       </c>
       <c r="L18" t="n">
-        <v>95.23</v>
+        <v>273.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:33:10</t>
+          <t>07:33:16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.85</v>
+        <v>2.58</v>
       </c>
       <c r="F19" t="n">
-        <v>7.2</v>
+        <v>7.38</v>
       </c>
       <c r="G19" t="n">
-        <v>115.2</v>
+        <v>121.1</v>
       </c>
       <c r="H19" t="n">
-        <v>91.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>-105.07</v>
+        <v>-12.3</v>
       </c>
       <c r="K19" t="n">
-        <v>-179.19</v>
+        <v>-88.97</v>
       </c>
       <c r="L19" t="n">
-        <v>207.72</v>
+        <v>89.81</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:38:56</t>
+          <t>07:38:38</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.26</v>
+        <v>2.53</v>
       </c>
       <c r="F20" t="n">
-        <v>7.19</v>
+        <v>7.62</v>
       </c>
       <c r="G20" t="n">
-        <v>117.3</v>
+        <v>109</v>
       </c>
       <c r="H20" t="n">
-        <v>82.5</v>
+        <v>92</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>-46.98</v>
+        <v>6.89</v>
       </c>
       <c r="K20" t="n">
-        <v>77.45</v>
+        <v>-313.96</v>
       </c>
       <c r="L20" t="n">
-        <v>90.58</v>
+        <v>314.04</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:41:09</t>
+          <t>07:40:41</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.42</v>
+        <v>2.83</v>
       </c>
       <c r="F21" t="n">
-        <v>7.49</v>
+        <v>7.21</v>
       </c>
       <c r="G21" t="n">
-        <v>108</v>
+        <v>113.5</v>
       </c>
       <c r="H21" t="n">
-        <v>94.3</v>
+        <v>81.3</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-266.18</v>
+        <v>106.96</v>
       </c>
       <c r="K21" t="n">
-        <v>-30.76</v>
+        <v>-13.19</v>
       </c>
       <c r="L21" t="n">
-        <v>267.95</v>
+        <v>107.77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:42:40</t>
+          <t>07:42:14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="F22" t="n">
-        <v>7.89</v>
+        <v>7.07</v>
       </c>
       <c r="G22" t="n">
-        <v>119.3</v>
+        <v>121.2</v>
       </c>
       <c r="H22" t="n">
-        <v>92.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>187.42</v>
+        <v>212.89</v>
       </c>
       <c r="K22" t="n">
-        <v>58.24</v>
+        <v>-3.54</v>
       </c>
       <c r="L22" t="n">
-        <v>196.26</v>
+        <v>212.92</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:47:43</t>
+          <t>07:48:32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="F23" t="n">
-        <v>7.94</v>
+        <v>7.59</v>
       </c>
       <c r="G23" t="n">
-        <v>120.9</v>
+        <v>115.2</v>
       </c>
       <c r="H23" t="n">
-        <v>91.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>-93.7</v>
+        <v>165.2</v>
       </c>
       <c r="K23" t="n">
-        <v>185.18</v>
+        <v>-240.57</v>
       </c>
       <c r="L23" t="n">
-        <v>207.54</v>
+        <v>291.84</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:50:04</t>
+          <t>07:50:47</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.06</v>
+        <v>2.45</v>
       </c>
       <c r="F24" t="n">
-        <v>7.04</v>
+        <v>7.19</v>
       </c>
       <c r="G24" t="n">
-        <v>109.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>83.5</v>
+        <v>80.3</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>-201.43</v>
+        <v>275.65</v>
       </c>
       <c r="K24" t="n">
-        <v>115.91</v>
+        <v>12.05</v>
       </c>
       <c r="L24" t="n">
-        <v>232.4</v>
+        <v>275.91</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:51:52</t>
+          <t>07:52:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>7.93</v>
       </c>
       <c r="G25" t="n">
-        <v>129.3</v>
+        <v>117.3</v>
       </c>
       <c r="H25" t="n">
-        <v>82.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>-98.94</v>
+        <v>-122.72</v>
       </c>
       <c r="K25" t="n">
-        <v>-87.17</v>
+        <v>-249.46</v>
       </c>
       <c r="L25" t="n">
-        <v>131.86</v>
+        <v>278.01</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:57:22</t>
+          <t>07:55:52</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.63</v>
+        <v>2.46</v>
       </c>
       <c r="F26" t="n">
-        <v>7.8</v>
+        <v>7.37</v>
       </c>
       <c r="G26" t="n">
-        <v>109.5</v>
+        <v>133.3</v>
       </c>
       <c r="H26" t="n">
-        <v>81.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="I26" t="n">
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>147.96</v>
+        <v>252.04</v>
       </c>
       <c r="K26" t="n">
-        <v>30.79</v>
+        <v>-483.63</v>
       </c>
       <c r="L26" t="n">
-        <v>151.13</v>
+        <v>545.37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:58:23</t>
+          <t>07:57:49</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.37</v>
+        <v>2.65</v>
       </c>
       <c r="F27" t="n">
-        <v>7.55</v>
+        <v>7.96</v>
       </c>
       <c r="G27" t="n">
-        <v>123.2</v>
+        <v>128.8</v>
       </c>
       <c r="H27" t="n">
-        <v>87.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>-77.56</v>
+        <v>380.58</v>
       </c>
       <c r="K27" t="n">
-        <v>378.91</v>
+        <v>452.1</v>
       </c>
       <c r="L27" t="n">
-        <v>386.77</v>
+        <v>590.96</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:59:40</t>
+          <t>08:00:26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="F28" t="n">
-        <v>7.26</v>
+        <v>7.21</v>
       </c>
       <c r="G28" t="n">
-        <v>113.4</v>
+        <v>103.8</v>
       </c>
       <c r="H28" t="n">
-        <v>85.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>195.85</v>
+        <v>-168.8</v>
       </c>
       <c r="K28" t="n">
-        <v>-329.56</v>
+        <v>243.81</v>
       </c>
       <c r="L28" t="n">
-        <v>383.37</v>
+        <v>296.54</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:09:20</t>
+          <t>08:13:35</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.16</v>
+        <v>2.91</v>
       </c>
       <c r="F29" t="n">
-        <v>7.2</v>
+        <v>7.83</v>
       </c>
       <c r="G29" t="n">
-        <v>127</v>
+        <v>99.5</v>
       </c>
       <c r="H29" t="n">
-        <v>89.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-138.86</v>
+        <v>32.46</v>
       </c>
       <c r="K29" t="n">
-        <v>-151.3</v>
+        <v>42.88</v>
       </c>
       <c r="L29" t="n">
-        <v>205.36</v>
+        <v>53.78</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:10:43</t>
+          <t>08:15:31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.87</v>
+        <v>3.63</v>
       </c>
       <c r="F30" t="n">
-        <v>7.78</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>87.40000000000001</v>
+        <v>119.9</v>
       </c>
       <c r="H30" t="n">
-        <v>84.90000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>60.84</v>
+        <v>19.18</v>
       </c>
       <c r="K30" t="n">
-        <v>-56.6</v>
+        <v>31.91</v>
       </c>
       <c r="L30" t="n">
-        <v>83.09999999999999</v>
+        <v>37.23</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:11:51</t>
+          <t>08:16:54</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="F31" t="n">
-        <v>7.97</v>
+        <v>6.93</v>
       </c>
       <c r="G31" t="n">
-        <v>100.7</v>
+        <v>123.1</v>
       </c>
       <c r="H31" t="n">
-        <v>85.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>36.77</v>
+        <v>-3.78</v>
       </c>
       <c r="K31" t="n">
-        <v>-14.05</v>
+        <v>90.14</v>
       </c>
       <c r="L31" t="n">
-        <v>39.36</v>
+        <v>90.22</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:15:14</t>
+          <t>08:21:49</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.71</v>
+        <v>2.94</v>
       </c>
       <c r="F32" t="n">
-        <v>7.45</v>
+        <v>7.25</v>
       </c>
       <c r="G32" t="n">
-        <v>118.5</v>
+        <v>130.1</v>
       </c>
       <c r="H32" t="n">
-        <v>86.90000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>75.02</v>
+        <v>13.08</v>
       </c>
       <c r="K32" t="n">
-        <v>-52.12</v>
+        <v>-36.57</v>
       </c>
       <c r="L32" t="n">
-        <v>91.34999999999999</v>
+        <v>38.84</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:17:33</t>
+          <t>08:23:27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.27</v>
+        <v>3.85</v>
       </c>
       <c r="F33" t="n">
-        <v>7.36</v>
+        <v>7.85</v>
       </c>
       <c r="G33" t="n">
-        <v>121.1</v>
+        <v>125.8</v>
       </c>
       <c r="H33" t="n">
-        <v>80.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-40.88</v>
+        <v>45.33</v>
       </c>
       <c r="K33" t="n">
-        <v>30.22</v>
+        <v>-41.7</v>
       </c>
       <c r="L33" t="n">
-        <v>50.84</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:19:04</t>
+          <t>08:25:33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.04</v>
+        <v>2.45</v>
       </c>
       <c r="F34" t="n">
-        <v>7.77</v>
+        <v>7.6</v>
       </c>
       <c r="G34" t="n">
-        <v>101.2</v>
+        <v>113</v>
       </c>
       <c r="H34" t="n">
-        <v>89.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-198.52</v>
+        <v>-33.41</v>
       </c>
       <c r="K34" t="n">
-        <v>12.69</v>
+        <v>-100.06</v>
       </c>
       <c r="L34" t="n">
-        <v>198.93</v>
+        <v>105.49</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:24:07</t>
+          <t>08:29:49</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="F35" t="n">
-        <v>6.76</v>
+        <v>7.53</v>
       </c>
       <c r="G35" t="n">
-        <v>106.6</v>
+        <v>116.6</v>
       </c>
       <c r="H35" t="n">
-        <v>81.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>-115.23</v>
+        <v>154.93</v>
       </c>
       <c r="K35" t="n">
-        <v>3.49</v>
+        <v>157.56</v>
       </c>
       <c r="L35" t="n">
-        <v>115.28</v>
+        <v>220.97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:26:36</t>
+          <t>08:31:01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="F36" t="n">
-        <v>7.53</v>
+        <v>7.74</v>
       </c>
       <c r="G36" t="n">
-        <v>113.9</v>
+        <v>109.7</v>
       </c>
       <c r="H36" t="n">
-        <v>87.5</v>
+        <v>85.5</v>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>-152.01</v>
+        <v>233.52</v>
       </c>
       <c r="K36" t="n">
-        <v>-260.31</v>
+        <v>-184.93</v>
       </c>
       <c r="L36" t="n">
-        <v>301.44</v>
+        <v>297.88</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:28:13</t>
+          <t>08:33:18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="F37" t="n">
-        <v>7.45</v>
+        <v>7.13</v>
       </c>
       <c r="G37" t="n">
-        <v>117.5</v>
+        <v>116.9</v>
       </c>
       <c r="H37" t="n">
-        <v>80.8</v>
+        <v>87.7</v>
       </c>
       <c r="I37" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>239.43</v>
+        <v>-306.52</v>
       </c>
       <c r="K37" t="n">
-        <v>-129.42</v>
+        <v>12.95</v>
       </c>
       <c r="L37" t="n">
-        <v>272.17</v>
+        <v>306.79</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:32:57</t>
+          <t>08:38:32</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="F38" t="n">
-        <v>8.32</v>
+        <v>6.64</v>
       </c>
       <c r="G38" t="n">
-        <v>120.7</v>
+        <v>114.8</v>
       </c>
       <c r="H38" t="n">
-        <v>75.40000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>3.82</v>
+        <v>-78.95999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>83.11</v>
+        <v>325.55</v>
       </c>
       <c r="L38" t="n">
-        <v>83.2</v>
+        <v>334.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:35:17</t>
+          <t>08:40:27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.31</v>
+        <v>2.63</v>
       </c>
       <c r="F39" t="n">
-        <v>7.86</v>
+        <v>7.34</v>
       </c>
       <c r="G39" t="n">
-        <v>108.5</v>
+        <v>111.4</v>
       </c>
       <c r="H39" t="n">
-        <v>84.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>602.15</v>
+        <v>-190.43</v>
       </c>
       <c r="K39" t="n">
-        <v>192.83</v>
+        <v>-41.71</v>
       </c>
       <c r="L39" t="n">
-        <v>632.27</v>
+        <v>194.95</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:36:32</t>
+          <t>08:41:59</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.42</v>
+        <v>2.68</v>
       </c>
       <c r="F40" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="G40" t="n">
-        <v>112.6</v>
+        <v>111.1</v>
       </c>
       <c r="H40" t="n">
-        <v>87.3</v>
+        <v>87.2</v>
       </c>
       <c r="I40" t="n">
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>153.5</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>-340.12</v>
+        <v>-317.29</v>
       </c>
       <c r="L40" t="n">
-        <v>373.15</v>
+        <v>332.59</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:41:11</t>
+          <t>08:45:31</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.82</v>
+        <v>3.17</v>
       </c>
       <c r="F41" t="n">
-        <v>7.24</v>
+        <v>7.18</v>
       </c>
       <c r="G41" t="n">
-        <v>101.2</v>
+        <v>117.9</v>
       </c>
       <c r="H41" t="n">
-        <v>82.40000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-137.35</v>
+        <v>-906.88</v>
       </c>
       <c r="K41" t="n">
-        <v>327.88</v>
+        <v>390.85</v>
       </c>
       <c r="L41" t="n">
-        <v>355.49</v>
+        <v>987.52</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:42:27</t>
+          <t>08:47:15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.02</v>
+        <v>2.92</v>
       </c>
       <c r="F42" t="n">
-        <v>7.66</v>
+        <v>7.45</v>
       </c>
       <c r="G42" t="n">
-        <v>111.2</v>
+        <v>111.4</v>
       </c>
       <c r="H42" t="n">
-        <v>83.8</v>
+        <v>92.3</v>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>-133.11</v>
+        <v>-415.13</v>
       </c>
       <c r="K42" t="n">
-        <v>281.68</v>
+        <v>-159.49</v>
       </c>
       <c r="L42" t="n">
-        <v>311.55</v>
+        <v>444.71</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:43:47</t>
+          <t>08:49:09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.41</v>
+        <v>2.86</v>
       </c>
       <c r="F43" t="n">
-        <v>7.38</v>
+        <v>7.53</v>
       </c>
       <c r="G43" t="n">
-        <v>117.4</v>
+        <v>120.2</v>
       </c>
       <c r="H43" t="n">
-        <v>88.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="I43" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>327.36</v>
+        <v>-70.54000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>-914.36</v>
+        <v>-708.12</v>
       </c>
       <c r="L43" t="n">
-        <v>971.1900000000001</v>
+        <v>711.63</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:54:58</t>
+          <t>08:58:30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="F44" t="n">
-        <v>7.08</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>106.9</v>
+        <v>107.9</v>
       </c>
       <c r="H44" t="n">
-        <v>88.8</v>
+        <v>91.3</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>13.86</v>
+        <v>-68.56999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>59.03</v>
+        <v>-17.22</v>
       </c>
       <c r="L44" t="n">
-        <v>60.63</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:56:59</t>
+          <t>08:59:51</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="F45" t="n">
-        <v>7.89</v>
+        <v>7.65</v>
       </c>
       <c r="G45" t="n">
-        <v>107.7</v>
+        <v>103.2</v>
       </c>
       <c r="H45" t="n">
-        <v>84.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>14.38</v>
+        <v>-48.02</v>
       </c>
       <c r="K45" t="n">
-        <v>25.39</v>
+        <v>-67.65000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>29.18</v>
+        <v>82.95999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:58:50</t>
+          <t>09:00:40</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="F46" t="n">
-        <v>7.71</v>
+        <v>8.07</v>
       </c>
       <c r="G46" t="n">
-        <v>114.8</v>
+        <v>112.4</v>
       </c>
       <c r="H46" t="n">
-        <v>81.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-36.72</v>
+        <v>-15.2</v>
       </c>
       <c r="K46" t="n">
-        <v>-45.57</v>
+        <v>-118.92</v>
       </c>
       <c r="L46" t="n">
-        <v>58.53</v>
+        <v>119.89</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:05:01</t>
+          <t>09:05:46</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="F47" t="n">
-        <v>6.99</v>
+        <v>7.55</v>
       </c>
       <c r="G47" t="n">
-        <v>106.4</v>
+        <v>120</v>
       </c>
       <c r="H47" t="n">
-        <v>87.5</v>
+        <v>88.2</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>158.51</v>
+        <v>-76.19</v>
       </c>
       <c r="K47" t="n">
-        <v>-64.94</v>
+        <v>190.35</v>
       </c>
       <c r="L47" t="n">
-        <v>171.3</v>
+        <v>205.03</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:05:42</t>
+          <t>09:06:35</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.91</v>
+        <v>3.18</v>
       </c>
       <c r="F48" t="n">
-        <v>8.1</v>
+        <v>7.93</v>
       </c>
       <c r="G48" t="n">
-        <v>119.9</v>
+        <v>109.5</v>
       </c>
       <c r="H48" t="n">
-        <v>79.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-107.17</v>
+        <v>156.77</v>
       </c>
       <c r="K48" t="n">
-        <v>115.4</v>
+        <v>119.35</v>
       </c>
       <c r="L48" t="n">
-        <v>157.49</v>
+        <v>197.04</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:08:03</t>
+          <t>09:08:08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.1</v>
+        <v>2.51</v>
       </c>
       <c r="F49" t="n">
-        <v>7.33</v>
+        <v>7.96</v>
       </c>
       <c r="G49" t="n">
-        <v>111.6</v>
+        <v>109.5</v>
       </c>
       <c r="H49" t="n">
-        <v>96</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I49" t="n">
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-29.69</v>
+        <v>-147.12</v>
       </c>
       <c r="K49" t="n">
-        <v>-42.75</v>
+        <v>-96.27</v>
       </c>
       <c r="L49" t="n">
-        <v>52.05</v>
+        <v>175.82</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:12:02</t>
+          <t>09:12:04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.62</v>
+        <v>2.99</v>
       </c>
       <c r="F50" t="n">
-        <v>7.7</v>
+        <v>7.83</v>
       </c>
       <c r="G50" t="n">
-        <v>110.5</v>
+        <v>118.9</v>
       </c>
       <c r="H50" t="n">
-        <v>87.90000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>105.78</v>
+        <v>188.84</v>
       </c>
       <c r="K50" t="n">
-        <v>119.23</v>
+        <v>213.69</v>
       </c>
       <c r="L50" t="n">
-        <v>159.39</v>
+        <v>285.17</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:14:11</t>
+          <t>09:14:30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.81</v>
+        <v>3.66</v>
       </c>
       <c r="F51" t="n">
-        <v>7.54</v>
+        <v>8.06</v>
       </c>
       <c r="G51" t="n">
-        <v>110.3</v>
+        <v>117.3</v>
       </c>
       <c r="H51" t="n">
-        <v>90.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>-22.84</v>
+        <v>327.8</v>
       </c>
       <c r="K51" t="n">
-        <v>322.09</v>
+        <v>-114.62</v>
       </c>
       <c r="L51" t="n">
-        <v>322.9</v>
+        <v>347.26</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:15:05</t>
+          <t>09:16:07</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="F52" t="n">
-        <v>8.32</v>
+        <v>7.14</v>
       </c>
       <c r="G52" t="n">
-        <v>108.6</v>
+        <v>118.5</v>
       </c>
       <c r="H52" t="n">
-        <v>93.7</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I52" t="n">
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>-262.86</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>70.2</v>
+        <v>-11.67</v>
       </c>
       <c r="L52" t="n">
-        <v>272.07</v>
+        <v>79.09999999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:20:42</t>
+          <t>09:20:02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="F53" t="n">
-        <v>6.88</v>
+        <v>6.89</v>
       </c>
       <c r="G53" t="n">
-        <v>114.4</v>
+        <v>112.5</v>
       </c>
       <c r="H53" t="n">
-        <v>91</v>
+        <v>85.7</v>
       </c>
       <c r="I53" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>212.68</v>
+        <v>-306.7</v>
       </c>
       <c r="K53" t="n">
-        <v>-106.26</v>
+        <v>456.23</v>
       </c>
       <c r="L53" t="n">
-        <v>237.75</v>
+        <v>549.74</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:23:02</t>
+          <t>09:21:21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.38</v>
+        <v>3.01</v>
       </c>
       <c r="F54" t="n">
-        <v>7.96</v>
+        <v>7.62</v>
       </c>
       <c r="G54" t="n">
-        <v>120.8</v>
+        <v>122.5</v>
       </c>
       <c r="H54" t="n">
-        <v>88.7</v>
+        <v>90.7</v>
       </c>
       <c r="I54" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>-109.42</v>
+        <v>-31.59</v>
       </c>
       <c r="K54" t="n">
-        <v>908.27</v>
+        <v>-133.9</v>
       </c>
       <c r="L54" t="n">
-        <v>914.84</v>
+        <v>137.57</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:24:19</t>
+          <t>09:23:23</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.41</v>
+        <v>3.05</v>
       </c>
       <c r="F55" t="n">
-        <v>7.71</v>
+        <v>7.65</v>
       </c>
       <c r="G55" t="n">
-        <v>114.7</v>
+        <v>112.4</v>
       </c>
       <c r="H55" t="n">
-        <v>85.09999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="I55" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>577.16</v>
+        <v>-72.92</v>
       </c>
       <c r="K55" t="n">
-        <v>-21.28</v>
+        <v>52.55</v>
       </c>
       <c r="L55" t="n">
-        <v>577.55</v>
+        <v>89.88</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:28:22</t>
+          <t>09:27:20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.04</v>
+        <v>3.33</v>
       </c>
       <c r="F56" t="n">
-        <v>7.85</v>
+        <v>7.74</v>
       </c>
       <c r="G56" t="n">
-        <v>117.8</v>
+        <v>114.6</v>
       </c>
       <c r="H56" t="n">
-        <v>85.40000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="I56" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>-323.17</v>
+        <v>307.3</v>
       </c>
       <c r="K56" t="n">
-        <v>155.91</v>
+        <v>90.88</v>
       </c>
       <c r="L56" t="n">
-        <v>358.81</v>
+        <v>320.46</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:29:48</t>
+          <t>09:28:57</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.74</v>
+        <v>3.35</v>
       </c>
       <c r="F57" t="n">
-        <v>7.46</v>
+        <v>7.51</v>
       </c>
       <c r="G57" t="n">
-        <v>111.1</v>
+        <v>116.2</v>
       </c>
       <c r="H57" t="n">
-        <v>83.2</v>
+        <v>88.3</v>
       </c>
       <c r="I57" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-994.24</v>
+        <v>-646.83</v>
       </c>
       <c r="K57" t="n">
-        <v>-340.79</v>
+        <v>-238.39</v>
       </c>
       <c r="L57" t="n">
-        <v>1051.02</v>
+        <v>689.36</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:31:22</t>
+          <t>09:30:51</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.56</v>
+        <v>2.88</v>
       </c>
       <c r="F58" t="n">
-        <v>7.58</v>
+        <v>8.27</v>
       </c>
       <c r="G58" t="n">
-        <v>119.7</v>
+        <v>107.5</v>
       </c>
       <c r="H58" t="n">
-        <v>85.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-203.59</v>
+        <v>-242.98</v>
       </c>
       <c r="K58" t="n">
-        <v>159.39</v>
+        <v>-657.29</v>
       </c>
       <c r="L58" t="n">
-        <v>258.56</v>
+        <v>700.76</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:44:07</t>
+          <t>09:42:23</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.34</v>
+        <v>2.99</v>
       </c>
       <c r="F59" t="n">
-        <v>7.21</v>
+        <v>7.62</v>
       </c>
       <c r="G59" t="n">
-        <v>115.2</v>
+        <v>101.6</v>
       </c>
       <c r="H59" t="n">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I59" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-166.32</v>
+        <v>-27.88</v>
       </c>
       <c r="K59" t="n">
-        <v>31.6</v>
+        <v>-238.17</v>
       </c>
       <c r="L59" t="n">
-        <v>169.3</v>
+        <v>239.8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:45:00</t>
+          <t>09:43:35</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.03</v>
+        <v>3.12</v>
       </c>
       <c r="F60" t="n">
-        <v>7.4</v>
+        <v>8.09</v>
       </c>
       <c r="G60" t="n">
-        <v>124.7</v>
+        <v>118.7</v>
       </c>
       <c r="H60" t="n">
-        <v>87.59999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="I60" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>15.16</v>
+        <v>-24.03</v>
       </c>
       <c r="K60" t="n">
-        <v>-32.61</v>
+        <v>278.99</v>
       </c>
       <c r="L60" t="n">
-        <v>35.96</v>
+        <v>280.02</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:46:11</t>
+          <t>09:44:29</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2602,31 +2602,31 @@
         <v>3.39</v>
       </c>
       <c r="F61" t="n">
-        <v>7.61</v>
+        <v>8.4</v>
       </c>
       <c r="G61" t="n">
-        <v>112.2</v>
+        <v>111.3</v>
       </c>
       <c r="H61" t="n">
-        <v>86.3</v>
+        <v>82.3</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>79.34</v>
+        <v>-203.71</v>
       </c>
       <c r="K61" t="n">
-        <v>70.19</v>
+        <v>-105.39</v>
       </c>
       <c r="L61" t="n">
-        <v>105.94</v>
+        <v>229.36</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:52:03</t>
+          <t>09:48:21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="F62" t="n">
-        <v>7.52</v>
+        <v>7.45</v>
       </c>
       <c r="G62" t="n">
-        <v>125.5</v>
+        <v>108.6</v>
       </c>
       <c r="H62" t="n">
-        <v>89.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>-8.41</v>
+        <v>-54.99</v>
       </c>
       <c r="K62" t="n">
-        <v>-99.95999999999999</v>
+        <v>114.89</v>
       </c>
       <c r="L62" t="n">
-        <v>100.31</v>
+        <v>127.37</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:53:44</t>
+          <t>09:49:37</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.01</v>
+        <v>3.22</v>
       </c>
       <c r="F63" t="n">
-        <v>7.78</v>
+        <v>7.5</v>
       </c>
       <c r="G63" t="n">
-        <v>109.4</v>
+        <v>114.8</v>
       </c>
       <c r="H63" t="n">
-        <v>84.40000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="I63" t="n">
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-36.33</v>
+        <v>223.69</v>
       </c>
       <c r="K63" t="n">
-        <v>-123.05</v>
+        <v>-208.54</v>
       </c>
       <c r="L63" t="n">
-        <v>128.3</v>
+        <v>305.82</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:55:46</t>
+          <t>09:51:38</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.03</v>
+        <v>3.44</v>
       </c>
       <c r="F64" t="n">
-        <v>7.27</v>
+        <v>7.46</v>
       </c>
       <c r="G64" t="n">
-        <v>111</v>
+        <v>111.1</v>
       </c>
       <c r="H64" t="n">
-        <v>83.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-37.11</v>
+        <v>146.7</v>
       </c>
       <c r="K64" t="n">
-        <v>15.89</v>
+        <v>89.2</v>
       </c>
       <c r="L64" t="n">
-        <v>40.37</v>
+        <v>171.69</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:59:56</t>
+          <t>09:56:25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.72</v>
+        <v>3.73</v>
       </c>
       <c r="F65" t="n">
-        <v>7.23</v>
+        <v>6.86</v>
       </c>
       <c r="G65" t="n">
-        <v>120.9</v>
+        <v>113.1</v>
       </c>
       <c r="H65" t="n">
-        <v>83.09999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>-260.31</v>
+        <v>-173.41</v>
       </c>
       <c r="K65" t="n">
-        <v>455.02</v>
+        <v>-209.4</v>
       </c>
       <c r="L65" t="n">
-        <v>524.22</v>
+        <v>271.88</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10:02:17</t>
+          <t>09:57:49</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.93</v>
+        <v>3.08</v>
       </c>
       <c r="F66" t="n">
-        <v>7.42</v>
+        <v>8.07</v>
       </c>
       <c r="G66" t="n">
-        <v>105</v>
+        <v>122.5</v>
       </c>
       <c r="H66" t="n">
-        <v>84.7</v>
+        <v>86</v>
       </c>
       <c r="I66" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>74.36</v>
+        <v>-142.51</v>
       </c>
       <c r="K66" t="n">
-        <v>232.94</v>
+        <v>-45.12</v>
       </c>
       <c r="L66" t="n">
-        <v>244.52</v>
+        <v>149.48</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:04:39</t>
+          <t>10:00:03</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.24</v>
+        <v>2.96</v>
       </c>
       <c r="F67" t="n">
-        <v>7.05</v>
+        <v>7.38</v>
       </c>
       <c r="G67" t="n">
-        <v>110.8</v>
+        <v>115.8</v>
       </c>
       <c r="H67" t="n">
-        <v>85.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="I67" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>253.34</v>
+        <v>-260.16</v>
       </c>
       <c r="K67" t="n">
-        <v>-528.13</v>
+        <v>-165.77</v>
       </c>
       <c r="L67" t="n">
-        <v>585.75</v>
+        <v>308.48</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:09:22</t>
+          <t>10:06:10</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.74</v>
+        <v>3.29</v>
       </c>
       <c r="F68" t="n">
-        <v>7.99</v>
+        <v>7.93</v>
       </c>
       <c r="G68" t="n">
-        <v>110.5</v>
+        <v>93</v>
       </c>
       <c r="H68" t="n">
-        <v>83</v>
+        <v>90.7</v>
       </c>
       <c r="I68" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-533.51</v>
+        <v>-278.28</v>
       </c>
       <c r="K68" t="n">
-        <v>-136.95</v>
+        <v>-458.83</v>
       </c>
       <c r="L68" t="n">
-        <v>550.8</v>
+        <v>536.62</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:11:11</t>
+          <t>10:07:11</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="F69" t="n">
-        <v>7.89</v>
+        <v>7.64</v>
       </c>
       <c r="G69" t="n">
-        <v>118.8</v>
+        <v>113.9</v>
       </c>
       <c r="H69" t="n">
-        <v>86.5</v>
+        <v>93</v>
       </c>
       <c r="I69" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-128.52</v>
+        <v>-407.77</v>
       </c>
       <c r="K69" t="n">
-        <v>-146.36</v>
+        <v>-53.13</v>
       </c>
       <c r="L69" t="n">
-        <v>194.78</v>
+        <v>411.22</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:13:17</t>
+          <t>10:08:24</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="F70" t="n">
-        <v>7.47</v>
+        <v>7.6</v>
       </c>
       <c r="G70" t="n">
-        <v>112.1</v>
+        <v>125</v>
       </c>
       <c r="H70" t="n">
-        <v>89.2</v>
+        <v>86.7</v>
       </c>
       <c r="I70" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-100.06</v>
+        <v>-438.83</v>
       </c>
       <c r="K70" t="n">
-        <v>-18.85</v>
+        <v>15.01</v>
       </c>
       <c r="L70" t="n">
-        <v>101.82</v>
+        <v>439.08</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:18:53</t>
+          <t>10:13:16</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.31</v>
+        <v>3.05</v>
       </c>
       <c r="F71" t="n">
-        <v>7.36</v>
+        <v>8.02</v>
       </c>
       <c r="G71" t="n">
-        <v>107.3</v>
+        <v>124.4</v>
       </c>
       <c r="H71" t="n">
-        <v>87.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="I71" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-729.01</v>
+        <v>-333.2</v>
       </c>
       <c r="K71" t="n">
-        <v>-251.43</v>
+        <v>-274.79</v>
       </c>
       <c r="L71" t="n">
-        <v>771.15</v>
+        <v>431.89</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:20:55</t>
+          <t>10:14:42</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.22</v>
+        <v>3.39</v>
       </c>
       <c r="F72" t="n">
-        <v>7.16</v>
+        <v>7.29</v>
       </c>
       <c r="G72" t="n">
-        <v>112.4</v>
+        <v>127</v>
       </c>
       <c r="H72" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>-137.69</v>
+        <v>1186.42</v>
       </c>
       <c r="K72" t="n">
-        <v>-595.3200000000001</v>
+        <v>-683.36</v>
       </c>
       <c r="L72" t="n">
-        <v>611.04</v>
+        <v>1369.15</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:21:53</t>
+          <t>10:15:41</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.21</v>
+        <v>3.33</v>
       </c>
       <c r="F73" t="n">
-        <v>7.34</v>
+        <v>7.3</v>
       </c>
       <c r="G73" t="n">
-        <v>119.9</v>
+        <v>95</v>
       </c>
       <c r="H73" t="n">
-        <v>93.8</v>
+        <v>84</v>
       </c>
       <c r="I73" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>-57.73</v>
+        <v>625.71</v>
       </c>
       <c r="K73" t="n">
-        <v>155.89</v>
+        <v>161.86</v>
       </c>
       <c r="L73" t="n">
-        <v>166.24</v>
+        <v>646.3099999999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:32:01</t>
+          <t>10:28:50</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="F74" t="n">
-        <v>7.18</v>
+        <v>7.45</v>
       </c>
       <c r="G74" t="n">
-        <v>115.1</v>
+        <v>117.5</v>
       </c>
       <c r="H74" t="n">
-        <v>83.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="I74" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>-61.64</v>
+        <v>-190.5</v>
       </c>
       <c r="K74" t="n">
-        <v>41.58</v>
+        <v>117.22</v>
       </c>
       <c r="L74" t="n">
-        <v>74.36</v>
+        <v>223.68</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:33:17</t>
+          <t>10:30:28</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.63</v>
+        <v>3.54</v>
       </c>
       <c r="F75" t="n">
-        <v>8.130000000000001</v>
+        <v>7.74</v>
       </c>
       <c r="G75" t="n">
-        <v>104.3</v>
+        <v>108.1</v>
       </c>
       <c r="H75" t="n">
-        <v>87.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J75" t="n">
-        <v>-217.3</v>
+        <v>59.37</v>
       </c>
       <c r="K75" t="n">
-        <v>30.93</v>
+        <v>53.55</v>
       </c>
       <c r="L75" t="n">
-        <v>219.49</v>
+        <v>79.95</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:34:35</t>
+          <t>10:31:40</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.21</v>
+        <v>3.58</v>
       </c>
       <c r="F76" t="n">
-        <v>7.59</v>
+        <v>7.93</v>
       </c>
       <c r="G76" t="n">
-        <v>114.6</v>
+        <v>111</v>
       </c>
       <c r="H76" t="n">
-        <v>85.40000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>143.09</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>74.72</v>
+        <v>83.47</v>
       </c>
       <c r="L76" t="n">
-        <v>161.42</v>
+        <v>108.48</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:39:43</t>
+          <t>10:37:44</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="F77" t="n">
-        <v>7.7</v>
+        <v>7.81</v>
       </c>
       <c r="G77" t="n">
-        <v>94.3</v>
+        <v>118.7</v>
       </c>
       <c r="H77" t="n">
-        <v>85.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>13.15</v>
+        <v>58.51</v>
       </c>
       <c r="K77" t="n">
-        <v>-71.14</v>
+        <v>-169.64</v>
       </c>
       <c r="L77" t="n">
-        <v>72.34</v>
+        <v>179.45</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:40:48</t>
+          <t>10:39:33</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="F78" t="n">
-        <v>7.7</v>
+        <v>7.62</v>
       </c>
       <c r="G78" t="n">
-        <v>115.8</v>
+        <v>115.9</v>
       </c>
       <c r="H78" t="n">
-        <v>92.3</v>
+        <v>83.2</v>
       </c>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>179.69</v>
+        <v>114.51</v>
       </c>
       <c r="K78" t="n">
-        <v>-73.51000000000001</v>
+        <v>33.74</v>
       </c>
       <c r="L78" t="n">
-        <v>194.14</v>
+        <v>119.38</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:42:47</t>
+          <t>10:41:31</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="F79" t="n">
-        <v>7.7</v>
+        <v>7.13</v>
       </c>
       <c r="G79" t="n">
-        <v>112.3</v>
+        <v>120.7</v>
       </c>
       <c r="H79" t="n">
-        <v>85.5</v>
+        <v>81</v>
       </c>
       <c r="I79" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>52.93</v>
+        <v>59.91</v>
       </c>
       <c r="K79" t="n">
-        <v>-75.52</v>
+        <v>-16.96</v>
       </c>
       <c r="L79" t="n">
-        <v>92.22</v>
+        <v>62.26</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:47:40</t>
+          <t>10:46:06</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="F80" t="n">
-        <v>7.18</v>
+        <v>7.55</v>
       </c>
       <c r="G80" t="n">
-        <v>112.2</v>
+        <v>106.2</v>
       </c>
       <c r="H80" t="n">
-        <v>86.3</v>
+        <v>83.5</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-150.11</v>
+        <v>-265.96</v>
       </c>
       <c r="K80" t="n">
-        <v>-205.29</v>
+        <v>-63.31</v>
       </c>
       <c r="L80" t="n">
-        <v>254.32</v>
+        <v>273.39</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:49:58</t>
+          <t>10:46:53</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.32</v>
+        <v>3.12</v>
       </c>
       <c r="F81" t="n">
-        <v>7.68</v>
+        <v>7.16</v>
       </c>
       <c r="G81" t="n">
-        <v>116.4</v>
+        <v>120</v>
       </c>
       <c r="H81" t="n">
-        <v>86.7</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I81" t="n">
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-194.18</v>
+        <v>-298.42</v>
       </c>
       <c r="K81" t="n">
-        <v>-30.53</v>
+        <v>-111.16</v>
       </c>
       <c r="L81" t="n">
-        <v>196.57</v>
+        <v>318.45</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:52:16</t>
+          <t>10:48:33</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="F82" t="n">
-        <v>6.82</v>
+        <v>7.71</v>
       </c>
       <c r="G82" t="n">
-        <v>105.1</v>
+        <v>110.3</v>
       </c>
       <c r="H82" t="n">
-        <v>78.09999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>117.66</v>
+        <v>-145.05</v>
       </c>
       <c r="K82" t="n">
-        <v>51.1</v>
+        <v>351.1</v>
       </c>
       <c r="L82" t="n">
-        <v>128.28</v>
+        <v>379.88</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:56:29</t>
+          <t>10:53:53</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.39</v>
+        <v>3.28</v>
       </c>
       <c r="F83" t="n">
-        <v>7.8</v>
+        <v>8.02</v>
       </c>
       <c r="G83" t="n">
-        <v>100.8</v>
+        <v>111.9</v>
       </c>
       <c r="H83" t="n">
-        <v>76.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="I83" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>72.18000000000001</v>
+        <v>346.65</v>
       </c>
       <c r="K83" t="n">
-        <v>12.87</v>
+        <v>-392.83</v>
       </c>
       <c r="L83" t="n">
-        <v>73.31</v>
+        <v>523.91</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:57:48</t>
+          <t>10:56:13</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.38</v>
+        <v>3.21</v>
       </c>
       <c r="F84" t="n">
-        <v>8.27</v>
+        <v>6.94</v>
       </c>
       <c r="G84" t="n">
-        <v>113.4</v>
+        <v>108.1</v>
       </c>
       <c r="H84" t="n">
-        <v>89.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I84" t="n">
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>-322.36</v>
+        <v>-32.9</v>
       </c>
       <c r="K84" t="n">
-        <v>178.88</v>
+        <v>-149.59</v>
       </c>
       <c r="L84" t="n">
-        <v>368.67</v>
+        <v>153.16</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>11:00:02</t>
+          <t>10:57:55</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.22</v>
+        <v>3.69</v>
       </c>
       <c r="F85" t="n">
-        <v>7.06</v>
+        <v>7.95</v>
       </c>
       <c r="G85" t="n">
-        <v>130.9</v>
+        <v>106.1</v>
       </c>
       <c r="H85" t="n">
-        <v>84.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>153.03</v>
+        <v>237.43</v>
       </c>
       <c r="K85" t="n">
-        <v>109.4</v>
+        <v>-415.91</v>
       </c>
       <c r="L85" t="n">
-        <v>188.11</v>
+        <v>478.91</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11:03:46</t>
+          <t>11:02:44</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.33</v>
+        <v>3.09</v>
       </c>
       <c r="F86" t="n">
-        <v>7.6</v>
+        <v>7.16</v>
       </c>
       <c r="G86" t="n">
-        <v>111.6</v>
+        <v>113.1</v>
       </c>
       <c r="H86" t="n">
-        <v>85.7</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I86" t="n">
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-41.89</v>
+        <v>269.75</v>
       </c>
       <c r="K86" t="n">
-        <v>-252.45</v>
+        <v>119.41</v>
       </c>
       <c r="L86" t="n">
-        <v>255.9</v>
+        <v>295</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11:05:13</t>
+          <t>11:05:09</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.32</v>
+        <v>3.37</v>
       </c>
       <c r="F87" t="n">
-        <v>7.79</v>
+        <v>7.75</v>
       </c>
       <c r="G87" t="n">
-        <v>114.6</v>
+        <v>116.9</v>
       </c>
       <c r="H87" t="n">
-        <v>82.09999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-225.31</v>
+        <v>868.61</v>
       </c>
       <c r="K87" t="n">
-        <v>-21.5</v>
+        <v>-43.39</v>
       </c>
       <c r="L87" t="n">
-        <v>226.33</v>
+        <v>869.7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:07:15</t>
+          <t>11:06:46</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.6</v>
+        <v>3.31</v>
       </c>
       <c r="F88" t="n">
-        <v>7.96</v>
+        <v>7.66</v>
       </c>
       <c r="G88" t="n">
-        <v>112.4</v>
+        <v>124.3</v>
       </c>
       <c r="H88" t="n">
-        <v>86.59999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>347.24</v>
+        <v>-20.99</v>
       </c>
       <c r="K88" t="n">
-        <v>-413.42</v>
+        <v>-110.29</v>
       </c>
       <c r="L88" t="n">
-        <v>539.9</v>
+        <v>112.27</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-03.xlsx
+++ b/output/2025-10-03.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.2</v>
+        <v>-1.24</v>
       </c>
       <c r="K14" t="n">
-        <v>130.83</v>
+        <v>135.57</v>
       </c>
       <c r="L14" t="n">
-        <v>130.83</v>
+        <v>135.58</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>9.619999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="K15" t="n">
-        <v>-304.61</v>
+        <v>-270.87</v>
       </c>
       <c r="L15" t="n">
-        <v>304.76</v>
+        <v>271.01</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>11.76</v>
+        <v>13.88</v>
       </c>
       <c r="K16" t="n">
-        <v>122.69</v>
+        <v>144.82</v>
       </c>
       <c r="L16" t="n">
-        <v>123.26</v>
+        <v>145.49</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>36.64</v>
+        <v>34.6</v>
       </c>
       <c r="K17" t="n">
-        <v>-149.67</v>
+        <v>-141.34</v>
       </c>
       <c r="L17" t="n">
-        <v>154.09</v>
+        <v>145.52</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>10.56</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-272.87</v>
+        <v>-257.31</v>
       </c>
       <c r="L18" t="n">
-        <v>273.08</v>
+        <v>257.5</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>-12.3</v>
+        <v>-15.49</v>
       </c>
       <c r="K19" t="n">
-        <v>-88.97</v>
+        <v>-112.08</v>
       </c>
       <c r="L19" t="n">
-        <v>89.81</v>
+        <v>113.14</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>6.89</v>
+        <v>6.67</v>
       </c>
       <c r="K20" t="n">
-        <v>-313.96</v>
+        <v>-303.95</v>
       </c>
       <c r="L20" t="n">
-        <v>314.04</v>
+        <v>304.03</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>106.96</v>
+        <v>176.58</v>
       </c>
       <c r="K21" t="n">
-        <v>-13.19</v>
+        <v>-21.77</v>
       </c>
       <c r="L21" t="n">
-        <v>107.77</v>
+        <v>177.92</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>212.89</v>
+        <v>252.61</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.54</v>
+        <v>-4.2</v>
       </c>
       <c r="L22" t="n">
-        <v>212.92</v>
+        <v>252.65</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>165.2</v>
+        <v>224.25</v>
       </c>
       <c r="K23" t="n">
-        <v>-240.57</v>
+        <v>-326.55</v>
       </c>
       <c r="L23" t="n">
-        <v>291.84</v>
+        <v>396.14</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>275.65</v>
+        <v>328.42</v>
       </c>
       <c r="K24" t="n">
-        <v>12.05</v>
+        <v>14.36</v>
       </c>
       <c r="L24" t="n">
-        <v>275.91</v>
+        <v>328.73</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>-122.72</v>
+        <v>-152.56</v>
       </c>
       <c r="K25" t="n">
-        <v>-249.46</v>
+        <v>-310.11</v>
       </c>
       <c r="L25" t="n">
-        <v>278.01</v>
+        <v>345.6</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>252.04</v>
+        <v>278.49</v>
       </c>
       <c r="K26" t="n">
-        <v>-483.63</v>
+        <v>-534.39</v>
       </c>
       <c r="L26" t="n">
-        <v>545.37</v>
+        <v>602.6</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>380.58</v>
+        <v>461.5</v>
       </c>
       <c r="K27" t="n">
-        <v>452.1</v>
+        <v>548.22</v>
       </c>
       <c r="L27" t="n">
-        <v>590.96</v>
+        <v>716.61</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-168.8</v>
+        <v>-264.47</v>
       </c>
       <c r="K28" t="n">
-        <v>243.81</v>
+        <v>381.99</v>
       </c>
       <c r="L28" t="n">
-        <v>296.54</v>
+        <v>464.61</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>32.46</v>
+        <v>55.91</v>
       </c>
       <c r="K29" t="n">
-        <v>42.88</v>
+        <v>73.84</v>
       </c>
       <c r="L29" t="n">
-        <v>53.78</v>
+        <v>92.61</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>19.18</v>
+        <v>55.76</v>
       </c>
       <c r="K30" t="n">
-        <v>31.91</v>
+        <v>92.78</v>
       </c>
       <c r="L30" t="n">
-        <v>37.23</v>
+        <v>108.24</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-3.78</v>
+        <v>-5.03</v>
       </c>
       <c r="K31" t="n">
-        <v>90.14</v>
+        <v>120</v>
       </c>
       <c r="L31" t="n">
-        <v>90.22</v>
+        <v>120.11</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>13.08</v>
+        <v>29.41</v>
       </c>
       <c r="K32" t="n">
-        <v>-36.57</v>
+        <v>-82.23999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>38.84</v>
+        <v>87.34</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>45.33</v>
+        <v>115.97</v>
       </c>
       <c r="K33" t="n">
-        <v>-41.7</v>
+        <v>-106.68</v>
       </c>
       <c r="L33" t="n">
-        <v>61.6</v>
+        <v>157.57</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-33.41</v>
+        <v>-37.54</v>
       </c>
       <c r="K34" t="n">
-        <v>-100.06</v>
+        <v>-112.45</v>
       </c>
       <c r="L34" t="n">
-        <v>105.49</v>
+        <v>118.55</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>154.93</v>
+        <v>202.8</v>
       </c>
       <c r="K35" t="n">
-        <v>157.56</v>
+        <v>206.25</v>
       </c>
       <c r="L35" t="n">
-        <v>220.97</v>
+        <v>289.25</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>233.52</v>
+        <v>311.01</v>
       </c>
       <c r="K36" t="n">
-        <v>-184.93</v>
+        <v>-246.29</v>
       </c>
       <c r="L36" t="n">
-        <v>297.88</v>
+        <v>396.72</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-306.52</v>
+        <v>-382.64</v>
       </c>
       <c r="K37" t="n">
-        <v>12.95</v>
+        <v>16.17</v>
       </c>
       <c r="L37" t="n">
-        <v>306.79</v>
+        <v>382.98</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-78.95999999999999</v>
+        <v>-99.29000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>325.55</v>
+        <v>409.36</v>
       </c>
       <c r="L38" t="n">
-        <v>334.99</v>
+        <v>421.23</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-190.43</v>
+        <v>-277.34</v>
       </c>
       <c r="K39" t="n">
-        <v>-41.71</v>
+        <v>-60.75</v>
       </c>
       <c r="L39" t="n">
-        <v>194.95</v>
+        <v>283.92</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>99.70999999999999</v>
+        <v>115.53</v>
       </c>
       <c r="K40" t="n">
-        <v>-317.29</v>
+        <v>-367.63</v>
       </c>
       <c r="L40" t="n">
-        <v>332.59</v>
+        <v>385.36</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-906.88</v>
+        <v>-1049.84</v>
       </c>
       <c r="K41" t="n">
-        <v>390.85</v>
+        <v>452.46</v>
       </c>
       <c r="L41" t="n">
-        <v>987.52</v>
+        <v>1143.19</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>-415.13</v>
+        <v>-612.78</v>
       </c>
       <c r="K42" t="n">
-        <v>-159.49</v>
+        <v>-235.44</v>
       </c>
       <c r="L42" t="n">
-        <v>444.71</v>
+        <v>656.45</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-70.54000000000001</v>
+        <v>-88.22</v>
       </c>
       <c r="K43" t="n">
-        <v>-708.12</v>
+        <v>-885.61</v>
       </c>
       <c r="L43" t="n">
-        <v>711.63</v>
+        <v>890</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>-68.56999999999999</v>
+        <v>-99.41</v>
       </c>
       <c r="K44" t="n">
-        <v>-17.22</v>
+        <v>-24.97</v>
       </c>
       <c r="L44" t="n">
-        <v>70.7</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-48.02</v>
+        <v>-59.26</v>
       </c>
       <c r="K45" t="n">
-        <v>-67.65000000000001</v>
+        <v>-83.48999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>82.95999999999999</v>
+        <v>102.38</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-15.2</v>
+        <v>-15.78</v>
       </c>
       <c r="K46" t="n">
-        <v>-118.92</v>
+        <v>-123.46</v>
       </c>
       <c r="L46" t="n">
-        <v>119.89</v>
+        <v>124.47</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-76.19</v>
+        <v>-71.25</v>
       </c>
       <c r="K47" t="n">
-        <v>190.35</v>
+        <v>177.99</v>
       </c>
       <c r="L47" t="n">
-        <v>205.03</v>
+        <v>191.72</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>156.77</v>
+        <v>175</v>
       </c>
       <c r="K48" t="n">
-        <v>119.35</v>
+        <v>133.23</v>
       </c>
       <c r="L48" t="n">
-        <v>197.04</v>
+        <v>219.95</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-147.12</v>
+        <v>-138.15</v>
       </c>
       <c r="K49" t="n">
-        <v>-96.27</v>
+        <v>-90.40000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>175.82</v>
+        <v>165.1</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>188.84</v>
+        <v>228.33</v>
       </c>
       <c r="K50" t="n">
-        <v>213.69</v>
+        <v>258.38</v>
       </c>
       <c r="L50" t="n">
-        <v>285.17</v>
+        <v>344.82</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>327.8</v>
+        <v>420.09</v>
       </c>
       <c r="K51" t="n">
-        <v>-114.62</v>
+        <v>-146.89</v>
       </c>
       <c r="L51" t="n">
-        <v>347.26</v>
+        <v>445.03</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>78.23999999999999</v>
+        <v>167.84</v>
       </c>
       <c r="K52" t="n">
-        <v>-11.67</v>
+        <v>-25.03</v>
       </c>
       <c r="L52" t="n">
-        <v>79.09999999999999</v>
+        <v>169.69</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>-306.7</v>
+        <v>-379.76</v>
       </c>
       <c r="K53" t="n">
-        <v>456.23</v>
+        <v>564.92</v>
       </c>
       <c r="L53" t="n">
-        <v>549.74</v>
+        <v>680.7</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>-31.59</v>
+        <v>-64.95</v>
       </c>
       <c r="K54" t="n">
-        <v>-133.9</v>
+        <v>-275.29</v>
       </c>
       <c r="L54" t="n">
-        <v>137.57</v>
+        <v>282.85</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-72.92</v>
+        <v>-186.02</v>
       </c>
       <c r="K55" t="n">
-        <v>52.55</v>
+        <v>134.07</v>
       </c>
       <c r="L55" t="n">
-        <v>89.88</v>
+        <v>229.3</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>307.3</v>
+        <v>559.26</v>
       </c>
       <c r="K56" t="n">
-        <v>90.88</v>
+        <v>165.39</v>
       </c>
       <c r="L56" t="n">
-        <v>320.46</v>
+        <v>583.2</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-646.83</v>
+        <v>-818.6900000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>-238.39</v>
+        <v>-301.73</v>
       </c>
       <c r="L57" t="n">
-        <v>689.36</v>
+        <v>872.52</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-242.98</v>
+        <v>-298.91</v>
       </c>
       <c r="K58" t="n">
-        <v>-657.29</v>
+        <v>-808.59</v>
       </c>
       <c r="L58" t="n">
-        <v>700.76</v>
+        <v>862.0700000000001</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-27.88</v>
+        <v>-27.15</v>
       </c>
       <c r="K59" t="n">
-        <v>-238.17</v>
+        <v>-232.01</v>
       </c>
       <c r="L59" t="n">
-        <v>239.8</v>
+        <v>233.59</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-24.03</v>
+        <v>-20.66</v>
       </c>
       <c r="K60" t="n">
-        <v>278.99</v>
+        <v>239.92</v>
       </c>
       <c r="L60" t="n">
-        <v>280.02</v>
+        <v>240.81</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-203.71</v>
+        <v>-216.45</v>
       </c>
       <c r="K61" t="n">
-        <v>-105.39</v>
+        <v>-111.98</v>
       </c>
       <c r="L61" t="n">
-        <v>229.36</v>
+        <v>243.7</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>-54.99</v>
+        <v>-76.17</v>
       </c>
       <c r="K62" t="n">
-        <v>114.89</v>
+        <v>159.15</v>
       </c>
       <c r="L62" t="n">
-        <v>127.37</v>
+        <v>176.44</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>223.69</v>
+        <v>210.74</v>
       </c>
       <c r="K63" t="n">
-        <v>-208.54</v>
+        <v>-196.46</v>
       </c>
       <c r="L63" t="n">
-        <v>305.82</v>
+        <v>288.11</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>146.7</v>
+        <v>188.17</v>
       </c>
       <c r="K64" t="n">
-        <v>89.2</v>
+        <v>114.42</v>
       </c>
       <c r="L64" t="n">
-        <v>171.69</v>
+        <v>220.22</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>-173.41</v>
+        <v>-245.58</v>
       </c>
       <c r="K65" t="n">
-        <v>-209.4</v>
+        <v>-296.56</v>
       </c>
       <c r="L65" t="n">
-        <v>271.88</v>
+        <v>385.04</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-142.51</v>
+        <v>-244.35</v>
       </c>
       <c r="K66" t="n">
-        <v>-45.12</v>
+        <v>-77.37</v>
       </c>
       <c r="L66" t="n">
-        <v>149.48</v>
+        <v>256.31</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-260.16</v>
+        <v>-318.9</v>
       </c>
       <c r="K67" t="n">
-        <v>-165.77</v>
+        <v>-203.21</v>
       </c>
       <c r="L67" t="n">
-        <v>308.48</v>
+        <v>378.14</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-278.28</v>
+        <v>-309.87</v>
       </c>
       <c r="K68" t="n">
-        <v>-458.83</v>
+        <v>-510.91</v>
       </c>
       <c r="L68" t="n">
-        <v>536.62</v>
+        <v>597.54</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-407.77</v>
+        <v>-507.16</v>
       </c>
       <c r="K69" t="n">
-        <v>-53.13</v>
+        <v>-66.08</v>
       </c>
       <c r="L69" t="n">
-        <v>411.22</v>
+        <v>511.45</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-438.83</v>
+        <v>-499.29</v>
       </c>
       <c r="K70" t="n">
-        <v>15.01</v>
+        <v>17.07</v>
       </c>
       <c r="L70" t="n">
-        <v>439.08</v>
+        <v>499.58</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-333.2</v>
+        <v>-520.14</v>
       </c>
       <c r="K71" t="n">
-        <v>-274.79</v>
+        <v>-428.96</v>
       </c>
       <c r="L71" t="n">
-        <v>431.89</v>
+        <v>674.21</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>1186.42</v>
+        <v>1378.97</v>
       </c>
       <c r="K72" t="n">
-        <v>-683.36</v>
+        <v>-794.27</v>
       </c>
       <c r="L72" t="n">
-        <v>1369.15</v>
+        <v>1591.36</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>625.71</v>
+        <v>846.17</v>
       </c>
       <c r="K73" t="n">
-        <v>161.86</v>
+        <v>218.88</v>
       </c>
       <c r="L73" t="n">
-        <v>646.3099999999999</v>
+        <v>874.02</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>-190.5</v>
+        <v>-202.55</v>
       </c>
       <c r="K74" t="n">
-        <v>117.22</v>
+        <v>124.64</v>
       </c>
       <c r="L74" t="n">
-        <v>223.68</v>
+        <v>237.83</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>17</v>
       </c>
       <c r="J75" t="n">
-        <v>59.37</v>
+        <v>104.72</v>
       </c>
       <c r="K75" t="n">
-        <v>53.55</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>79.95</v>
+        <v>141.03</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>69.29000000000001</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>83.47</v>
+        <v>109.61</v>
       </c>
       <c r="L76" t="n">
-        <v>108.48</v>
+        <v>142.45</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>58.51</v>
+        <v>67.47</v>
       </c>
       <c r="K77" t="n">
-        <v>-169.64</v>
+        <v>-195.61</v>
       </c>
       <c r="L77" t="n">
-        <v>179.45</v>
+        <v>206.91</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>114.51</v>
+        <v>155.3</v>
       </c>
       <c r="K78" t="n">
-        <v>33.74</v>
+        <v>45.75</v>
       </c>
       <c r="L78" t="n">
-        <v>119.38</v>
+        <v>161.9</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>59.91</v>
+        <v>106.37</v>
       </c>
       <c r="K79" t="n">
-        <v>-16.96</v>
+        <v>-30.11</v>
       </c>
       <c r="L79" t="n">
-        <v>62.26</v>
+        <v>110.55</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-265.96</v>
+        <v>-302.33</v>
       </c>
       <c r="K80" t="n">
-        <v>-63.31</v>
+        <v>-71.97</v>
       </c>
       <c r="L80" t="n">
-        <v>273.39</v>
+        <v>310.77</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-298.42</v>
+        <v>-332.2</v>
       </c>
       <c r="K81" t="n">
-        <v>-111.16</v>
+        <v>-123.74</v>
       </c>
       <c r="L81" t="n">
-        <v>318.45</v>
+        <v>354.5</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-145.05</v>
+        <v>-160.23</v>
       </c>
       <c r="K82" t="n">
-        <v>351.1</v>
+        <v>387.85</v>
       </c>
       <c r="L82" t="n">
-        <v>379.88</v>
+        <v>419.65</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>346.65</v>
+        <v>448.19</v>
       </c>
       <c r="K83" t="n">
-        <v>-392.83</v>
+        <v>-507.9</v>
       </c>
       <c r="L83" t="n">
-        <v>523.91</v>
+        <v>677.38</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>-32.9</v>
+        <v>-63.44</v>
       </c>
       <c r="K84" t="n">
-        <v>-149.59</v>
+        <v>-288.46</v>
       </c>
       <c r="L84" t="n">
-        <v>153.16</v>
+        <v>295.35</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>237.43</v>
+        <v>308.83</v>
       </c>
       <c r="K85" t="n">
-        <v>-415.91</v>
+        <v>-540.98</v>
       </c>
       <c r="L85" t="n">
-        <v>478.91</v>
+        <v>622.9299999999999</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>269.75</v>
+        <v>451.05</v>
       </c>
       <c r="K86" t="n">
-        <v>119.41</v>
+        <v>199.66</v>
       </c>
       <c r="L86" t="n">
-        <v>295</v>
+        <v>493.26</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>868.61</v>
+        <v>1133.87</v>
       </c>
       <c r="K87" t="n">
-        <v>-43.39</v>
+        <v>-56.64</v>
       </c>
       <c r="L87" t="n">
-        <v>869.7</v>
+        <v>1135.28</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-20.99</v>
+        <v>-60.68</v>
       </c>
       <c r="K88" t="n">
-        <v>-110.29</v>
+        <v>-318.81</v>
       </c>
       <c r="L88" t="n">
-        <v>112.27</v>
+        <v>324.53</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-03.xlsx
+++ b/output/2025-10-03.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.24</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>135.57</v>
+        <v>102.29</v>
       </c>
       <c r="L14" t="n">
-        <v>135.58</v>
+        <v>102.3</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>8.56</v>
+        <v>6.01</v>
       </c>
       <c r="K15" t="n">
-        <v>-270.87</v>
+        <v>-190.25</v>
       </c>
       <c r="L15" t="n">
-        <v>271.01</v>
+        <v>190.35</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>13.88</v>
+        <v>9.74</v>
       </c>
       <c r="K16" t="n">
-        <v>144.82</v>
+        <v>101.62</v>
       </c>
       <c r="L16" t="n">
-        <v>145.49</v>
+        <v>102.08</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>34.6</v>
+        <v>26</v>
       </c>
       <c r="K17" t="n">
-        <v>-141.34</v>
+        <v>-106.19</v>
       </c>
       <c r="L17" t="n">
-        <v>145.52</v>
+        <v>109.33</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>9.960000000000001</v>
+        <v>6.87</v>
       </c>
       <c r="K18" t="n">
-        <v>-257.31</v>
+        <v>-177.51</v>
       </c>
       <c r="L18" t="n">
-        <v>257.5</v>
+        <v>177.65</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>-15.49</v>
+        <v>-11.36</v>
       </c>
       <c r="K19" t="n">
-        <v>-112.08</v>
+        <v>-82.20999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>113.14</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>6.67</v>
+        <v>4.27</v>
       </c>
       <c r="K20" t="n">
-        <v>-303.95</v>
+        <v>-194.61</v>
       </c>
       <c r="L20" t="n">
-        <v>304.03</v>
+        <v>194.66</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>176.58</v>
+        <v>109.54</v>
       </c>
       <c r="K21" t="n">
-        <v>-21.77</v>
+        <v>-13.51</v>
       </c>
       <c r="L21" t="n">
-        <v>177.92</v>
+        <v>110.37</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>252.61</v>
+        <v>160.31</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.2</v>
+        <v>-2.67</v>
       </c>
       <c r="L22" t="n">
-        <v>252.65</v>
+        <v>160.33</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>224.25</v>
+        <v>111.97</v>
       </c>
       <c r="K23" t="n">
-        <v>-326.55</v>
+        <v>-163.06</v>
       </c>
       <c r="L23" t="n">
-        <v>396.14</v>
+        <v>197.8</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>328.42</v>
+        <v>181.83</v>
       </c>
       <c r="K24" t="n">
-        <v>14.36</v>
+        <v>7.95</v>
       </c>
       <c r="L24" t="n">
-        <v>328.73</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>-152.56</v>
+        <v>-86.28</v>
       </c>
       <c r="K25" t="n">
-        <v>-310.11</v>
+        <v>-175.39</v>
       </c>
       <c r="L25" t="n">
-        <v>345.6</v>
+        <v>195.46</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>278.49</v>
+        <v>146.31</v>
       </c>
       <c r="K26" t="n">
-        <v>-534.39</v>
+        <v>-280.74</v>
       </c>
       <c r="L26" t="n">
-        <v>602.6</v>
+        <v>316.58</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>461.5</v>
+        <v>219.52</v>
       </c>
       <c r="K27" t="n">
-        <v>548.22</v>
+        <v>260.78</v>
       </c>
       <c r="L27" t="n">
-        <v>716.61</v>
+        <v>340.87</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-264.47</v>
+        <v>-125.89</v>
       </c>
       <c r="K28" t="n">
-        <v>381.99</v>
+        <v>181.83</v>
       </c>
       <c r="L28" t="n">
-        <v>464.61</v>
+        <v>221.16</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>55.91</v>
+        <v>39.78</v>
       </c>
       <c r="K29" t="n">
-        <v>73.84</v>
+        <v>52.54</v>
       </c>
       <c r="L29" t="n">
-        <v>92.61</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>55.76</v>
+        <v>36.42</v>
       </c>
       <c r="K30" t="n">
-        <v>92.78</v>
+        <v>60.6</v>
       </c>
       <c r="L30" t="n">
-        <v>108.24</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-5.03</v>
+        <v>-3.39</v>
       </c>
       <c r="K31" t="n">
-        <v>120</v>
+        <v>80.92</v>
       </c>
       <c r="L31" t="n">
-        <v>120.11</v>
+        <v>80.98999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>29.41</v>
+        <v>21.5</v>
       </c>
       <c r="K32" t="n">
-        <v>-82.23999999999999</v>
+        <v>-60.14</v>
       </c>
       <c r="L32" t="n">
-        <v>87.34</v>
+        <v>63.87</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>115.97</v>
+        <v>69.52</v>
       </c>
       <c r="K33" t="n">
-        <v>-106.68</v>
+        <v>-63.95</v>
       </c>
       <c r="L33" t="n">
-        <v>157.57</v>
+        <v>94.45999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-37.54</v>
+        <v>-27.94</v>
       </c>
       <c r="K34" t="n">
-        <v>-112.45</v>
+        <v>-83.68000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>118.55</v>
+        <v>88.22</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>202.8</v>
+        <v>115.24</v>
       </c>
       <c r="K35" t="n">
-        <v>206.25</v>
+        <v>117.2</v>
       </c>
       <c r="L35" t="n">
-        <v>289.25</v>
+        <v>164.37</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>311.01</v>
+        <v>166.55</v>
       </c>
       <c r="K36" t="n">
-        <v>-246.29</v>
+        <v>-131.9</v>
       </c>
       <c r="L36" t="n">
-        <v>396.72</v>
+        <v>212.45</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-382.64</v>
+        <v>-205.54</v>
       </c>
       <c r="K37" t="n">
-        <v>16.17</v>
+        <v>8.69</v>
       </c>
       <c r="L37" t="n">
-        <v>382.98</v>
+        <v>205.72</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-99.29000000000001</v>
+        <v>-51.67</v>
       </c>
       <c r="K38" t="n">
-        <v>409.36</v>
+        <v>213.01</v>
       </c>
       <c r="L38" t="n">
-        <v>421.23</v>
+        <v>219.19</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-277.34</v>
+        <v>-150.61</v>
       </c>
       <c r="K39" t="n">
-        <v>-60.75</v>
+        <v>-32.99</v>
       </c>
       <c r="L39" t="n">
-        <v>283.92</v>
+        <v>154.19</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>115.53</v>
+        <v>64.23</v>
       </c>
       <c r="K40" t="n">
-        <v>-367.63</v>
+        <v>-204.37</v>
       </c>
       <c r="L40" t="n">
-        <v>385.36</v>
+        <v>214.23</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-1049.84</v>
+        <v>-483.57</v>
       </c>
       <c r="K41" t="n">
-        <v>452.46</v>
+        <v>208.41</v>
       </c>
       <c r="L41" t="n">
-        <v>1143.19</v>
+        <v>526.5700000000001</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>-612.78</v>
+        <v>-272.53</v>
       </c>
       <c r="K42" t="n">
-        <v>-235.44</v>
+        <v>-104.71</v>
       </c>
       <c r="L42" t="n">
-        <v>656.45</v>
+        <v>291.95</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-88.22</v>
+        <v>-39.38</v>
       </c>
       <c r="K43" t="n">
-        <v>-885.61</v>
+        <v>-395.34</v>
       </c>
       <c r="L43" t="n">
-        <v>890</v>
+        <v>397.3</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>-99.41</v>
+        <v>-68.68000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>-24.97</v>
+        <v>-17.25</v>
       </c>
       <c r="L44" t="n">
-        <v>102.5</v>
+        <v>70.81</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-59.26</v>
+        <v>-45.81</v>
       </c>
       <c r="K45" t="n">
-        <v>-83.48999999999999</v>
+        <v>-64.54000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>102.38</v>
+        <v>79.14</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-15.78</v>
+        <v>-12.02</v>
       </c>
       <c r="K46" t="n">
-        <v>-123.46</v>
+        <v>-94.08</v>
       </c>
       <c r="L46" t="n">
-        <v>124.47</v>
+        <v>94.84</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-71.25</v>
+        <v>-50.86</v>
       </c>
       <c r="K47" t="n">
-        <v>177.99</v>
+        <v>127.05</v>
       </c>
       <c r="L47" t="n">
-        <v>191.72</v>
+        <v>136.85</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>175</v>
+        <v>115.46</v>
       </c>
       <c r="K48" t="n">
-        <v>133.23</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>219.95</v>
+        <v>145.11</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-138.15</v>
+        <v>-102.1</v>
       </c>
       <c r="K49" t="n">
-        <v>-90.40000000000001</v>
+        <v>-66.81</v>
       </c>
       <c r="L49" t="n">
-        <v>165.1</v>
+        <v>122.02</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>228.33</v>
+        <v>128.87</v>
       </c>
       <c r="K50" t="n">
-        <v>258.38</v>
+        <v>145.83</v>
       </c>
       <c r="L50" t="n">
-        <v>344.82</v>
+        <v>194.61</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>420.09</v>
+        <v>227.37</v>
       </c>
       <c r="K51" t="n">
-        <v>-146.89</v>
+        <v>-79.5</v>
       </c>
       <c r="L51" t="n">
-        <v>445.03</v>
+        <v>240.87</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>167.84</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>-25.03</v>
+        <v>-14.87</v>
       </c>
       <c r="L52" t="n">
-        <v>169.69</v>
+        <v>100.81</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>-379.76</v>
+        <v>-179.1</v>
       </c>
       <c r="K53" t="n">
-        <v>564.92</v>
+        <v>266.42</v>
       </c>
       <c r="L53" t="n">
-        <v>680.7</v>
+        <v>321.02</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>-64.95</v>
+        <v>-32.39</v>
       </c>
       <c r="K54" t="n">
-        <v>-275.29</v>
+        <v>-137.27</v>
       </c>
       <c r="L54" t="n">
-        <v>282.85</v>
+        <v>141.04</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-186.02</v>
+        <v>-97.43000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>134.07</v>
+        <v>70.22</v>
       </c>
       <c r="L55" t="n">
-        <v>229.3</v>
+        <v>120.1</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>559.26</v>
+        <v>243.27</v>
       </c>
       <c r="K56" t="n">
-        <v>165.39</v>
+        <v>71.94</v>
       </c>
       <c r="L56" t="n">
-        <v>583.2</v>
+        <v>253.69</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-818.6900000000001</v>
+        <v>-383.99</v>
       </c>
       <c r="K57" t="n">
-        <v>-301.73</v>
+        <v>-141.52</v>
       </c>
       <c r="L57" t="n">
-        <v>872.52</v>
+        <v>409.24</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-298.91</v>
+        <v>-136.51</v>
       </c>
       <c r="K58" t="n">
-        <v>-808.59</v>
+        <v>-369.29</v>
       </c>
       <c r="L58" t="n">
-        <v>862.0700000000001</v>
+        <v>393.71</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-27.15</v>
+        <v>-18.23</v>
       </c>
       <c r="K59" t="n">
-        <v>-232.01</v>
+        <v>-155.75</v>
       </c>
       <c r="L59" t="n">
-        <v>233.59</v>
+        <v>156.81</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-20.66</v>
+        <v>-15.66</v>
       </c>
       <c r="K60" t="n">
-        <v>239.92</v>
+        <v>181.85</v>
       </c>
       <c r="L60" t="n">
-        <v>240.81</v>
+        <v>182.52</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-216.45</v>
+        <v>-143.65</v>
       </c>
       <c r="K61" t="n">
-        <v>-111.98</v>
+        <v>-74.31999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>243.7</v>
+        <v>161.74</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>-76.17</v>
+        <v>-47.96</v>
       </c>
       <c r="K62" t="n">
-        <v>159.15</v>
+        <v>100.22</v>
       </c>
       <c r="L62" t="n">
-        <v>176.44</v>
+        <v>111.1</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>210.74</v>
+        <v>146.51</v>
       </c>
       <c r="K63" t="n">
-        <v>-196.46</v>
+        <v>-136.58</v>
       </c>
       <c r="L63" t="n">
-        <v>288.11</v>
+        <v>200.3</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>188.17</v>
+        <v>118.65</v>
       </c>
       <c r="K64" t="n">
-        <v>114.42</v>
+        <v>72.14</v>
       </c>
       <c r="L64" t="n">
-        <v>220.22</v>
+        <v>138.86</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>-245.58</v>
+        <v>-132.48</v>
       </c>
       <c r="K65" t="n">
-        <v>-296.56</v>
+        <v>-159.98</v>
       </c>
       <c r="L65" t="n">
-        <v>385.04</v>
+        <v>207.71</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-244.35</v>
+        <v>-130.63</v>
       </c>
       <c r="K66" t="n">
-        <v>-77.37</v>
+        <v>-41.36</v>
       </c>
       <c r="L66" t="n">
-        <v>256.31</v>
+        <v>137.02</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-318.9</v>
+        <v>-172.16</v>
       </c>
       <c r="K67" t="n">
-        <v>-203.21</v>
+        <v>-109.7</v>
       </c>
       <c r="L67" t="n">
-        <v>378.14</v>
+        <v>204.14</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-309.87</v>
+        <v>-169.21</v>
       </c>
       <c r="K68" t="n">
-        <v>-510.91</v>
+        <v>-279</v>
       </c>
       <c r="L68" t="n">
-        <v>597.54</v>
+        <v>326.3</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-507.16</v>
+        <v>-258.42</v>
       </c>
       <c r="K69" t="n">
-        <v>-66.08</v>
+        <v>-33.67</v>
       </c>
       <c r="L69" t="n">
-        <v>511.45</v>
+        <v>260.61</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-499.29</v>
+        <v>-265.48</v>
       </c>
       <c r="K70" t="n">
-        <v>17.07</v>
+        <v>9.08</v>
       </c>
       <c r="L70" t="n">
-        <v>499.58</v>
+        <v>265.63</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-520.14</v>
+        <v>-224.36</v>
       </c>
       <c r="K71" t="n">
-        <v>-428.96</v>
+        <v>-185.03</v>
       </c>
       <c r="L71" t="n">
-        <v>674.21</v>
+        <v>290.81</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>1378.97</v>
+        <v>598.3</v>
       </c>
       <c r="K72" t="n">
-        <v>-794.27</v>
+        <v>-344.61</v>
       </c>
       <c r="L72" t="n">
-        <v>1591.36</v>
+        <v>690.45</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>846.17</v>
+        <v>377.05</v>
       </c>
       <c r="K73" t="n">
-        <v>218.88</v>
+        <v>97.53</v>
       </c>
       <c r="L73" t="n">
-        <v>874.02</v>
+        <v>389.46</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>-202.55</v>
+        <v>-139.63</v>
       </c>
       <c r="K74" t="n">
-        <v>124.64</v>
+        <v>85.92</v>
       </c>
       <c r="L74" t="n">
-        <v>237.83</v>
+        <v>163.95</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>17</v>
       </c>
       <c r="J75" t="n">
-        <v>104.72</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>94.45999999999999</v>
+        <v>60.57</v>
       </c>
       <c r="L75" t="n">
-        <v>141.03</v>
+        <v>90.43000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>90.98999999999999</v>
+        <v>66.58</v>
       </c>
       <c r="K76" t="n">
-        <v>109.61</v>
+        <v>80.2</v>
       </c>
       <c r="L76" t="n">
-        <v>142.45</v>
+        <v>104.23</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>67.47</v>
+        <v>45.35</v>
       </c>
       <c r="K77" t="n">
-        <v>-195.61</v>
+        <v>-131.48</v>
       </c>
       <c r="L77" t="n">
-        <v>206.91</v>
+        <v>139.08</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>155.3</v>
+        <v>102.67</v>
       </c>
       <c r="K78" t="n">
-        <v>45.75</v>
+        <v>30.25</v>
       </c>
       <c r="L78" t="n">
-        <v>161.9</v>
+        <v>107.04</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>106.37</v>
+        <v>73.20999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>-30.11</v>
+        <v>-20.72</v>
       </c>
       <c r="L79" t="n">
-        <v>110.55</v>
+        <v>76.08</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-302.33</v>
+        <v>-188.59</v>
       </c>
       <c r="K80" t="n">
-        <v>-71.97</v>
+        <v>-44.89</v>
       </c>
       <c r="L80" t="n">
-        <v>310.77</v>
+        <v>193.86</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-332.2</v>
+        <v>-201.11</v>
       </c>
       <c r="K81" t="n">
-        <v>-123.74</v>
+        <v>-74.91</v>
       </c>
       <c r="L81" t="n">
-        <v>354.5</v>
+        <v>214.6</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-160.23</v>
+        <v>-89.13</v>
       </c>
       <c r="K82" t="n">
-        <v>387.85</v>
+        <v>215.73</v>
       </c>
       <c r="L82" t="n">
-        <v>419.65</v>
+        <v>233.42</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>448.19</v>
+        <v>209.24</v>
       </c>
       <c r="K83" t="n">
-        <v>-507.9</v>
+        <v>-237.11</v>
       </c>
       <c r="L83" t="n">
-        <v>677.38</v>
+        <v>316.23</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>-63.44</v>
+        <v>-32.86</v>
       </c>
       <c r="K84" t="n">
-        <v>-288.46</v>
+        <v>-149.38</v>
       </c>
       <c r="L84" t="n">
-        <v>295.35</v>
+        <v>152.95</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>308.83</v>
+        <v>155.49</v>
       </c>
       <c r="K85" t="n">
-        <v>-540.98</v>
+        <v>-272.37</v>
       </c>
       <c r="L85" t="n">
-        <v>622.9299999999999</v>
+        <v>313.62</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>451.05</v>
+        <v>214.34</v>
       </c>
       <c r="K86" t="n">
-        <v>199.66</v>
+        <v>94.88</v>
       </c>
       <c r="L86" t="n">
-        <v>493.26</v>
+        <v>234.4</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>1133.87</v>
+        <v>481.23</v>
       </c>
       <c r="K87" t="n">
-        <v>-56.64</v>
+        <v>-24.04</v>
       </c>
       <c r="L87" t="n">
-        <v>1135.28</v>
+        <v>481.83</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-60.68</v>
+        <v>-30.22</v>
       </c>
       <c r="K88" t="n">
-        <v>-318.81</v>
+        <v>-158.78</v>
       </c>
       <c r="L88" t="n">
-        <v>324.53</v>
+        <v>161.64</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-03.xlsx
+++ b/output/2025-10-03.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.99</v>
       </c>
       <c r="K14" t="n">
-        <v>102.29</v>
+        <v>107.66</v>
       </c>
       <c r="L14" t="n">
-        <v>102.3</v>
+        <v>107.67</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>6.01</v>
+        <v>6.3</v>
       </c>
       <c r="K15" t="n">
-        <v>-190.25</v>
+        <v>-199.42</v>
       </c>
       <c r="L15" t="n">
-        <v>190.35</v>
+        <v>199.51</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>9.74</v>
+        <v>10.27</v>
       </c>
       <c r="K16" t="n">
-        <v>101.62</v>
+        <v>107.17</v>
       </c>
       <c r="L16" t="n">
-        <v>102.08</v>
+        <v>107.66</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>26</v>
+        <v>28.13</v>
       </c>
       <c r="K17" t="n">
-        <v>-106.19</v>
+        <v>-114.91</v>
       </c>
       <c r="L17" t="n">
-        <v>109.33</v>
+        <v>118.31</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>6.87</v>
+        <v>7.58</v>
       </c>
       <c r="K18" t="n">
-        <v>-177.51</v>
+        <v>-195.77</v>
       </c>
       <c r="L18" t="n">
-        <v>177.65</v>
+        <v>195.91</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>-11.36</v>
+        <v>-12.33</v>
       </c>
       <c r="K19" t="n">
-        <v>-82.20999999999999</v>
+        <v>-89.22</v>
       </c>
       <c r="L19" t="n">
-        <v>83</v>
+        <v>90.06999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>4.27</v>
+        <v>4.86</v>
       </c>
       <c r="K20" t="n">
-        <v>-194.61</v>
+        <v>-221.56</v>
       </c>
       <c r="L20" t="n">
-        <v>194.66</v>
+        <v>221.62</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>109.54</v>
+        <v>122.96</v>
       </c>
       <c r="K21" t="n">
-        <v>-13.51</v>
+        <v>-15.16</v>
       </c>
       <c r="L21" t="n">
-        <v>110.37</v>
+        <v>123.89</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>160.31</v>
+        <v>180.29</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.67</v>
+        <v>-3</v>
       </c>
       <c r="L22" t="n">
-        <v>160.33</v>
+        <v>180.32</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>111.97</v>
+        <v>131.83</v>
       </c>
       <c r="K23" t="n">
-        <v>-163.06</v>
+        <v>-191.97</v>
       </c>
       <c r="L23" t="n">
-        <v>197.8</v>
+        <v>232.88</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>181.83</v>
+        <v>210.34</v>
       </c>
       <c r="K24" t="n">
-        <v>7.95</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>182</v>
+        <v>210.54</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>-86.28</v>
+        <v>-99.53</v>
       </c>
       <c r="K25" t="n">
-        <v>-175.39</v>
+        <v>-202.32</v>
       </c>
       <c r="L25" t="n">
-        <v>195.46</v>
+        <v>225.47</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>146.31</v>
+        <v>171.09</v>
       </c>
       <c r="K26" t="n">
-        <v>-280.74</v>
+        <v>-328.29</v>
       </c>
       <c r="L26" t="n">
-        <v>316.58</v>
+        <v>370.19</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>219.52</v>
+        <v>260.04</v>
       </c>
       <c r="K27" t="n">
-        <v>260.78</v>
+        <v>308.91</v>
       </c>
       <c r="L27" t="n">
-        <v>340.87</v>
+        <v>403.79</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-125.89</v>
+        <v>-148.42</v>
       </c>
       <c r="K28" t="n">
-        <v>181.83</v>
+        <v>214.37</v>
       </c>
       <c r="L28" t="n">
-        <v>221.16</v>
+        <v>260.73</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>39.78</v>
+        <v>41.94</v>
       </c>
       <c r="K29" t="n">
-        <v>52.54</v>
+        <v>55.4</v>
       </c>
       <c r="L29" t="n">
-        <v>65.90000000000001</v>
+        <v>69.48999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>36.42</v>
+        <v>39.15</v>
       </c>
       <c r="K30" t="n">
-        <v>60.6</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>70.7</v>
+        <v>76.01000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-3.39</v>
+        <v>-3.65</v>
       </c>
       <c r="K31" t="n">
-        <v>80.92</v>
+        <v>86.92</v>
       </c>
       <c r="L31" t="n">
-        <v>80.98999999999999</v>
+        <v>86.98999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>21.5</v>
+        <v>23.53</v>
       </c>
       <c r="K32" t="n">
-        <v>-60.14</v>
+        <v>-65.81</v>
       </c>
       <c r="L32" t="n">
-        <v>63.87</v>
+        <v>69.89</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>69.52</v>
+        <v>76.55</v>
       </c>
       <c r="K33" t="n">
-        <v>-63.95</v>
+        <v>-70.42</v>
       </c>
       <c r="L33" t="n">
-        <v>94.45999999999999</v>
+        <v>104.02</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-27.94</v>
+        <v>-30.3</v>
       </c>
       <c r="K34" t="n">
-        <v>-83.68000000000001</v>
+        <v>-90.76000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>88.22</v>
+        <v>95.68000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>115.24</v>
+        <v>131.44</v>
       </c>
       <c r="K35" t="n">
-        <v>117.2</v>
+        <v>133.68</v>
       </c>
       <c r="L35" t="n">
-        <v>164.37</v>
+        <v>187.47</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="J36" t="n">
-        <v>166.55</v>
+        <v>191.21</v>
       </c>
       <c r="K36" t="n">
-        <v>-131.9</v>
+        <v>-151.42</v>
       </c>
       <c r="L36" t="n">
-        <v>212.45</v>
+        <v>243.91</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-205.54</v>
+        <v>-237.59</v>
       </c>
       <c r="K37" t="n">
-        <v>8.69</v>
+        <v>10.04</v>
       </c>
       <c r="L37" t="n">
-        <v>205.72</v>
+        <v>237.8</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-51.67</v>
+        <v>-60.47</v>
       </c>
       <c r="K38" t="n">
-        <v>213.01</v>
+        <v>249.29</v>
       </c>
       <c r="L38" t="n">
-        <v>219.19</v>
+        <v>256.52</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-150.61</v>
+        <v>-175.04</v>
       </c>
       <c r="K39" t="n">
-        <v>-32.99</v>
+        <v>-38.34</v>
       </c>
       <c r="L39" t="n">
-        <v>154.19</v>
+        <v>179.19</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>64.23</v>
+        <v>74.45</v>
       </c>
       <c r="K40" t="n">
-        <v>-204.37</v>
+        <v>-236.9</v>
       </c>
       <c r="L40" t="n">
-        <v>214.23</v>
+        <v>248.33</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-483.57</v>
+        <v>-571.21</v>
       </c>
       <c r="K41" t="n">
-        <v>208.41</v>
+        <v>246.18</v>
       </c>
       <c r="L41" t="n">
-        <v>526.5700000000001</v>
+        <v>622</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>-272.53</v>
+        <v>-326.65</v>
       </c>
       <c r="K42" t="n">
-        <v>-104.71</v>
+        <v>-125.5</v>
       </c>
       <c r="L42" t="n">
-        <v>291.95</v>
+        <v>349.93</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-39.38</v>
+        <v>-47.05</v>
       </c>
       <c r="K43" t="n">
-        <v>-395.34</v>
+        <v>-472.35</v>
       </c>
       <c r="L43" t="n">
-        <v>397.3</v>
+        <v>474.69</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>-68.68000000000001</v>
+        <v>-73.81</v>
       </c>
       <c r="K44" t="n">
-        <v>-17.25</v>
+        <v>-18.54</v>
       </c>
       <c r="L44" t="n">
-        <v>70.81</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-45.81</v>
+        <v>-48.07</v>
       </c>
       <c r="K45" t="n">
-        <v>-64.54000000000001</v>
+        <v>-67.73</v>
       </c>
       <c r="L45" t="n">
-        <v>79.14</v>
+        <v>83.06</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.02</v>
+        <v>-12.73</v>
       </c>
       <c r="K46" t="n">
-        <v>-94.08</v>
+        <v>-99.56</v>
       </c>
       <c r="L46" t="n">
-        <v>94.84</v>
+        <v>100.37</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-50.86</v>
+        <v>-55.7</v>
       </c>
       <c r="K47" t="n">
-        <v>127.05</v>
+        <v>139.17</v>
       </c>
       <c r="L47" t="n">
-        <v>136.85</v>
+        <v>149.9</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>115.46</v>
+        <v>129</v>
       </c>
       <c r="K48" t="n">
-        <v>87.90000000000001</v>
+        <v>98.20999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>145.11</v>
+        <v>162.13</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-102.1</v>
+        <v>-110.77</v>
       </c>
       <c r="K49" t="n">
-        <v>-66.81</v>
+        <v>-72.48</v>
       </c>
       <c r="L49" t="n">
-        <v>122.02</v>
+        <v>132.38</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>128.87</v>
+        <v>148.48</v>
       </c>
       <c r="K50" t="n">
-        <v>145.83</v>
+        <v>168.02</v>
       </c>
       <c r="L50" t="n">
-        <v>194.61</v>
+        <v>224.23</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>227.37</v>
+        <v>259.68</v>
       </c>
       <c r="K51" t="n">
-        <v>-79.5</v>
+        <v>-90.8</v>
       </c>
       <c r="L51" t="n">
-        <v>240.87</v>
+        <v>275.09</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>99.70999999999999</v>
+        <v>112.89</v>
       </c>
       <c r="K52" t="n">
-        <v>-14.87</v>
+        <v>-16.84</v>
       </c>
       <c r="L52" t="n">
-        <v>100.81</v>
+        <v>114.14</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>-179.1</v>
+        <v>-210.65</v>
       </c>
       <c r="K53" t="n">
-        <v>266.42</v>
+        <v>313.35</v>
       </c>
       <c r="L53" t="n">
-        <v>321.02</v>
+        <v>377.57</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>-32.39</v>
+        <v>-38.08</v>
       </c>
       <c r="K54" t="n">
-        <v>-137.27</v>
+        <v>-161.41</v>
       </c>
       <c r="L54" t="n">
-        <v>141.04</v>
+        <v>165.84</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-97.43000000000001</v>
+        <v>-111.18</v>
       </c>
       <c r="K55" t="n">
-        <v>70.22</v>
+        <v>80.13</v>
       </c>
       <c r="L55" t="n">
-        <v>120.1</v>
+        <v>137.05</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>243.27</v>
+        <v>289.64</v>
       </c>
       <c r="K56" t="n">
-        <v>71.94</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>253.69</v>
+        <v>302.04</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-383.99</v>
+        <v>-452.06</v>
       </c>
       <c r="K57" t="n">
-        <v>-141.52</v>
+        <v>-166.6</v>
       </c>
       <c r="L57" t="n">
-        <v>409.24</v>
+        <v>481.78</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-136.51</v>
+        <v>-161.65</v>
       </c>
       <c r="K58" t="n">
-        <v>-369.29</v>
+        <v>-437.29</v>
       </c>
       <c r="L58" t="n">
-        <v>393.71</v>
+        <v>466.21</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-18.23</v>
+        <v>-19.73</v>
       </c>
       <c r="K59" t="n">
-        <v>-155.75</v>
+        <v>-168.58</v>
       </c>
       <c r="L59" t="n">
-        <v>156.81</v>
+        <v>169.73</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-15.66</v>
+        <v>-16.43</v>
       </c>
       <c r="K60" t="n">
-        <v>181.85</v>
+        <v>190.78</v>
       </c>
       <c r="L60" t="n">
-        <v>182.52</v>
+        <v>191.48</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-143.65</v>
+        <v>-152.56</v>
       </c>
       <c r="K61" t="n">
-        <v>-74.31999999999999</v>
+        <v>-78.93000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>161.74</v>
+        <v>171.77</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>-47.96</v>
+        <v>-53.6</v>
       </c>
       <c r="K62" t="n">
-        <v>100.22</v>
+        <v>111.98</v>
       </c>
       <c r="L62" t="n">
-        <v>111.1</v>
+        <v>124.15</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>146.51</v>
+        <v>161.74</v>
       </c>
       <c r="K63" t="n">
-        <v>-136.58</v>
+        <v>-150.79</v>
       </c>
       <c r="L63" t="n">
-        <v>200.3</v>
+        <v>221.13</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>118.65</v>
+        <v>132.14</v>
       </c>
       <c r="K64" t="n">
-        <v>72.14</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>138.86</v>
+        <v>154.66</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>-132.48</v>
+        <v>-151.84</v>
       </c>
       <c r="K65" t="n">
-        <v>-159.98</v>
+        <v>-183.36</v>
       </c>
       <c r="L65" t="n">
-        <v>207.71</v>
+        <v>238.07</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-130.63</v>
+        <v>-150.66</v>
       </c>
       <c r="K66" t="n">
-        <v>-41.36</v>
+        <v>-47.7</v>
       </c>
       <c r="L66" t="n">
-        <v>137.02</v>
+        <v>158.03</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-172.16</v>
+        <v>-200.92</v>
       </c>
       <c r="K67" t="n">
-        <v>-109.7</v>
+        <v>-128.03</v>
       </c>
       <c r="L67" t="n">
-        <v>204.14</v>
+        <v>238.24</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-169.21</v>
+        <v>-195.21</v>
       </c>
       <c r="K68" t="n">
-        <v>-279</v>
+        <v>-321.86</v>
       </c>
       <c r="L68" t="n">
-        <v>326.3</v>
+        <v>376.43</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-258.42</v>
+        <v>-303.38</v>
       </c>
       <c r="K69" t="n">
-        <v>-33.67</v>
+        <v>-39.53</v>
       </c>
       <c r="L69" t="n">
-        <v>260.61</v>
+        <v>305.94</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-265.48</v>
+        <v>-308.32</v>
       </c>
       <c r="K70" t="n">
-        <v>9.08</v>
+        <v>10.54</v>
       </c>
       <c r="L70" t="n">
-        <v>265.63</v>
+        <v>308.5</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-224.36</v>
+        <v>-267.53</v>
       </c>
       <c r="K71" t="n">
-        <v>-185.03</v>
+        <v>-220.63</v>
       </c>
       <c r="L71" t="n">
-        <v>290.81</v>
+        <v>346.78</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>598.3</v>
+        <v>707.34</v>
       </c>
       <c r="K72" t="n">
-        <v>-344.61</v>
+        <v>-407.42</v>
       </c>
       <c r="L72" t="n">
-        <v>690.45</v>
+        <v>816.28</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>377.05</v>
+        <v>444.91</v>
       </c>
       <c r="K73" t="n">
-        <v>97.53</v>
+        <v>115.09</v>
       </c>
       <c r="L73" t="n">
-        <v>389.46</v>
+        <v>459.56</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>-139.63</v>
+        <v>-148.22</v>
       </c>
       <c r="K74" t="n">
-        <v>85.92</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>163.95</v>
+        <v>174.03</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>17</v>
       </c>
       <c r="J75" t="n">
-        <v>67.15000000000001</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>60.57</v>
+        <v>64.98</v>
       </c>
       <c r="L75" t="n">
-        <v>90.43000000000001</v>
+        <v>97.02</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>66.58</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>80.2</v>
+        <v>84.53</v>
       </c>
       <c r="L76" t="n">
-        <v>104.23</v>
+        <v>109.87</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>45.35</v>
+        <v>49.97</v>
       </c>
       <c r="K77" t="n">
-        <v>-131.48</v>
+        <v>-144.88</v>
       </c>
       <c r="L77" t="n">
-        <v>139.08</v>
+        <v>153.25</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>102.67</v>
+        <v>113.11</v>
       </c>
       <c r="K78" t="n">
-        <v>30.25</v>
+        <v>33.32</v>
       </c>
       <c r="L78" t="n">
-        <v>107.04</v>
+        <v>117.92</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>73.20999999999999</v>
+        <v>79.89</v>
       </c>
       <c r="K79" t="n">
-        <v>-20.72</v>
+        <v>-22.61</v>
       </c>
       <c r="L79" t="n">
-        <v>76.08</v>
+        <v>83.03</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-188.59</v>
+        <v>-211.34</v>
       </c>
       <c r="K80" t="n">
-        <v>-44.89</v>
+        <v>-50.31</v>
       </c>
       <c r="L80" t="n">
-        <v>193.86</v>
+        <v>217.25</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-201.11</v>
+        <v>-228.93</v>
       </c>
       <c r="K81" t="n">
-        <v>-74.91</v>
+        <v>-85.27</v>
       </c>
       <c r="L81" t="n">
-        <v>214.6</v>
+        <v>244.29</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-89.13</v>
+        <v>-102.47</v>
       </c>
       <c r="K82" t="n">
-        <v>215.73</v>
+        <v>248.03</v>
       </c>
       <c r="L82" t="n">
-        <v>233.42</v>
+        <v>268.37</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>209.24</v>
+        <v>247.34</v>
       </c>
       <c r="K83" t="n">
-        <v>-237.11</v>
+        <v>-280.3</v>
       </c>
       <c r="L83" t="n">
-        <v>316.23</v>
+        <v>373.83</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>-32.86</v>
+        <v>-38.1</v>
       </c>
       <c r="K84" t="n">
-        <v>-149.38</v>
+        <v>-173.23</v>
       </c>
       <c r="L84" t="n">
-        <v>152.95</v>
+        <v>177.37</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>155.49</v>
+        <v>178.99</v>
       </c>
       <c r="K85" t="n">
-        <v>-272.37</v>
+        <v>-313.54</v>
       </c>
       <c r="L85" t="n">
-        <v>313.62</v>
+        <v>361.04</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>214.34</v>
+        <v>252.08</v>
       </c>
       <c r="K86" t="n">
-        <v>94.88</v>
+        <v>111.59</v>
       </c>
       <c r="L86" t="n">
-        <v>234.4</v>
+        <v>275.67</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>481.23</v>
+        <v>574.49</v>
       </c>
       <c r="K87" t="n">
-        <v>-24.04</v>
+        <v>-28.7</v>
       </c>
       <c r="L87" t="n">
-        <v>481.83</v>
+        <v>575.2</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-30.22</v>
+        <v>-35.36</v>
       </c>
       <c r="K88" t="n">
-        <v>-158.78</v>
+        <v>-185.77</v>
       </c>
       <c r="L88" t="n">
-        <v>161.64</v>
+        <v>189.1</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-03.xlsx
+++ b/output/2025-10-03.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.88</v>
+        <v>3.51</v>
       </c>
       <c r="F14" t="n">
-        <v>7.84</v>
+        <v>6.75</v>
       </c>
       <c r="G14" t="n">
-        <v>112.7</v>
+        <v>119</v>
       </c>
       <c r="H14" t="n">
-        <v>88.3</v>
+        <v>89.8</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.99</v>
+        <v>33.67</v>
       </c>
       <c r="K14" t="n">
-        <v>107.66</v>
+        <v>23.87</v>
       </c>
       <c r="L14" t="n">
-        <v>107.67</v>
+        <v>41.27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:24:29</t>
+          <t>07:23:05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.03</v>
+        <v>2.6</v>
       </c>
       <c r="F15" t="n">
-        <v>7.67</v>
+        <v>7.66</v>
       </c>
       <c r="G15" t="n">
-        <v>113.8</v>
+        <v>112.9</v>
       </c>
       <c r="H15" t="n">
-        <v>78.59999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>6.3</v>
+        <v>-45.4</v>
       </c>
       <c r="K15" t="n">
-        <v>-199.42</v>
+        <v>-51.12</v>
       </c>
       <c r="L15" t="n">
-        <v>199.51</v>
+        <v>68.37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:26:17</t>
+          <t>07:24:02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.04</v>
+        <v>2.63</v>
       </c>
       <c r="F16" t="n">
-        <v>7.7</v>
+        <v>7.52</v>
       </c>
       <c r="G16" t="n">
-        <v>115.8</v>
+        <v>125.4</v>
       </c>
       <c r="H16" t="n">
-        <v>83.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>10.27</v>
+        <v>-9.07</v>
       </c>
       <c r="K16" t="n">
-        <v>107.17</v>
+        <v>55.19</v>
       </c>
       <c r="L16" t="n">
-        <v>107.66</v>
+        <v>55.93</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:30:26</t>
+          <t>07:27:20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.37</v>
+        <v>3.07</v>
       </c>
       <c r="F17" t="n">
-        <v>7.2</v>
+        <v>7.99</v>
       </c>
       <c r="G17" t="n">
-        <v>116.7</v>
+        <v>105.5</v>
       </c>
       <c r="H17" t="n">
-        <v>85.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>28.13</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-114.91</v>
+        <v>-19.4</v>
       </c>
       <c r="L17" t="n">
-        <v>118.31</v>
+        <v>21.19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:31:08</t>
+          <t>07:29:28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.94</v>
+        <v>2.26</v>
       </c>
       <c r="F18" t="n">
-        <v>8.41</v>
+        <v>7.73</v>
       </c>
       <c r="G18" t="n">
-        <v>123</v>
+        <v>107.4</v>
       </c>
       <c r="H18" t="n">
-        <v>89.2</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>7.58</v>
+        <v>-66.39</v>
       </c>
       <c r="K18" t="n">
-        <v>-195.77</v>
+        <v>-120.29</v>
       </c>
       <c r="L18" t="n">
-        <v>195.91</v>
+        <v>137.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:33:16</t>
+          <t>07:31:44</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.58</v>
+        <v>2.67</v>
       </c>
       <c r="F19" t="n">
-        <v>7.38</v>
+        <v>7.53</v>
       </c>
       <c r="G19" t="n">
-        <v>121.1</v>
+        <v>117.3</v>
       </c>
       <c r="H19" t="n">
-        <v>84.40000000000001</v>
+        <v>85</v>
       </c>
       <c r="I19" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-12.33</v>
+        <v>3.37</v>
       </c>
       <c r="K19" t="n">
-        <v>-89.22</v>
+        <v>-75.72</v>
       </c>
       <c r="L19" t="n">
-        <v>90.06999999999999</v>
+        <v>75.79000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:38:38</t>
+          <t>07:37:12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.53</v>
+        <v>2.37</v>
       </c>
       <c r="F20" t="n">
-        <v>7.62</v>
+        <v>7.44</v>
       </c>
       <c r="G20" t="n">
-        <v>109</v>
+        <v>113.1</v>
       </c>
       <c r="H20" t="n">
-        <v>92</v>
+        <v>81.8</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>4.86</v>
+        <v>-116.87</v>
       </c>
       <c r="K20" t="n">
-        <v>-221.56</v>
+        <v>-21.1</v>
       </c>
       <c r="L20" t="n">
-        <v>221.62</v>
+        <v>118.76</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:40:41</t>
+          <t>07:38:50</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="F21" t="n">
-        <v>7.21</v>
+        <v>7.61</v>
       </c>
       <c r="G21" t="n">
-        <v>113.5</v>
+        <v>106.9</v>
       </c>
       <c r="H21" t="n">
-        <v>81.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>122.96</v>
+        <v>105.19</v>
       </c>
       <c r="K21" t="n">
-        <v>-15.16</v>
+        <v>7.02</v>
       </c>
       <c r="L21" t="n">
-        <v>123.89</v>
+        <v>105.42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:42:14</t>
+          <t>07:40:02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="F22" t="n">
-        <v>7.07</v>
+        <v>7.57</v>
       </c>
       <c r="G22" t="n">
-        <v>121.2</v>
+        <v>116.9</v>
       </c>
       <c r="H22" t="n">
-        <v>86.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>180.29</v>
+        <v>-111.59</v>
       </c>
       <c r="K22" t="n">
-        <v>-3</v>
+        <v>-55.64</v>
       </c>
       <c r="L22" t="n">
-        <v>180.32</v>
+        <v>124.69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:48:32</t>
+          <t>07:45:27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="F23" t="n">
-        <v>7.59</v>
+        <v>7.73</v>
       </c>
       <c r="G23" t="n">
-        <v>115.2</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>86.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="I23" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>131.83</v>
+        <v>70.89</v>
       </c>
       <c r="K23" t="n">
-        <v>-191.97</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>232.88</v>
+        <v>112.11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:50:47</t>
+          <t>07:46:58</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="F24" t="n">
-        <v>7.19</v>
+        <v>7.8</v>
       </c>
       <c r="G24" t="n">
-        <v>96.59999999999999</v>
+        <v>115.3</v>
       </c>
       <c r="H24" t="n">
-        <v>80.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>210.34</v>
+        <v>119.15</v>
       </c>
       <c r="K24" t="n">
-        <v>9.199999999999999</v>
+        <v>-26.76</v>
       </c>
       <c r="L24" t="n">
-        <v>210.54</v>
+        <v>122.12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:52:00</t>
+          <t>07:48:27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="F25" t="n">
-        <v>7.93</v>
+        <v>7.95</v>
       </c>
       <c r="G25" t="n">
-        <v>117.3</v>
+        <v>111</v>
       </c>
       <c r="H25" t="n">
-        <v>88.09999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-99.53</v>
+        <v>6.28</v>
       </c>
       <c r="K25" t="n">
-        <v>-202.32</v>
+        <v>-162.72</v>
       </c>
       <c r="L25" t="n">
-        <v>225.47</v>
+        <v>162.84</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:55:52</t>
+          <t>07:53:51</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>7.37</v>
+        <v>7.95</v>
       </c>
       <c r="G26" t="n">
-        <v>133.3</v>
+        <v>98.5</v>
       </c>
       <c r="H26" t="n">
-        <v>86.7</v>
+        <v>90.5</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>171.09</v>
+        <v>-290.44</v>
       </c>
       <c r="K26" t="n">
-        <v>-328.29</v>
+        <v>-3.51</v>
       </c>
       <c r="L26" t="n">
-        <v>370.19</v>
+        <v>290.46</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:57:49</t>
+          <t>07:55:27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.65</v>
+        <v>2.96</v>
       </c>
       <c r="F27" t="n">
-        <v>7.96</v>
+        <v>7.45</v>
       </c>
       <c r="G27" t="n">
-        <v>128.8</v>
+        <v>110.6</v>
       </c>
       <c r="H27" t="n">
-        <v>87.8</v>
+        <v>88.7</v>
       </c>
       <c r="I27" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>260.04</v>
+        <v>-151.6</v>
       </c>
       <c r="K27" t="n">
-        <v>308.91</v>
+        <v>-164.03</v>
       </c>
       <c r="L27" t="n">
-        <v>403.79</v>
+        <v>223.36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08:00:26</t>
+          <t>07:57:35</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.64</v>
+        <v>2.89</v>
       </c>
       <c r="F28" t="n">
-        <v>7.21</v>
+        <v>7.77</v>
       </c>
       <c r="G28" t="n">
-        <v>103.8</v>
+        <v>125.7</v>
       </c>
       <c r="H28" t="n">
-        <v>84.09999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-148.42</v>
+        <v>75.94</v>
       </c>
       <c r="K28" t="n">
-        <v>214.37</v>
+        <v>71.06</v>
       </c>
       <c r="L28" t="n">
-        <v>260.73</v>
+        <v>104.01</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:13:35</t>
+          <t>08:07:44</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="F29" t="n">
-        <v>7.83</v>
+        <v>8.43</v>
       </c>
       <c r="G29" t="n">
-        <v>99.5</v>
+        <v>110.4</v>
       </c>
       <c r="H29" t="n">
-        <v>83</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>41.94</v>
+        <v>-23.39</v>
       </c>
       <c r="K29" t="n">
-        <v>55.4</v>
+        <v>-32.53</v>
       </c>
       <c r="L29" t="n">
-        <v>69.48999999999999</v>
+        <v>40.07</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:15:31</t>
+          <t>08:09:19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.63</v>
+        <v>2.3</v>
       </c>
       <c r="F30" t="n">
-        <v>8.119999999999999</v>
+        <v>7.37</v>
       </c>
       <c r="G30" t="n">
-        <v>119.9</v>
+        <v>111.3</v>
       </c>
       <c r="H30" t="n">
-        <v>86.90000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>39.15</v>
+        <v>32.25</v>
       </c>
       <c r="K30" t="n">
-        <v>65.15000000000001</v>
+        <v>-29.94</v>
       </c>
       <c r="L30" t="n">
-        <v>76.01000000000001</v>
+        <v>44.01</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:16:54</t>
+          <t>08:11:15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.76</v>
+        <v>3.18</v>
       </c>
       <c r="F31" t="n">
-        <v>6.93</v>
+        <v>7.78</v>
       </c>
       <c r="G31" t="n">
-        <v>123.1</v>
+        <v>119.2</v>
       </c>
       <c r="H31" t="n">
-        <v>87.90000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-3.65</v>
+        <v>35.87</v>
       </c>
       <c r="K31" t="n">
-        <v>86.92</v>
+        <v>44.88</v>
       </c>
       <c r="L31" t="n">
-        <v>86.98999999999999</v>
+        <v>57.46</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:21:49</t>
+          <t>08:15:14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="F32" t="n">
-        <v>7.25</v>
+        <v>7.71</v>
       </c>
       <c r="G32" t="n">
-        <v>130.1</v>
+        <v>110.2</v>
       </c>
       <c r="H32" t="n">
-        <v>90.09999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I32" t="n">
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>23.53</v>
+        <v>-52.37</v>
       </c>
       <c r="K32" t="n">
-        <v>-65.81</v>
+        <v>-54.86</v>
       </c>
       <c r="L32" t="n">
-        <v>69.89</v>
+        <v>75.84999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:23:27</t>
+          <t>08:17:18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="F33" t="n">
-        <v>7.85</v>
+        <v>7.4</v>
       </c>
       <c r="G33" t="n">
-        <v>125.8</v>
+        <v>117</v>
       </c>
       <c r="H33" t="n">
-        <v>80.40000000000001</v>
+        <v>94</v>
       </c>
       <c r="I33" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>76.55</v>
+        <v>-62.81</v>
       </c>
       <c r="K33" t="n">
-        <v>-70.42</v>
+        <v>-5.83</v>
       </c>
       <c r="L33" t="n">
-        <v>104.02</v>
+        <v>63.08</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:25:33</t>
+          <t>08:18:23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.45</v>
+        <v>3.46</v>
       </c>
       <c r="F34" t="n">
-        <v>7.6</v>
+        <v>7.44</v>
       </c>
       <c r="G34" t="n">
-        <v>113</v>
+        <v>113.5</v>
       </c>
       <c r="H34" t="n">
-        <v>85.7</v>
+        <v>87.7</v>
       </c>
       <c r="I34" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-30.3</v>
+        <v>-79.37</v>
       </c>
       <c r="K34" t="n">
-        <v>-90.76000000000001</v>
+        <v>-11.8</v>
       </c>
       <c r="L34" t="n">
-        <v>95.68000000000001</v>
+        <v>80.23999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:29:49</t>
+          <t>08:23:26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.91</v>
+        <v>2.55</v>
       </c>
       <c r="F35" t="n">
-        <v>7.53</v>
+        <v>7.8</v>
       </c>
       <c r="G35" t="n">
-        <v>116.6</v>
+        <v>100</v>
       </c>
       <c r="H35" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>131.44</v>
+        <v>143.29</v>
       </c>
       <c r="K35" t="n">
-        <v>133.68</v>
+        <v>86.44</v>
       </c>
       <c r="L35" t="n">
-        <v>187.47</v>
+        <v>167.34</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:31:01</t>
+          <t>08:25:03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="F36" t="n">
         <v>7.74</v>
       </c>
       <c r="G36" t="n">
-        <v>109.7</v>
+        <v>117.2</v>
       </c>
       <c r="H36" t="n">
         <v>85.5</v>
       </c>
       <c r="I36" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>191.21</v>
+        <v>-90.56999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-151.42</v>
+        <v>132.2</v>
       </c>
       <c r="L36" t="n">
-        <v>243.91</v>
+        <v>160.25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:33:18</t>
+          <t>08:25:55</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.02</v>
+        <v>2.89</v>
       </c>
       <c r="F37" t="n">
-        <v>7.13</v>
+        <v>7.62</v>
       </c>
       <c r="G37" t="n">
-        <v>116.9</v>
+        <v>123.1</v>
       </c>
       <c r="H37" t="n">
-        <v>87.7</v>
+        <v>92</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-237.59</v>
+        <v>59.08</v>
       </c>
       <c r="K37" t="n">
-        <v>10.04</v>
+        <v>10.17</v>
       </c>
       <c r="L37" t="n">
-        <v>237.8</v>
+        <v>59.95</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:38:32</t>
+          <t>08:30:13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.8</v>
+        <v>3.53</v>
       </c>
       <c r="F38" t="n">
-        <v>6.64</v>
+        <v>7.9</v>
       </c>
       <c r="G38" t="n">
-        <v>114.8</v>
+        <v>114.6</v>
       </c>
       <c r="H38" t="n">
-        <v>88.8</v>
+        <v>81.8</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>-60.47</v>
+        <v>152.96</v>
       </c>
       <c r="K38" t="n">
-        <v>249.29</v>
+        <v>145.8</v>
       </c>
       <c r="L38" t="n">
-        <v>256.52</v>
+        <v>211.31</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:40:27</t>
+          <t>08:32:03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="F39" t="n">
-        <v>7.34</v>
+        <v>8.02</v>
       </c>
       <c r="G39" t="n">
-        <v>111.4</v>
+        <v>125.4</v>
       </c>
       <c r="H39" t="n">
-        <v>85.40000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-175.04</v>
+        <v>-27.21</v>
       </c>
       <c r="K39" t="n">
-        <v>-38.34</v>
+        <v>-88.56999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>179.19</v>
+        <v>92.66</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:41:59</t>
+          <t>08:33:13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.68</v>
+        <v>2.87</v>
       </c>
       <c r="F40" t="n">
-        <v>7.5</v>
+        <v>7.38</v>
       </c>
       <c r="G40" t="n">
-        <v>111.1</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>87.2</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>74.45</v>
+        <v>220.69</v>
       </c>
       <c r="K40" t="n">
-        <v>-236.9</v>
+        <v>-0</v>
       </c>
       <c r="L40" t="n">
-        <v>248.33</v>
+        <v>220.69</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:45:31</t>
+          <t>08:37:28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.17</v>
+        <v>2.94</v>
       </c>
       <c r="F41" t="n">
-        <v>7.18</v>
+        <v>7.3</v>
       </c>
       <c r="G41" t="n">
-        <v>117.9</v>
+        <v>131.1</v>
       </c>
       <c r="H41" t="n">
-        <v>88.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-571.21</v>
+        <v>11.46</v>
       </c>
       <c r="K41" t="n">
-        <v>246.18</v>
+        <v>-143.88</v>
       </c>
       <c r="L41" t="n">
-        <v>622</v>
+        <v>144.34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:47:15</t>
+          <t>08:39:24</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.92</v>
+        <v>3.18</v>
       </c>
       <c r="F42" t="n">
-        <v>7.45</v>
+        <v>7.43</v>
       </c>
       <c r="G42" t="n">
-        <v>111.4</v>
+        <v>114.6</v>
       </c>
       <c r="H42" t="n">
-        <v>92.3</v>
+        <v>85.8</v>
       </c>
       <c r="I42" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-326.65</v>
+        <v>-113.39</v>
       </c>
       <c r="K42" t="n">
-        <v>-125.5</v>
+        <v>-328.45</v>
       </c>
       <c r="L42" t="n">
-        <v>349.93</v>
+        <v>347.47</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:49:09</t>
+          <t>08:42:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.86</v>
+        <v>2.49</v>
       </c>
       <c r="F43" t="n">
-        <v>7.53</v>
+        <v>7.32</v>
       </c>
       <c r="G43" t="n">
-        <v>120.2</v>
+        <v>110.7</v>
       </c>
       <c r="H43" t="n">
-        <v>89.5</v>
+        <v>86</v>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-47.05</v>
+        <v>162.29</v>
       </c>
       <c r="K43" t="n">
-        <v>-472.35</v>
+        <v>28.79</v>
       </c>
       <c r="L43" t="n">
-        <v>474.69</v>
+        <v>164.82</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:58:30</t>
+          <t>08:53:42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.75</v>
+        <v>3.36</v>
       </c>
       <c r="F44" t="n">
-        <v>8.050000000000001</v>
+        <v>7.65</v>
       </c>
       <c r="G44" t="n">
-        <v>107.9</v>
+        <v>106.4</v>
       </c>
       <c r="H44" t="n">
-        <v>91.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>-73.81</v>
+        <v>-30.32</v>
       </c>
       <c r="K44" t="n">
-        <v>-18.54</v>
+        <v>-43.29</v>
       </c>
       <c r="L44" t="n">
-        <v>76.09999999999999</v>
+        <v>52.85</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:59:51</t>
+          <t>08:55:49</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="F45" t="n">
-        <v>7.65</v>
+        <v>7.16</v>
       </c>
       <c r="G45" t="n">
-        <v>103.2</v>
+        <v>114.4</v>
       </c>
       <c r="H45" t="n">
-        <v>89.59999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-48.07</v>
+        <v>27.2</v>
       </c>
       <c r="K45" t="n">
-        <v>-67.73</v>
+        <v>-12.59</v>
       </c>
       <c r="L45" t="n">
-        <v>83.06</v>
+        <v>29.97</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09:00:40</t>
+          <t>08:56:39</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="F46" t="n">
-        <v>8.07</v>
+        <v>7.35</v>
       </c>
       <c r="G46" t="n">
-        <v>112.4</v>
+        <v>111.2</v>
       </c>
       <c r="H46" t="n">
-        <v>92.5</v>
+        <v>91.8</v>
       </c>
       <c r="I46" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.73</v>
+        <v>-43.63</v>
       </c>
       <c r="K46" t="n">
-        <v>-99.56</v>
+        <v>-48.67</v>
       </c>
       <c r="L46" t="n">
-        <v>100.37</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:05:46</t>
+          <t>09:00:55</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.57</v>
+        <v>2.85</v>
       </c>
       <c r="F47" t="n">
-        <v>7.55</v>
+        <v>7.85</v>
       </c>
       <c r="G47" t="n">
-        <v>120</v>
+        <v>98.7</v>
       </c>
       <c r="H47" t="n">
-        <v>88.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>-55.7</v>
+        <v>-57.94</v>
       </c>
       <c r="K47" t="n">
-        <v>139.17</v>
+        <v>29.05</v>
       </c>
       <c r="L47" t="n">
-        <v>149.9</v>
+        <v>64.81</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:06:35</t>
+          <t>09:02:34</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.18</v>
+        <v>2.96</v>
       </c>
       <c r="F48" t="n">
-        <v>7.93</v>
+        <v>7.27</v>
       </c>
       <c r="G48" t="n">
-        <v>109.5</v>
+        <v>112.4</v>
       </c>
       <c r="H48" t="n">
-        <v>93.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>129</v>
+        <v>52.22</v>
       </c>
       <c r="K48" t="n">
-        <v>98.20999999999999</v>
+        <v>-78.02</v>
       </c>
       <c r="L48" t="n">
-        <v>162.13</v>
+        <v>93.88</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:08:08</t>
+          <t>09:04:02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.51</v>
+        <v>3.01</v>
       </c>
       <c r="F49" t="n">
-        <v>7.96</v>
+        <v>7.86</v>
       </c>
       <c r="G49" t="n">
-        <v>109.5</v>
+        <v>111.8</v>
       </c>
       <c r="H49" t="n">
-        <v>85.09999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-110.77</v>
+        <v>-5.48</v>
       </c>
       <c r="K49" t="n">
-        <v>-72.48</v>
+        <v>-95.15000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>132.38</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:12:04</t>
+          <t>09:10:02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>7.83</v>
+        <v>7.73</v>
       </c>
       <c r="G50" t="n">
-        <v>118.9</v>
+        <v>98.8</v>
       </c>
       <c r="H50" t="n">
-        <v>91.3</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>148.48</v>
+        <v>80.8</v>
       </c>
       <c r="K50" t="n">
-        <v>168.02</v>
+        <v>-48.88</v>
       </c>
       <c r="L50" t="n">
-        <v>224.23</v>
+        <v>94.43000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:14:30</t>
+          <t>09:11:33</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.66</v>
+        <v>3.25</v>
       </c>
       <c r="F51" t="n">
-        <v>8.06</v>
+        <v>8.69</v>
       </c>
       <c r="G51" t="n">
-        <v>117.3</v>
+        <v>110.9</v>
       </c>
       <c r="H51" t="n">
-        <v>84.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J51" t="n">
-        <v>259.68</v>
+        <v>-22.91</v>
       </c>
       <c r="K51" t="n">
-        <v>-90.8</v>
+        <v>-90.17</v>
       </c>
       <c r="L51" t="n">
-        <v>275.09</v>
+        <v>93.03</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:16:07</t>
+          <t>09:12:51</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="F52" t="n">
-        <v>7.14</v>
+        <v>8.06</v>
       </c>
       <c r="G52" t="n">
-        <v>118.5</v>
+        <v>127.4</v>
       </c>
       <c r="H52" t="n">
-        <v>84.40000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>112.89</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>-16.84</v>
+        <v>-44.34</v>
       </c>
       <c r="L52" t="n">
-        <v>114.14</v>
+        <v>86.23999999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:20:02</t>
+          <t>09:17:44</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.13</v>
+        <v>2.76</v>
       </c>
       <c r="F53" t="n">
-        <v>6.89</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>112.5</v>
+        <v>107.8</v>
       </c>
       <c r="H53" t="n">
-        <v>85.7</v>
+        <v>90.3</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-210.65</v>
+        <v>-48.15</v>
       </c>
       <c r="K53" t="n">
-        <v>313.35</v>
+        <v>-83.76000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>377.57</v>
+        <v>96.61</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:21:21</t>
+          <t>09:18:36</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.01</v>
+        <v>3.49</v>
       </c>
       <c r="F54" t="n">
-        <v>7.62</v>
+        <v>7.83</v>
       </c>
       <c r="G54" t="n">
-        <v>122.5</v>
+        <v>121.6</v>
       </c>
       <c r="H54" t="n">
-        <v>90.7</v>
+        <v>84.5</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-38.08</v>
+        <v>11.91</v>
       </c>
       <c r="K54" t="n">
-        <v>-161.41</v>
+        <v>-194.26</v>
       </c>
       <c r="L54" t="n">
-        <v>165.84</v>
+        <v>194.63</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:23:23</t>
+          <t>09:19:37</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2350,31 +2350,31 @@
         <v>3.05</v>
       </c>
       <c r="F55" t="n">
-        <v>7.65</v>
+        <v>7.7</v>
       </c>
       <c r="G55" t="n">
-        <v>112.4</v>
+        <v>108.9</v>
       </c>
       <c r="H55" t="n">
-        <v>74.8</v>
+        <v>82.5</v>
       </c>
       <c r="I55" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-111.18</v>
+        <v>31.34</v>
       </c>
       <c r="K55" t="n">
-        <v>80.13</v>
+        <v>-93.81999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>137.05</v>
+        <v>98.91</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:27:20</t>
+          <t>09:23:22</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.33</v>
+        <v>4.18</v>
       </c>
       <c r="F56" t="n">
-        <v>7.74</v>
+        <v>7.23</v>
       </c>
       <c r="G56" t="n">
-        <v>114.6</v>
+        <v>114</v>
       </c>
       <c r="H56" t="n">
-        <v>87.7</v>
+        <v>89.7</v>
       </c>
       <c r="I56" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>289.64</v>
+        <v>186.08</v>
       </c>
       <c r="K56" t="n">
-        <v>85.65000000000001</v>
+        <v>258.91</v>
       </c>
       <c r="L56" t="n">
-        <v>302.04</v>
+        <v>318.84</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:28:57</t>
+          <t>09:24:55</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.35</v>
+        <v>2.78</v>
       </c>
       <c r="F57" t="n">
-        <v>7.51</v>
+        <v>7.44</v>
       </c>
       <c r="G57" t="n">
-        <v>116.2</v>
+        <v>128.4</v>
       </c>
       <c r="H57" t="n">
-        <v>88.3</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-452.06</v>
+        <v>-118.06</v>
       </c>
       <c r="K57" t="n">
-        <v>-166.6</v>
+        <v>-10.39</v>
       </c>
       <c r="L57" t="n">
-        <v>481.78</v>
+        <v>118.52</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:30:51</t>
+          <t>09:27:07</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.88</v>
+        <v>3.16</v>
       </c>
       <c r="F58" t="n">
-        <v>8.27</v>
+        <v>7.8</v>
       </c>
       <c r="G58" t="n">
-        <v>107.5</v>
+        <v>108.8</v>
       </c>
       <c r="H58" t="n">
-        <v>85.90000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="I58" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-161.65</v>
+        <v>200.86</v>
       </c>
       <c r="K58" t="n">
-        <v>-437.29</v>
+        <v>-123.33</v>
       </c>
       <c r="L58" t="n">
-        <v>466.21</v>
+        <v>235.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:42:23</t>
+          <t>09:35:01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="F59" t="n">
-        <v>7.62</v>
+        <v>7.55</v>
       </c>
       <c r="G59" t="n">
-        <v>101.6</v>
+        <v>131.5</v>
       </c>
       <c r="H59" t="n">
-        <v>96.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>-19.73</v>
+        <v>-18.46</v>
       </c>
       <c r="K59" t="n">
-        <v>-168.58</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>169.73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:43:35</t>
+          <t>09:36:14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="F60" t="n">
-        <v>8.09</v>
+        <v>7.17</v>
       </c>
       <c r="G60" t="n">
-        <v>118.7</v>
+        <v>102.3</v>
       </c>
       <c r="H60" t="n">
-        <v>89.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-16.43</v>
+        <v>-32.81</v>
       </c>
       <c r="K60" t="n">
-        <v>190.78</v>
+        <v>-36.74</v>
       </c>
       <c r="L60" t="n">
-        <v>191.48</v>
+        <v>49.26</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:44:29</t>
+          <t>09:37:55</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.39</v>
+        <v>2.89</v>
       </c>
       <c r="F61" t="n">
-        <v>8.4</v>
+        <v>6.53</v>
       </c>
       <c r="G61" t="n">
-        <v>111.3</v>
+        <v>109.7</v>
       </c>
       <c r="H61" t="n">
-        <v>82.3</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>-152.56</v>
+        <v>45.05</v>
       </c>
       <c r="K61" t="n">
-        <v>-78.93000000000001</v>
+        <v>-16.74</v>
       </c>
       <c r="L61" t="n">
-        <v>171.77</v>
+        <v>48.06</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:48:21</t>
+          <t>09:43:42</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.14</v>
+        <v>2.83</v>
       </c>
       <c r="F62" t="n">
-        <v>7.45</v>
+        <v>7.59</v>
       </c>
       <c r="G62" t="n">
-        <v>108.6</v>
+        <v>112.2</v>
       </c>
       <c r="H62" t="n">
-        <v>87.8</v>
+        <v>81</v>
       </c>
       <c r="I62" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-53.6</v>
+        <v>48.53</v>
       </c>
       <c r="K62" t="n">
-        <v>111.98</v>
+        <v>17.92</v>
       </c>
       <c r="L62" t="n">
-        <v>124.15</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:49:37</t>
+          <t>09:44:44</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.22</v>
+        <v>3.36</v>
       </c>
       <c r="F63" t="n">
-        <v>7.5</v>
+        <v>7.26</v>
       </c>
       <c r="G63" t="n">
-        <v>114.8</v>
+        <v>126.2</v>
       </c>
       <c r="H63" t="n">
-        <v>90.8</v>
+        <v>74.2</v>
       </c>
       <c r="I63" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>161.74</v>
+        <v>87.91</v>
       </c>
       <c r="K63" t="n">
-        <v>-150.79</v>
+        <v>31.83</v>
       </c>
       <c r="L63" t="n">
-        <v>221.13</v>
+        <v>93.48999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:51:38</t>
+          <t>09:46:51</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.44</v>
+        <v>3.23</v>
       </c>
       <c r="F64" t="n">
-        <v>7.46</v>
+        <v>7.71</v>
       </c>
       <c r="G64" t="n">
-        <v>111.1</v>
+        <v>104.2</v>
       </c>
       <c r="H64" t="n">
-        <v>89.09999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>132.14</v>
+        <v>-15.66</v>
       </c>
       <c r="K64" t="n">
-        <v>80.34999999999999</v>
+        <v>70.14</v>
       </c>
       <c r="L64" t="n">
-        <v>154.66</v>
+        <v>71.87</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:56:25</t>
+          <t>09:51:21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.73</v>
+        <v>3.43</v>
       </c>
       <c r="F65" t="n">
-        <v>6.86</v>
+        <v>7.24</v>
       </c>
       <c r="G65" t="n">
-        <v>113.1</v>
+        <v>102.1</v>
       </c>
       <c r="H65" t="n">
-        <v>87.3</v>
+        <v>80.2</v>
       </c>
       <c r="I65" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-151.84</v>
+        <v>-65.95999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>-183.36</v>
+        <v>50.12</v>
       </c>
       <c r="L65" t="n">
-        <v>238.07</v>
+        <v>82.84999999999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:57:49</t>
+          <t>09:53:02</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="F66" t="n">
-        <v>8.07</v>
+        <v>7.96</v>
       </c>
       <c r="G66" t="n">
-        <v>122.5</v>
+        <v>106.5</v>
       </c>
       <c r="H66" t="n">
-        <v>86</v>
+        <v>88.7</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>-150.66</v>
+        <v>54.87</v>
       </c>
       <c r="K66" t="n">
-        <v>-47.7</v>
+        <v>-58.09</v>
       </c>
       <c r="L66" t="n">
-        <v>158.03</v>
+        <v>79.91</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:00:03</t>
+          <t>09:55:33</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.96</v>
+        <v>3.48</v>
       </c>
       <c r="F67" t="n">
-        <v>7.38</v>
+        <v>7.1</v>
       </c>
       <c r="G67" t="n">
-        <v>115.8</v>
+        <v>141</v>
       </c>
       <c r="H67" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-200.92</v>
+        <v>-52.75</v>
       </c>
       <c r="K67" t="n">
-        <v>-128.03</v>
+        <v>-104.76</v>
       </c>
       <c r="L67" t="n">
-        <v>238.24</v>
+        <v>117.29</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:06:10</t>
+          <t>10:00:34</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.29</v>
+        <v>2.92</v>
       </c>
       <c r="F68" t="n">
-        <v>7.93</v>
+        <v>7.4</v>
       </c>
       <c r="G68" t="n">
-        <v>93</v>
+        <v>102.1</v>
       </c>
       <c r="H68" t="n">
-        <v>90.7</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>-195.21</v>
+        <v>-120.01</v>
       </c>
       <c r="K68" t="n">
-        <v>-321.86</v>
+        <v>109.65</v>
       </c>
       <c r="L68" t="n">
-        <v>376.43</v>
+        <v>162.56</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:07:11</t>
+          <t>10:01:42</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.06</v>
+        <v>2.99</v>
       </c>
       <c r="F69" t="n">
-        <v>7.64</v>
+        <v>7.22</v>
       </c>
       <c r="G69" t="n">
-        <v>113.9</v>
+        <v>116.7</v>
       </c>
       <c r="H69" t="n">
-        <v>93</v>
+        <v>91.5</v>
       </c>
       <c r="I69" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-303.38</v>
+        <v>134.18</v>
       </c>
       <c r="K69" t="n">
-        <v>-39.53</v>
+        <v>-36.76</v>
       </c>
       <c r="L69" t="n">
-        <v>305.94</v>
+        <v>139.12</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:08:24</t>
+          <t>10:03:38</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.86</v>
+        <v>3.02</v>
       </c>
       <c r="F70" t="n">
         <v>7.6</v>
       </c>
       <c r="G70" t="n">
-        <v>125</v>
+        <v>114.6</v>
       </c>
       <c r="H70" t="n">
-        <v>86.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-308.32</v>
+        <v>113.43</v>
       </c>
       <c r="K70" t="n">
-        <v>10.54</v>
+        <v>47.65</v>
       </c>
       <c r="L70" t="n">
-        <v>308.5</v>
+        <v>123.03</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:13:16</t>
+          <t>10:08:54</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="F71" t="n">
-        <v>8.02</v>
+        <v>7.91</v>
       </c>
       <c r="G71" t="n">
-        <v>124.4</v>
+        <v>124.1</v>
       </c>
       <c r="H71" t="n">
-        <v>86.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-267.53</v>
+        <v>212.99</v>
       </c>
       <c r="K71" t="n">
-        <v>-220.63</v>
+        <v>-107.83</v>
       </c>
       <c r="L71" t="n">
-        <v>346.78</v>
+        <v>238.73</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:14:42</t>
+          <t>10:10:36</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.39</v>
+        <v>3.12</v>
       </c>
       <c r="F72" t="n">
-        <v>7.29</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G72" t="n">
-        <v>127</v>
+        <v>107.9</v>
       </c>
       <c r="H72" t="n">
-        <v>81.40000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>707.34</v>
+        <v>58.92</v>
       </c>
       <c r="K72" t="n">
-        <v>-407.42</v>
+        <v>118.07</v>
       </c>
       <c r="L72" t="n">
-        <v>816.28</v>
+        <v>131.95</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:15:41</t>
+          <t>10:11:58</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.33</v>
+        <v>3.06</v>
       </c>
       <c r="F73" t="n">
-        <v>7.3</v>
+        <v>7.44</v>
       </c>
       <c r="G73" t="n">
-        <v>95</v>
+        <v>118.3</v>
       </c>
       <c r="H73" t="n">
-        <v>84</v>
+        <v>89.5</v>
       </c>
       <c r="I73" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>444.91</v>
+        <v>-55.33</v>
       </c>
       <c r="K73" t="n">
-        <v>115.09</v>
+        <v>-198.45</v>
       </c>
       <c r="L73" t="n">
-        <v>459.56</v>
+        <v>206.02</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:28:50</t>
+          <t>10:19:37</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="F74" t="n">
-        <v>7.45</v>
+        <v>7.37</v>
       </c>
       <c r="G74" t="n">
-        <v>117.5</v>
+        <v>98.8</v>
       </c>
       <c r="H74" t="n">
-        <v>84.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>-148.22</v>
+        <v>39.03</v>
       </c>
       <c r="K74" t="n">
-        <v>91.20999999999999</v>
+        <v>-16.93</v>
       </c>
       <c r="L74" t="n">
-        <v>174.03</v>
+        <v>42.54</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:30:28</t>
+          <t>10:21:28</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.54</v>
+        <v>3.29</v>
       </c>
       <c r="F75" t="n">
-        <v>7.74</v>
+        <v>7.8</v>
       </c>
       <c r="G75" t="n">
-        <v>108.1</v>
+        <v>116.6</v>
       </c>
       <c r="H75" t="n">
-        <v>83.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="I75" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>72.04000000000001</v>
+        <v>-29.14</v>
       </c>
       <c r="K75" t="n">
-        <v>64.98</v>
+        <v>-73.94</v>
       </c>
       <c r="L75" t="n">
-        <v>97.02</v>
+        <v>79.48</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:31:40</t>
+          <t>10:22:59</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.58</v>
+        <v>3.41</v>
       </c>
       <c r="F76" t="n">
-        <v>7.93</v>
+        <v>7.65</v>
       </c>
       <c r="G76" t="n">
-        <v>111</v>
+        <v>106.2</v>
       </c>
       <c r="H76" t="n">
-        <v>86.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>70.18000000000001</v>
+        <v>2.75</v>
       </c>
       <c r="K76" t="n">
-        <v>84.53</v>
+        <v>112.92</v>
       </c>
       <c r="L76" t="n">
-        <v>109.87</v>
+        <v>112.96</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:37:44</t>
+          <t>10:27:27</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.29</v>
+        <v>3.46</v>
       </c>
       <c r="F77" t="n">
-        <v>7.81</v>
+        <v>6.99</v>
       </c>
       <c r="G77" t="n">
-        <v>118.7</v>
+        <v>115.8</v>
       </c>
       <c r="H77" t="n">
-        <v>86.09999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>49.97</v>
+        <v>-98.34</v>
       </c>
       <c r="K77" t="n">
-        <v>-144.88</v>
+        <v>-79.98999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>153.25</v>
+        <v>126.76</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:39:33</t>
+          <t>10:28:41</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.15</v>
+        <v>3.73</v>
       </c>
       <c r="F78" t="n">
-        <v>7.62</v>
+        <v>6.76</v>
       </c>
       <c r="G78" t="n">
-        <v>115.9</v>
+        <v>108.3</v>
       </c>
       <c r="H78" t="n">
-        <v>83.2</v>
+        <v>92.2</v>
       </c>
       <c r="I78" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>113.11</v>
+        <v>132.27</v>
       </c>
       <c r="K78" t="n">
-        <v>33.32</v>
+        <v>-69.01000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>117.92</v>
+        <v>149.19</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:41:31</t>
+          <t>10:30:43</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.97</v>
+        <v>3.67</v>
       </c>
       <c r="F79" t="n">
-        <v>7.13</v>
+        <v>7.83</v>
       </c>
       <c r="G79" t="n">
-        <v>120.7</v>
+        <v>107.6</v>
       </c>
       <c r="H79" t="n">
-        <v>81</v>
+        <v>83.5</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>79.89</v>
+        <v>19.87</v>
       </c>
       <c r="K79" t="n">
-        <v>-22.61</v>
+        <v>60.26</v>
       </c>
       <c r="L79" t="n">
-        <v>83.03</v>
+        <v>63.45</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:46:06</t>
+          <t>10:35:13</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="F80" t="n">
-        <v>7.55</v>
+        <v>7.21</v>
       </c>
       <c r="G80" t="n">
-        <v>106.2</v>
+        <v>131.1</v>
       </c>
       <c r="H80" t="n">
-        <v>83.5</v>
+        <v>87.5</v>
       </c>
       <c r="I80" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-211.34</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>-50.31</v>
+        <v>8.02</v>
       </c>
       <c r="L80" t="n">
-        <v>217.25</v>
+        <v>99.83</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:46:53</t>
+          <t>10:37:32</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.12</v>
+        <v>3.38</v>
       </c>
       <c r="F81" t="n">
-        <v>7.16</v>
+        <v>7.52</v>
       </c>
       <c r="G81" t="n">
-        <v>120</v>
+        <v>114.1</v>
       </c>
       <c r="H81" t="n">
-        <v>91.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="I81" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J81" t="n">
-        <v>-228.93</v>
+        <v>56.68</v>
       </c>
       <c r="K81" t="n">
-        <v>-85.27</v>
+        <v>-87.95</v>
       </c>
       <c r="L81" t="n">
-        <v>244.29</v>
+        <v>104.63</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:48:33</t>
+          <t>10:38:39</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="F82" t="n">
-        <v>7.71</v>
+        <v>7.26</v>
       </c>
       <c r="G82" t="n">
-        <v>110.3</v>
+        <v>118.9</v>
       </c>
       <c r="H82" t="n">
-        <v>86.59999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-102.47</v>
+        <v>-11.37</v>
       </c>
       <c r="K82" t="n">
-        <v>248.03</v>
+        <v>53.74</v>
       </c>
       <c r="L82" t="n">
-        <v>268.37</v>
+        <v>54.93</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:53:53</t>
+          <t>10:42:35</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="F83" t="n">
-        <v>8.02</v>
+        <v>7.68</v>
       </c>
       <c r="G83" t="n">
-        <v>111.9</v>
+        <v>119.1</v>
       </c>
       <c r="H83" t="n">
-        <v>90</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J83" t="n">
-        <v>247.34</v>
+        <v>-48.21</v>
       </c>
       <c r="K83" t="n">
-        <v>-280.3</v>
+        <v>-139.03</v>
       </c>
       <c r="L83" t="n">
-        <v>373.83</v>
+        <v>147.15</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:56:13</t>
+          <t>10:44:51</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.21</v>
+        <v>3.43</v>
       </c>
       <c r="F84" t="n">
-        <v>6.94</v>
+        <v>7.25</v>
       </c>
       <c r="G84" t="n">
-        <v>108.1</v>
+        <v>119.3</v>
       </c>
       <c r="H84" t="n">
-        <v>87.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="I84" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-38.1</v>
+        <v>-144.68</v>
       </c>
       <c r="K84" t="n">
-        <v>-173.23</v>
+        <v>-38.47</v>
       </c>
       <c r="L84" t="n">
-        <v>177.37</v>
+        <v>149.71</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:57:55</t>
+          <t>10:46:37</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.69</v>
+        <v>3.51</v>
       </c>
       <c r="F85" t="n">
-        <v>7.95</v>
+        <v>6.94</v>
       </c>
       <c r="G85" t="n">
-        <v>106.1</v>
+        <v>124.5</v>
       </c>
       <c r="H85" t="n">
-        <v>79.3</v>
+        <v>89.3</v>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>178.99</v>
+        <v>-79.12</v>
       </c>
       <c r="K85" t="n">
-        <v>-313.54</v>
+        <v>-119.04</v>
       </c>
       <c r="L85" t="n">
-        <v>361.04</v>
+        <v>142.94</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11:02:44</t>
+          <t>10:51:39</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.09</v>
+        <v>3.19</v>
       </c>
       <c r="F86" t="n">
-        <v>7.16</v>
+        <v>7.18</v>
       </c>
       <c r="G86" t="n">
-        <v>113.1</v>
+        <v>115.1</v>
       </c>
       <c r="H86" t="n">
-        <v>88.40000000000001</v>
+        <v>85</v>
       </c>
       <c r="I86" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>252.08</v>
+        <v>54.13</v>
       </c>
       <c r="K86" t="n">
-        <v>111.59</v>
+        <v>17.8</v>
       </c>
       <c r="L86" t="n">
-        <v>275.67</v>
+        <v>56.98</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11:05:09</t>
+          <t>10:52:56</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.37</v>
+        <v>2.89</v>
       </c>
       <c r="F87" t="n">
-        <v>7.75</v>
+        <v>7.78</v>
       </c>
       <c r="G87" t="n">
-        <v>116.9</v>
+        <v>128.2</v>
       </c>
       <c r="H87" t="n">
-        <v>86.09999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>574.49</v>
+        <v>117.52</v>
       </c>
       <c r="K87" t="n">
-        <v>-28.7</v>
+        <v>-165.74</v>
       </c>
       <c r="L87" t="n">
-        <v>575.2</v>
+        <v>203.18</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:06:46</t>
+          <t>10:53:47</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="F88" t="n">
-        <v>7.66</v>
+        <v>7.84</v>
       </c>
       <c r="G88" t="n">
-        <v>124.3</v>
+        <v>112</v>
       </c>
       <c r="H88" t="n">
-        <v>91.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>-35.36</v>
+        <v>52.98</v>
       </c>
       <c r="K88" t="n">
-        <v>-185.77</v>
+        <v>1.13</v>
       </c>
       <c r="L88" t="n">
-        <v>189.1</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-03.xlsx
+++ b/output/2025-10-03.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>33.67</v>
+        <v>36.01</v>
       </c>
       <c r="K14" t="n">
-        <v>23.87</v>
+        <v>25.53</v>
       </c>
       <c r="L14" t="n">
-        <v>41.27</v>
+        <v>44.14</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-45.4</v>
+        <v>-44.81</v>
       </c>
       <c r="K15" t="n">
-        <v>-51.12</v>
+        <v>-50.45</v>
       </c>
       <c r="L15" t="n">
-        <v>68.37</v>
+        <v>67.48</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.07</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>55.19</v>
+        <v>55.01</v>
       </c>
       <c r="L16" t="n">
-        <v>55.93</v>
+        <v>55.75</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>8.529999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="K17" t="n">
-        <v>-19.4</v>
+        <v>-18.98</v>
       </c>
       <c r="L17" t="n">
-        <v>21.19</v>
+        <v>20.73</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-66.39</v>
+        <v>-62.18</v>
       </c>
       <c r="K18" t="n">
-        <v>-120.29</v>
+        <v>-112.66</v>
       </c>
       <c r="L18" t="n">
-        <v>137.4</v>
+        <v>128.68</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="K19" t="n">
-        <v>-75.72</v>
+        <v>-75.34999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>75.79000000000001</v>
+        <v>75.43000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-116.87</v>
+        <v>-115.19</v>
       </c>
       <c r="K20" t="n">
-        <v>-21.1</v>
+        <v>-20.8</v>
       </c>
       <c r="L20" t="n">
-        <v>118.76</v>
+        <v>117.05</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>105.19</v>
+        <v>104.49</v>
       </c>
       <c r="K21" t="n">
-        <v>7.02</v>
+        <v>6.97</v>
       </c>
       <c r="L21" t="n">
-        <v>105.42</v>
+        <v>104.72</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-111.59</v>
+        <v>-108.5</v>
       </c>
       <c r="K22" t="n">
-        <v>-55.64</v>
+        <v>-54.1</v>
       </c>
       <c r="L22" t="n">
-        <v>124.69</v>
+        <v>121.24</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>70.89</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>86.84999999999999</v>
+        <v>90.23</v>
       </c>
       <c r="L23" t="n">
-        <v>112.11</v>
+        <v>116.47</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>119.15</v>
+        <v>121.71</v>
       </c>
       <c r="K24" t="n">
-        <v>-26.76</v>
+        <v>-27.34</v>
       </c>
       <c r="L24" t="n">
-        <v>122.12</v>
+        <v>124.75</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>6.28</v>
+        <v>6.19</v>
       </c>
       <c r="K25" t="n">
-        <v>-162.72</v>
+        <v>-160.24</v>
       </c>
       <c r="L25" t="n">
-        <v>162.84</v>
+        <v>160.36</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-290.44</v>
+        <v>-279.33</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.51</v>
+        <v>-3.37</v>
       </c>
       <c r="L26" t="n">
-        <v>290.46</v>
+        <v>279.35</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-151.6</v>
+        <v>-149.57</v>
       </c>
       <c r="K27" t="n">
-        <v>-164.03</v>
+        <v>-161.84</v>
       </c>
       <c r="L27" t="n">
-        <v>223.36</v>
+        <v>220.37</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>75.94</v>
+        <v>74.08</v>
       </c>
       <c r="K28" t="n">
-        <v>71.06</v>
+        <v>69.31</v>
       </c>
       <c r="L28" t="n">
-        <v>104.01</v>
+        <v>101.45</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>-23.39</v>
+        <v>-24.81</v>
       </c>
       <c r="K29" t="n">
-        <v>-32.53</v>
+        <v>-34.5</v>
       </c>
       <c r="L29" t="n">
-        <v>40.07</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>32.25</v>
+        <v>32.6</v>
       </c>
       <c r="K30" t="n">
-        <v>-29.94</v>
+        <v>-30.25</v>
       </c>
       <c r="L30" t="n">
-        <v>44.01</v>
+        <v>44.47</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>35.87</v>
+        <v>36.25</v>
       </c>
       <c r="K31" t="n">
-        <v>44.88</v>
+        <v>45.36</v>
       </c>
       <c r="L31" t="n">
-        <v>57.46</v>
+        <v>58.07</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>-52.37</v>
+        <v>-52.26</v>
       </c>
       <c r="K32" t="n">
-        <v>-54.86</v>
+        <v>-54.75</v>
       </c>
       <c r="L32" t="n">
-        <v>75.84999999999999</v>
+        <v>75.69</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-62.81</v>
+        <v>-64.45</v>
       </c>
       <c r="K33" t="n">
-        <v>-5.83</v>
+        <v>-5.98</v>
       </c>
       <c r="L33" t="n">
-        <v>63.08</v>
+        <v>64.73</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-79.37</v>
+        <v>-78.84999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>-11.8</v>
+        <v>-11.72</v>
       </c>
       <c r="L34" t="n">
-        <v>80.23999999999999</v>
+        <v>79.72</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>143.29</v>
+        <v>136.33</v>
       </c>
       <c r="K35" t="n">
-        <v>86.44</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>167.34</v>
+        <v>159.21</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-90.56999999999999</v>
+        <v>-86.98999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>132.2</v>
+        <v>126.98</v>
       </c>
       <c r="L36" t="n">
-        <v>160.25</v>
+        <v>153.92</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>59.08</v>
+        <v>64.14</v>
       </c>
       <c r="K37" t="n">
-        <v>10.17</v>
+        <v>11.05</v>
       </c>
       <c r="L37" t="n">
-        <v>59.95</v>
+        <v>65.09</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>152.96</v>
+        <v>148.64</v>
       </c>
       <c r="K38" t="n">
-        <v>145.8</v>
+        <v>141.68</v>
       </c>
       <c r="L38" t="n">
-        <v>211.31</v>
+        <v>205.35</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-27.21</v>
+        <v>-29.21</v>
       </c>
       <c r="K39" t="n">
-        <v>-88.56999999999999</v>
+        <v>-95.05</v>
       </c>
       <c r="L39" t="n">
-        <v>92.66</v>
+        <v>99.44</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>220.69</v>
+        <v>210.36</v>
       </c>
       <c r="K40" t="n">
         <v>-0</v>
       </c>
       <c r="L40" t="n">
-        <v>220.69</v>
+        <v>210.36</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>11.46</v>
+        <v>11.98</v>
       </c>
       <c r="K41" t="n">
-        <v>-143.88</v>
+        <v>-150.42</v>
       </c>
       <c r="L41" t="n">
-        <v>144.34</v>
+        <v>150.89</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-113.39</v>
+        <v>-107.39</v>
       </c>
       <c r="K42" t="n">
-        <v>-328.45</v>
+        <v>-311.06</v>
       </c>
       <c r="L42" t="n">
-        <v>347.47</v>
+        <v>329.08</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>162.29</v>
+        <v>163.8</v>
       </c>
       <c r="K43" t="n">
-        <v>28.79</v>
+        <v>29.06</v>
       </c>
       <c r="L43" t="n">
-        <v>164.82</v>
+        <v>166.36</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>-30.32</v>
+        <v>-30.74</v>
       </c>
       <c r="K44" t="n">
-        <v>-43.29</v>
+        <v>-43.89</v>
       </c>
       <c r="L44" t="n">
-        <v>52.85</v>
+        <v>53.58</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>27.2</v>
+        <v>29.84</v>
       </c>
       <c r="K45" t="n">
-        <v>-12.59</v>
+        <v>-13.82</v>
       </c>
       <c r="L45" t="n">
-        <v>29.97</v>
+        <v>32.88</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>-43.63</v>
+        <v>-42.69</v>
       </c>
       <c r="K46" t="n">
-        <v>-48.67</v>
+        <v>-47.62</v>
       </c>
       <c r="L46" t="n">
-        <v>65.37</v>
+        <v>63.95</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>-57.94</v>
+        <v>-58.95</v>
       </c>
       <c r="K47" t="n">
-        <v>29.05</v>
+        <v>29.56</v>
       </c>
       <c r="L47" t="n">
-        <v>64.81</v>
+        <v>65.94</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>52.22</v>
+        <v>50.53</v>
       </c>
       <c r="K48" t="n">
-        <v>-78.02</v>
+        <v>-75.5</v>
       </c>
       <c r="L48" t="n">
-        <v>93.88</v>
+        <v>90.84999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.48</v>
+        <v>-5.3</v>
       </c>
       <c r="K49" t="n">
-        <v>-95.15000000000001</v>
+        <v>-92.04000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>95.3</v>
+        <v>92.19</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>80.8</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>-48.88</v>
+        <v>-49.58</v>
       </c>
       <c r="L50" t="n">
-        <v>94.43000000000001</v>
+        <v>95.79000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>28</v>
       </c>
       <c r="J51" t="n">
-        <v>-22.91</v>
+        <v>-22.97</v>
       </c>
       <c r="K51" t="n">
-        <v>-90.17</v>
+        <v>-90.39</v>
       </c>
       <c r="L51" t="n">
-        <v>93.03</v>
+        <v>93.26000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>73.95999999999999</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-44.34</v>
+        <v>-44.99</v>
       </c>
       <c r="L52" t="n">
-        <v>86.23999999999999</v>
+        <v>87.48999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-48.15</v>
+        <v>-50.57</v>
       </c>
       <c r="K53" t="n">
-        <v>-83.76000000000001</v>
+        <v>-87.97</v>
       </c>
       <c r="L53" t="n">
-        <v>96.61</v>
+        <v>101.47</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>11.91</v>
+        <v>11.61</v>
       </c>
       <c r="K54" t="n">
-        <v>-194.26</v>
+        <v>-189.34</v>
       </c>
       <c r="L54" t="n">
-        <v>194.63</v>
+        <v>189.69</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>31.34</v>
+        <v>32.87</v>
       </c>
       <c r="K55" t="n">
-        <v>-93.81999999999999</v>
+        <v>-98.41</v>
       </c>
       <c r="L55" t="n">
-        <v>98.91</v>
+        <v>103.75</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>186.08</v>
+        <v>187.86</v>
       </c>
       <c r="K56" t="n">
-        <v>258.91</v>
+        <v>261.39</v>
       </c>
       <c r="L56" t="n">
-        <v>318.84</v>
+        <v>321.89</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-118.06</v>
+        <v>-125.06</v>
       </c>
       <c r="K57" t="n">
-        <v>-10.39</v>
+        <v>-11.01</v>
       </c>
       <c r="L57" t="n">
-        <v>118.52</v>
+        <v>125.55</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>200.86</v>
+        <v>197.24</v>
       </c>
       <c r="K58" t="n">
-        <v>-123.33</v>
+        <v>-121.1</v>
       </c>
       <c r="L58" t="n">
-        <v>235.7</v>
+        <v>231.45</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>-18.46</v>
+        <v>-15.09</v>
       </c>
       <c r="K59" t="n">
-        <v>96.23999999999999</v>
+        <v>78.64</v>
       </c>
       <c r="L59" t="n">
-        <v>98</v>
+        <v>80.06999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-32.81</v>
+        <v>-33.24</v>
       </c>
       <c r="K60" t="n">
-        <v>-36.74</v>
+        <v>-37.22</v>
       </c>
       <c r="L60" t="n">
-        <v>49.26</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>45.05</v>
+        <v>46.4</v>
       </c>
       <c r="K61" t="n">
-        <v>-16.74</v>
+        <v>-17.25</v>
       </c>
       <c r="L61" t="n">
-        <v>48.06</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>48.53</v>
+        <v>50.78</v>
       </c>
       <c r="K62" t="n">
-        <v>17.92</v>
+        <v>18.75</v>
       </c>
       <c r="L62" t="n">
-        <v>51.73</v>
+        <v>54.13</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>87.91</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>31.83</v>
+        <v>31.21</v>
       </c>
       <c r="L63" t="n">
-        <v>93.48999999999999</v>
+        <v>91.68000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2743,10 +2743,10 @@
         <v>-15.66</v>
       </c>
       <c r="K64" t="n">
-        <v>70.14</v>
+        <v>70.12</v>
       </c>
       <c r="L64" t="n">
-        <v>71.87</v>
+        <v>71.84999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-65.95999999999999</v>
+        <v>-68.42</v>
       </c>
       <c r="K65" t="n">
-        <v>50.12</v>
+        <v>51.99</v>
       </c>
       <c r="L65" t="n">
-        <v>82.84999999999999</v>
+        <v>85.94</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>54.87</v>
+        <v>57.09</v>
       </c>
       <c r="K66" t="n">
-        <v>-58.09</v>
+        <v>-60.44</v>
       </c>
       <c r="L66" t="n">
-        <v>79.91</v>
+        <v>83.15000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-52.75</v>
+        <v>-52.27</v>
       </c>
       <c r="K67" t="n">
-        <v>-104.76</v>
+        <v>-103.8</v>
       </c>
       <c r="L67" t="n">
-        <v>117.29</v>
+        <v>116.22</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>-120.01</v>
+        <v>-118.84</v>
       </c>
       <c r="K68" t="n">
-        <v>109.65</v>
+        <v>108.59</v>
       </c>
       <c r="L68" t="n">
-        <v>162.56</v>
+        <v>160.98</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>134.18</v>
+        <v>134.29</v>
       </c>
       <c r="K69" t="n">
-        <v>-36.76</v>
+        <v>-36.79</v>
       </c>
       <c r="L69" t="n">
-        <v>139.12</v>
+        <v>139.23</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>113.43</v>
+        <v>116.74</v>
       </c>
       <c r="K70" t="n">
-        <v>47.65</v>
+        <v>49.04</v>
       </c>
       <c r="L70" t="n">
-        <v>123.03</v>
+        <v>126.62</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>212.99</v>
+        <v>208.03</v>
       </c>
       <c r="K71" t="n">
-        <v>-107.83</v>
+        <v>-105.32</v>
       </c>
       <c r="L71" t="n">
-        <v>238.73</v>
+        <v>233.17</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>58.92</v>
+        <v>62.93</v>
       </c>
       <c r="K72" t="n">
-        <v>118.07</v>
+        <v>126.11</v>
       </c>
       <c r="L72" t="n">
-        <v>131.95</v>
+        <v>140.94</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-55.33</v>
+        <v>-55.31</v>
       </c>
       <c r="K73" t="n">
-        <v>-198.45</v>
+        <v>-198.39</v>
       </c>
       <c r="L73" t="n">
-        <v>206.02</v>
+        <v>205.95</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>39.03</v>
+        <v>41</v>
       </c>
       <c r="K74" t="n">
-        <v>-16.93</v>
+        <v>-17.79</v>
       </c>
       <c r="L74" t="n">
-        <v>42.54</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-29.14</v>
+        <v>-26.89</v>
       </c>
       <c r="K75" t="n">
-        <v>-73.94</v>
+        <v>-68.23999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>79.48</v>
+        <v>73.34999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="K76" t="n">
-        <v>112.92</v>
+        <v>106.42</v>
       </c>
       <c r="L76" t="n">
-        <v>112.96</v>
+        <v>106.45</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-98.34</v>
+        <v>-92.93000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-79.98999999999999</v>
+        <v>-75.59</v>
       </c>
       <c r="L77" t="n">
-        <v>126.76</v>
+        <v>119.79</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>132.27</v>
+        <v>122.96</v>
       </c>
       <c r="K78" t="n">
-        <v>-69.01000000000001</v>
+        <v>-64.15000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>149.19</v>
+        <v>138.69</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>19.87</v>
+        <v>20.29</v>
       </c>
       <c r="K79" t="n">
-        <v>60.26</v>
+        <v>61.53</v>
       </c>
       <c r="L79" t="n">
-        <v>63.45</v>
+        <v>64.78</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>99.51000000000001</v>
+        <v>100.22</v>
       </c>
       <c r="K80" t="n">
-        <v>8.02</v>
+        <v>8.07</v>
       </c>
       <c r="L80" t="n">
-        <v>99.83</v>
+        <v>100.54</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>26</v>
       </c>
       <c r="J81" t="n">
-        <v>56.68</v>
+        <v>56.42</v>
       </c>
       <c r="K81" t="n">
-        <v>-87.95</v>
+        <v>-87.55</v>
       </c>
       <c r="L81" t="n">
-        <v>104.63</v>
+        <v>104.15</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-11.37</v>
+        <v>-12.32</v>
       </c>
       <c r="K82" t="n">
-        <v>53.74</v>
+        <v>58.23</v>
       </c>
       <c r="L82" t="n">
-        <v>54.93</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>28</v>
       </c>
       <c r="J83" t="n">
-        <v>-48.21</v>
+        <v>-47.97</v>
       </c>
       <c r="K83" t="n">
-        <v>-139.03</v>
+        <v>-138.32</v>
       </c>
       <c r="L83" t="n">
-        <v>147.15</v>
+        <v>146.4</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-144.68</v>
+        <v>-145.23</v>
       </c>
       <c r="K84" t="n">
-        <v>-38.47</v>
+        <v>-38.62</v>
       </c>
       <c r="L84" t="n">
-        <v>149.71</v>
+        <v>150.28</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-79.12</v>
+        <v>-79.81</v>
       </c>
       <c r="K85" t="n">
-        <v>-119.04</v>
+        <v>-120.08</v>
       </c>
       <c r="L85" t="n">
-        <v>142.94</v>
+        <v>144.18</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>54.13</v>
+        <v>52.95</v>
       </c>
       <c r="K86" t="n">
-        <v>17.8</v>
+        <v>17.41</v>
       </c>
       <c r="L86" t="n">
-        <v>56.98</v>
+        <v>55.74</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>117.52</v>
+        <v>116.77</v>
       </c>
       <c r="K87" t="n">
-        <v>-165.74</v>
+        <v>-164.68</v>
       </c>
       <c r="L87" t="n">
-        <v>203.18</v>
+        <v>201.88</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>52.98</v>
+        <v>51.84</v>
       </c>
       <c r="K88" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="L88" t="n">
-        <v>53</v>
+        <v>51.85</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-03.xlsx
+++ b/output/2025-10-03.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>36.01</v>
+        <v>38.98</v>
       </c>
       <c r="K14" t="n">
-        <v>25.53</v>
+        <v>27.64</v>
       </c>
       <c r="L14" t="n">
-        <v>44.14</v>
+        <v>47.79</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-44.81</v>
+        <v>-44.14</v>
       </c>
       <c r="K15" t="n">
-        <v>-50.45</v>
+        <v>-49.7</v>
       </c>
       <c r="L15" t="n">
-        <v>67.48</v>
+        <v>66.47</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.039999999999999</v>
+        <v>-9.01</v>
       </c>
       <c r="K16" t="n">
-        <v>55.01</v>
+        <v>54.81</v>
       </c>
       <c r="L16" t="n">
-        <v>55.75</v>
+        <v>55.55</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>8.35</v>
+        <v>9.07</v>
       </c>
       <c r="K17" t="n">
-        <v>-18.98</v>
+        <v>-20.62</v>
       </c>
       <c r="L17" t="n">
-        <v>20.73</v>
+        <v>22.53</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-62.18</v>
+        <v>-57.36</v>
       </c>
       <c r="K18" t="n">
-        <v>-112.66</v>
+        <v>-103.93</v>
       </c>
       <c r="L18" t="n">
-        <v>128.68</v>
+        <v>118.71</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="K19" t="n">
-        <v>-75.34999999999999</v>
+        <v>-74.94</v>
       </c>
       <c r="L19" t="n">
-        <v>75.43000000000001</v>
+        <v>75.01000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-115.19</v>
+        <v>-113.27</v>
       </c>
       <c r="K20" t="n">
-        <v>-20.8</v>
+        <v>-20.45</v>
       </c>
       <c r="L20" t="n">
-        <v>117.05</v>
+        <v>115.1</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>104.49</v>
+        <v>103.7</v>
       </c>
       <c r="K21" t="n">
-        <v>6.97</v>
+        <v>6.92</v>
       </c>
       <c r="L21" t="n">
-        <v>104.72</v>
+        <v>103.93</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-108.5</v>
+        <v>-104.97</v>
       </c>
       <c r="K22" t="n">
-        <v>-54.1</v>
+        <v>-52.34</v>
       </c>
       <c r="L22" t="n">
-        <v>121.24</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>73.65000000000001</v>
+        <v>76.81</v>
       </c>
       <c r="K23" t="n">
-        <v>90.23</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>116.47</v>
+        <v>121.46</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>121.71</v>
+        <v>124.64</v>
       </c>
       <c r="K24" t="n">
-        <v>-27.34</v>
+        <v>-27.99</v>
       </c>
       <c r="L24" t="n">
-        <v>124.75</v>
+        <v>127.75</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>6.19</v>
+        <v>6.08</v>
       </c>
       <c r="K25" t="n">
-        <v>-160.24</v>
+        <v>-157.4</v>
       </c>
       <c r="L25" t="n">
-        <v>160.36</v>
+        <v>157.51</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-279.33</v>
+        <v>-266.64</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.37</v>
+        <v>-3.22</v>
       </c>
       <c r="L26" t="n">
-        <v>279.35</v>
+        <v>266.66</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-149.57</v>
+        <v>-147.25</v>
       </c>
       <c r="K27" t="n">
-        <v>-161.84</v>
+        <v>-159.32</v>
       </c>
       <c r="L27" t="n">
-        <v>220.37</v>
+        <v>216.95</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>74.08</v>
+        <v>81.44</v>
       </c>
       <c r="K28" t="n">
-        <v>69.31</v>
+        <v>76.2</v>
       </c>
       <c r="L28" t="n">
-        <v>101.45</v>
+        <v>111.53</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>-24.81</v>
+        <v>-26.42</v>
       </c>
       <c r="K29" t="n">
-        <v>-34.5</v>
+        <v>-36.76</v>
       </c>
       <c r="L29" t="n">
-        <v>42.5</v>
+        <v>45.27</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>32.6</v>
+        <v>32.99</v>
       </c>
       <c r="K30" t="n">
-        <v>-30.25</v>
+        <v>-30.62</v>
       </c>
       <c r="L30" t="n">
-        <v>44.47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>36.25</v>
+        <v>36.69</v>
       </c>
       <c r="K31" t="n">
-        <v>45.36</v>
+        <v>45.9</v>
       </c>
       <c r="L31" t="n">
-        <v>58.07</v>
+        <v>58.76</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>-52.26</v>
+        <v>-52.13</v>
       </c>
       <c r="K32" t="n">
-        <v>-54.75</v>
+        <v>-54.62</v>
       </c>
       <c r="L32" t="n">
-        <v>75.69</v>
+        <v>75.51000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-64.45</v>
+        <v>-66.33</v>
       </c>
       <c r="K33" t="n">
-        <v>-5.98</v>
+        <v>-6.16</v>
       </c>
       <c r="L33" t="n">
-        <v>64.73</v>
+        <v>66.62</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-78.84999999999999</v>
+        <v>-78.84</v>
       </c>
       <c r="K34" t="n">
         <v>-11.72</v>
       </c>
       <c r="L34" t="n">
-        <v>79.72</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>136.33</v>
+        <v>128.37</v>
       </c>
       <c r="K35" t="n">
-        <v>82.23999999999999</v>
+        <v>77.44</v>
       </c>
       <c r="L35" t="n">
-        <v>159.21</v>
+        <v>149.92</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-86.98999999999999</v>
+        <v>-82.90000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>126.98</v>
+        <v>121.01</v>
       </c>
       <c r="L36" t="n">
-        <v>153.92</v>
+        <v>146.69</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>64.14</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>11.05</v>
+        <v>12.04</v>
       </c>
       <c r="L37" t="n">
-        <v>65.09</v>
+        <v>70.95999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>148.64</v>
+        <v>143.34</v>
       </c>
       <c r="K38" t="n">
-        <v>141.68</v>
+        <v>136.64</v>
       </c>
       <c r="L38" t="n">
-        <v>205.35</v>
+        <v>198.03</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-29.21</v>
+        <v>-31.41</v>
       </c>
       <c r="K39" t="n">
-        <v>-95.05</v>
+        <v>-102.22</v>
       </c>
       <c r="L39" t="n">
-        <v>99.44</v>
+        <v>106.93</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>210.36</v>
+        <v>198.55</v>
       </c>
       <c r="K40" t="n">
         <v>-0</v>
       </c>
       <c r="L40" t="n">
-        <v>210.36</v>
+        <v>198.55</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>11.98</v>
+        <v>12.58</v>
       </c>
       <c r="K41" t="n">
-        <v>-150.42</v>
+        <v>-157.89</v>
       </c>
       <c r="L41" t="n">
-        <v>150.89</v>
+        <v>158.39</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-107.39</v>
+        <v>-100.53</v>
       </c>
       <c r="K42" t="n">
-        <v>-311.06</v>
+        <v>-291.2</v>
       </c>
       <c r="L42" t="n">
-        <v>329.08</v>
+        <v>308.06</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>163.8</v>
+        <v>165.52</v>
       </c>
       <c r="K43" t="n">
-        <v>29.06</v>
+        <v>29.37</v>
       </c>
       <c r="L43" t="n">
-        <v>166.36</v>
+        <v>168.1</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>-30.74</v>
+        <v>-31.33</v>
       </c>
       <c r="K44" t="n">
-        <v>-43.89</v>
+        <v>-44.73</v>
       </c>
       <c r="L44" t="n">
-        <v>53.58</v>
+        <v>54.61</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>29.84</v>
+        <v>32.86</v>
       </c>
       <c r="K45" t="n">
-        <v>-13.82</v>
+        <v>-15.22</v>
       </c>
       <c r="L45" t="n">
-        <v>32.88</v>
+        <v>36.21</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>-42.69</v>
+        <v>-41.61</v>
       </c>
       <c r="K46" t="n">
-        <v>-47.62</v>
+        <v>-46.41</v>
       </c>
       <c r="L46" t="n">
-        <v>63.95</v>
+        <v>62.33</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>-58.95</v>
+        <v>-60.11</v>
       </c>
       <c r="K47" t="n">
-        <v>29.56</v>
+        <v>30.14</v>
       </c>
       <c r="L47" t="n">
-        <v>65.94</v>
+        <v>67.23999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>50.53</v>
+        <v>48.61</v>
       </c>
       <c r="K48" t="n">
-        <v>-75.5</v>
+        <v>-72.62</v>
       </c>
       <c r="L48" t="n">
-        <v>90.84999999999999</v>
+        <v>87.39</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.3</v>
+        <v>-5.1</v>
       </c>
       <c r="K49" t="n">
-        <v>-92.04000000000001</v>
+        <v>-88.48999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>92.19</v>
+        <v>88.64</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>81.95999999999999</v>
+        <v>83.28</v>
       </c>
       <c r="K50" t="n">
-        <v>-49.58</v>
+        <v>-50.38</v>
       </c>
       <c r="L50" t="n">
-        <v>95.79000000000001</v>
+        <v>97.34</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>28</v>
       </c>
       <c r="J51" t="n">
-        <v>-22.97</v>
+        <v>-23.03</v>
       </c>
       <c r="K51" t="n">
-        <v>-90.39</v>
+        <v>-90.65000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>93.26000000000001</v>
+        <v>93.53</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>75.04000000000001</v>
+        <v>76.27</v>
       </c>
       <c r="K52" t="n">
-        <v>-44.99</v>
+        <v>-45.73</v>
       </c>
       <c r="L52" t="n">
-        <v>87.48999999999999</v>
+        <v>88.93000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-50.57</v>
+        <v>-53.33</v>
       </c>
       <c r="K53" t="n">
-        <v>-87.97</v>
+        <v>-92.78</v>
       </c>
       <c r="L53" t="n">
-        <v>101.47</v>
+        <v>107.01</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>11.61</v>
+        <v>11.24</v>
       </c>
       <c r="K54" t="n">
-        <v>-189.34</v>
+        <v>-183.32</v>
       </c>
       <c r="L54" t="n">
-        <v>189.69</v>
+        <v>183.66</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>32.87</v>
+        <v>34.62</v>
       </c>
       <c r="K55" t="n">
-        <v>-98.41</v>
+        <v>-103.65</v>
       </c>
       <c r="L55" t="n">
-        <v>103.75</v>
+        <v>109.28</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>187.86</v>
+        <v>180.29</v>
       </c>
       <c r="K56" t="n">
-        <v>261.39</v>
+        <v>250.85</v>
       </c>
       <c r="L56" t="n">
-        <v>321.89</v>
+        <v>308.91</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-125.06</v>
+        <v>-133.06</v>
       </c>
       <c r="K57" t="n">
-        <v>-11.01</v>
+        <v>-11.71</v>
       </c>
       <c r="L57" t="n">
-        <v>125.55</v>
+        <v>133.57</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>197.24</v>
+        <v>193.09</v>
       </c>
       <c r="K58" t="n">
-        <v>-121.1</v>
+        <v>-118.56</v>
       </c>
       <c r="L58" t="n">
-        <v>231.45</v>
+        <v>226.58</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>-15.09</v>
+        <v>-14.74</v>
       </c>
       <c r="K59" t="n">
-        <v>78.64</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>80.06999999999999</v>
+        <v>78.25</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-33.24</v>
+        <v>-33.72</v>
       </c>
       <c r="K60" t="n">
-        <v>-37.22</v>
+        <v>-37.76</v>
       </c>
       <c r="L60" t="n">
-        <v>49.9</v>
+        <v>50.63</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>46.4</v>
+        <v>47.95</v>
       </c>
       <c r="K61" t="n">
-        <v>-17.25</v>
+        <v>-17.82</v>
       </c>
       <c r="L61" t="n">
-        <v>49.5</v>
+        <v>51.15</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>50.78</v>
+        <v>53.35</v>
       </c>
       <c r="K62" t="n">
-        <v>18.75</v>
+        <v>19.7</v>
       </c>
       <c r="L62" t="n">
-        <v>54.13</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>86.20999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>31.21</v>
+        <v>30.63</v>
       </c>
       <c r="L63" t="n">
-        <v>91.68000000000001</v>
+        <v>89.98</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-15.66</v>
+        <v>-15.65</v>
       </c>
       <c r="K64" t="n">
-        <v>70.12</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>71.84999999999999</v>
+        <v>71.81999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-68.42</v>
+        <v>-71.39</v>
       </c>
       <c r="K65" t="n">
-        <v>51.99</v>
+        <v>54.25</v>
       </c>
       <c r="L65" t="n">
-        <v>85.94</v>
+        <v>89.67</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>57.09</v>
+        <v>59.64</v>
       </c>
       <c r="K66" t="n">
-        <v>-60.44</v>
+        <v>-63.14</v>
       </c>
       <c r="L66" t="n">
-        <v>83.15000000000001</v>
+        <v>86.84999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-52.27</v>
+        <v>-51.88</v>
       </c>
       <c r="K67" t="n">
-        <v>-103.8</v>
+        <v>-103.02</v>
       </c>
       <c r="L67" t="n">
-        <v>116.22</v>
+        <v>115.35</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>-118.84</v>
+        <v>-117.5</v>
       </c>
       <c r="K68" t="n">
-        <v>108.59</v>
+        <v>107.37</v>
       </c>
       <c r="L68" t="n">
-        <v>160.98</v>
+        <v>159.17</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>134.29</v>
+        <v>134.41</v>
       </c>
       <c r="K69" t="n">
-        <v>-36.79</v>
+        <v>-36.82</v>
       </c>
       <c r="L69" t="n">
-        <v>139.23</v>
+        <v>139.36</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>116.74</v>
+        <v>120.52</v>
       </c>
       <c r="K70" t="n">
-        <v>49.04</v>
+        <v>50.63</v>
       </c>
       <c r="L70" t="n">
-        <v>126.62</v>
+        <v>130.73</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>208.03</v>
+        <v>202.36</v>
       </c>
       <c r="K71" t="n">
-        <v>-105.32</v>
+        <v>-102.45</v>
       </c>
       <c r="L71" t="n">
-        <v>233.17</v>
+        <v>226.82</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>62.93</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="K72" t="n">
-        <v>126.11</v>
+        <v>135.3</v>
       </c>
       <c r="L72" t="n">
-        <v>140.94</v>
+        <v>151.2</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-55.31</v>
+        <v>-55.29</v>
       </c>
       <c r="K73" t="n">
-        <v>-198.39</v>
+        <v>-198.31</v>
       </c>
       <c r="L73" t="n">
-        <v>205.95</v>
+        <v>205.88</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>41</v>
+        <v>43.46</v>
       </c>
       <c r="K74" t="n">
-        <v>-17.79</v>
+        <v>-18.85</v>
       </c>
       <c r="L74" t="n">
-        <v>44.7</v>
+        <v>47.38</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-26.89</v>
+        <v>-26.58</v>
       </c>
       <c r="K75" t="n">
-        <v>-68.23999999999999</v>
+        <v>-67.45</v>
       </c>
       <c r="L75" t="n">
-        <v>73.34999999999999</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>2.59</v>
+        <v>2.43</v>
       </c>
       <c r="K76" t="n">
-        <v>106.42</v>
+        <v>99.62</v>
       </c>
       <c r="L76" t="n">
-        <v>106.45</v>
+        <v>99.65000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-92.93000000000001</v>
+        <v>-87.48</v>
       </c>
       <c r="K77" t="n">
-        <v>-75.59</v>
+        <v>-71.15000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>119.79</v>
+        <v>112.76</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>122.96</v>
+        <v>114.49</v>
       </c>
       <c r="K78" t="n">
-        <v>-64.15000000000001</v>
+        <v>-59.73</v>
       </c>
       <c r="L78" t="n">
-        <v>138.69</v>
+        <v>129.13</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>20.29</v>
+        <v>21.04</v>
       </c>
       <c r="K79" t="n">
-        <v>61.53</v>
+        <v>63.82</v>
       </c>
       <c r="L79" t="n">
-        <v>64.78</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>100.22</v>
+        <v>101.02</v>
       </c>
       <c r="K80" t="n">
-        <v>8.07</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>100.54</v>
+        <v>101.35</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>26</v>
       </c>
       <c r="J81" t="n">
-        <v>56.42</v>
+        <v>56.22</v>
       </c>
       <c r="K81" t="n">
-        <v>-87.55</v>
+        <v>-87.23999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>104.15</v>
+        <v>103.78</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-12.32</v>
+        <v>-13.4</v>
       </c>
       <c r="K82" t="n">
-        <v>58.23</v>
+        <v>63.37</v>
       </c>
       <c r="L82" t="n">
-        <v>59.52</v>
+        <v>64.77</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>28</v>
       </c>
       <c r="J83" t="n">
-        <v>-47.97</v>
+        <v>-47.6</v>
       </c>
       <c r="K83" t="n">
-        <v>-138.32</v>
+        <v>-137.25</v>
       </c>
       <c r="L83" t="n">
-        <v>146.4</v>
+        <v>145.27</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-145.23</v>
+        <v>-145.64</v>
       </c>
       <c r="K84" t="n">
-        <v>-38.62</v>
+        <v>-38.73</v>
       </c>
       <c r="L84" t="n">
-        <v>150.28</v>
+        <v>150.7</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-79.81</v>
+        <v>-80.43000000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>-120.08</v>
+        <v>-121.01</v>
       </c>
       <c r="L85" t="n">
-        <v>144.18</v>
+        <v>145.3</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>52.95</v>
+        <v>57.6</v>
       </c>
       <c r="K86" t="n">
-        <v>17.41</v>
+        <v>18.94</v>
       </c>
       <c r="L86" t="n">
-        <v>55.74</v>
+        <v>60.63</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>116.77</v>
+        <v>115.91</v>
       </c>
       <c r="K87" t="n">
-        <v>-164.68</v>
+        <v>-163.47</v>
       </c>
       <c r="L87" t="n">
-        <v>201.88</v>
+        <v>200.39</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>51.84</v>
+        <v>56.35</v>
       </c>
       <c r="K88" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="L88" t="n">
-        <v>51.85</v>
+        <v>56.36</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-03.xlsx
+++ b/output/2025-10-03.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.51</v>
+        <v>2.63</v>
       </c>
       <c r="F14" t="n">
-        <v>6.75</v>
+        <v>6.79</v>
       </c>
       <c r="G14" t="n">
-        <v>119</v>
+        <v>120.8</v>
       </c>
       <c r="H14" t="n">
-        <v>89.8</v>
+        <v>85.8</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>38.98</v>
+        <v>10.06</v>
       </c>
       <c r="K14" t="n">
-        <v>27.64</v>
+        <v>-42.38</v>
       </c>
       <c r="L14" t="n">
-        <v>47.79</v>
+        <v>43.55</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:23:05</t>
+          <t>07:23:34</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6</v>
+        <v>3.59</v>
       </c>
       <c r="F15" t="n">
-        <v>7.66</v>
+        <v>7.01</v>
       </c>
       <c r="G15" t="n">
-        <v>112.9</v>
+        <v>113.5</v>
       </c>
       <c r="H15" t="n">
-        <v>86.59999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-44.14</v>
+        <v>-25.38</v>
       </c>
       <c r="K15" t="n">
-        <v>-49.7</v>
+        <v>18.45</v>
       </c>
       <c r="L15" t="n">
-        <v>66.47</v>
+        <v>31.38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:24:02</t>
+          <t>07:25:02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="F16" t="n">
-        <v>7.52</v>
+        <v>8.74</v>
       </c>
       <c r="G16" t="n">
-        <v>125.4</v>
+        <v>120.6</v>
       </c>
       <c r="H16" t="n">
-        <v>85.90000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.01</v>
+        <v>-56.39</v>
       </c>
       <c r="K16" t="n">
-        <v>54.81</v>
+        <v>48</v>
       </c>
       <c r="L16" t="n">
-        <v>55.55</v>
+        <v>74.05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:27:20</t>
+          <t>07:30:47</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.07</v>
+        <v>2.25</v>
       </c>
       <c r="F17" t="n">
-        <v>7.99</v>
+        <v>5.31</v>
       </c>
       <c r="G17" t="n">
-        <v>105.5</v>
+        <v>116</v>
       </c>
       <c r="H17" t="n">
-        <v>94.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>9.07</v>
+        <v>27.19</v>
       </c>
       <c r="K17" t="n">
-        <v>-20.62</v>
+        <v>63.05</v>
       </c>
       <c r="L17" t="n">
-        <v>22.53</v>
+        <v>68.67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:29:28</t>
+          <t>07:32:49</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="F18" t="n">
-        <v>7.73</v>
+        <v>5.48</v>
       </c>
       <c r="G18" t="n">
-        <v>107.4</v>
+        <v>125.5</v>
       </c>
       <c r="H18" t="n">
-        <v>87.09999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>-57.36</v>
+        <v>49.91</v>
       </c>
       <c r="K18" t="n">
-        <v>-103.93</v>
+        <v>-30.86</v>
       </c>
       <c r="L18" t="n">
-        <v>118.71</v>
+        <v>58.68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:31:44</t>
+          <t>07:34:10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.67</v>
+        <v>2.31</v>
       </c>
       <c r="F19" t="n">
-        <v>7.53</v>
+        <v>3.63</v>
       </c>
       <c r="G19" t="n">
-        <v>117.3</v>
+        <v>105.3</v>
       </c>
       <c r="H19" t="n">
-        <v>85</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>3.34</v>
+        <v>-42.69</v>
       </c>
       <c r="K19" t="n">
-        <v>-74.94</v>
+        <v>34.14</v>
       </c>
       <c r="L19" t="n">
-        <v>75.01000000000001</v>
+        <v>54.66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:37:12</t>
+          <t>07:40:37</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="F20" t="n">
-        <v>7.44</v>
+        <v>5.03</v>
       </c>
       <c r="G20" t="n">
-        <v>113.1</v>
+        <v>116.8</v>
       </c>
       <c r="H20" t="n">
-        <v>81.8</v>
+        <v>87.3</v>
       </c>
       <c r="I20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>-113.27</v>
+        <v>-94.91</v>
       </c>
       <c r="K20" t="n">
-        <v>-20.45</v>
+        <v>-4.4</v>
       </c>
       <c r="L20" t="n">
-        <v>115.1</v>
+        <v>95.01000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:38:50</t>
+          <t>07:42:28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="F21" t="n">
-        <v>7.61</v>
+        <v>6.63</v>
       </c>
       <c r="G21" t="n">
-        <v>106.9</v>
+        <v>110.1</v>
       </c>
       <c r="H21" t="n">
-        <v>87.09999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>103.7</v>
+        <v>16.85</v>
       </c>
       <c r="K21" t="n">
-        <v>6.92</v>
+        <v>-34.04</v>
       </c>
       <c r="L21" t="n">
-        <v>103.93</v>
+        <v>37.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:40:02</t>
+          <t>07:43:20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.73</v>
+        <v>2.3</v>
       </c>
       <c r="F22" t="n">
-        <v>7.57</v>
+        <v>5.29</v>
       </c>
       <c r="G22" t="n">
-        <v>116.9</v>
+        <v>99.7</v>
       </c>
       <c r="H22" t="n">
-        <v>84.09999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="I22" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-104.97</v>
+        <v>-131.34</v>
       </c>
       <c r="K22" t="n">
-        <v>-52.34</v>
+        <v>22.52</v>
       </c>
       <c r="L22" t="n">
-        <v>117.3</v>
+        <v>133.25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:45:27</t>
+          <t>07:48:28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.67</v>
+        <v>3.03</v>
       </c>
       <c r="F23" t="n">
-        <v>7.73</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>99.59999999999999</v>
+        <v>108.6</v>
       </c>
       <c r="H23" t="n">
-        <v>82.3</v>
+        <v>88</v>
       </c>
       <c r="I23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>76.81</v>
+        <v>129.18</v>
       </c>
       <c r="K23" t="n">
-        <v>94.09999999999999</v>
+        <v>-63.26</v>
       </c>
       <c r="L23" t="n">
-        <v>121.46</v>
+        <v>143.84</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:46:58</t>
+          <t>07:49:49</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.49</v>
+        <v>2.95</v>
       </c>
       <c r="F24" t="n">
-        <v>7.8</v>
+        <v>7.81</v>
       </c>
       <c r="G24" t="n">
-        <v>115.3</v>
+        <v>118.8</v>
       </c>
       <c r="H24" t="n">
-        <v>83.40000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>124.64</v>
+        <v>-39.95</v>
       </c>
       <c r="K24" t="n">
-        <v>-27.99</v>
+        <v>137.26</v>
       </c>
       <c r="L24" t="n">
-        <v>127.75</v>
+        <v>142.95</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:48:27</t>
+          <t>07:52:18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.81</v>
+        <v>3.01</v>
       </c>
       <c r="F25" t="n">
-        <v>7.95</v>
+        <v>5.16</v>
       </c>
       <c r="G25" t="n">
-        <v>111</v>
+        <v>119.4</v>
       </c>
       <c r="H25" t="n">
-        <v>83.5</v>
+        <v>87.2</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>6.08</v>
+        <v>-178.99</v>
       </c>
       <c r="K25" t="n">
-        <v>-157.4</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>157.51</v>
+        <v>193.31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:53:51</t>
+          <t>07:57:08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="F26" t="n">
-        <v>7.95</v>
+        <v>7.88</v>
       </c>
       <c r="G26" t="n">
-        <v>98.5</v>
+        <v>103.5</v>
       </c>
       <c r="H26" t="n">
-        <v>90.5</v>
+        <v>89.5</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>-266.64</v>
+        <v>189.4</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.22</v>
+        <v>-122.94</v>
       </c>
       <c r="L26" t="n">
-        <v>266.66</v>
+        <v>225.81</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:55:27</t>
+          <t>07:58:47</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="F27" t="n">
-        <v>7.45</v>
+        <v>4.98</v>
       </c>
       <c r="G27" t="n">
-        <v>110.6</v>
+        <v>122.4</v>
       </c>
       <c r="H27" t="n">
-        <v>88.7</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-147.25</v>
+        <v>218.44</v>
       </c>
       <c r="K27" t="n">
-        <v>-159.32</v>
+        <v>26.4</v>
       </c>
       <c r="L27" t="n">
-        <v>216.95</v>
+        <v>220.03</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:57:35</t>
+          <t>08:00:22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.89</v>
+        <v>3.24</v>
       </c>
       <c r="F28" t="n">
-        <v>7.77</v>
+        <v>8.58</v>
       </c>
       <c r="G28" t="n">
-        <v>125.7</v>
+        <v>109.8</v>
       </c>
       <c r="H28" t="n">
         <v>88.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>81.44</v>
+        <v>-125.21</v>
       </c>
       <c r="K28" t="n">
-        <v>76.2</v>
+        <v>-165.25</v>
       </c>
       <c r="L28" t="n">
-        <v>111.53</v>
+        <v>207.33</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:07:44</t>
+          <t>08:09:14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.92</v>
+        <v>3.33</v>
       </c>
       <c r="F29" t="n">
-        <v>8.43</v>
+        <v>7.97</v>
       </c>
       <c r="G29" t="n">
-        <v>110.4</v>
+        <v>106.8</v>
       </c>
       <c r="H29" t="n">
-        <v>82.90000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-26.42</v>
+        <v>-34.79</v>
       </c>
       <c r="K29" t="n">
-        <v>-36.76</v>
+        <v>-50.8</v>
       </c>
       <c r="L29" t="n">
-        <v>45.27</v>
+        <v>61.57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:09:19</t>
+          <t>08:11:04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="F30" t="n">
-        <v>7.37</v>
+        <v>6.21</v>
       </c>
       <c r="G30" t="n">
-        <v>111.3</v>
+        <v>117.6</v>
       </c>
       <c r="H30" t="n">
-        <v>83.3</v>
+        <v>92.2</v>
       </c>
       <c r="I30" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>32.99</v>
+        <v>-33.1</v>
       </c>
       <c r="K30" t="n">
-        <v>-30.62</v>
+        <v>43.08</v>
       </c>
       <c r="L30" t="n">
-        <v>45</v>
+        <v>54.33</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:11:15</t>
+          <t>08:13:07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="F31" t="n">
-        <v>7.78</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>119.2</v>
+        <v>124.4</v>
       </c>
       <c r="H31" t="n">
-        <v>84.7</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>36.69</v>
+        <v>-51.49</v>
       </c>
       <c r="K31" t="n">
-        <v>45.9</v>
+        <v>24.7</v>
       </c>
       <c r="L31" t="n">
-        <v>58.76</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:15:14</t>
+          <t>08:17:56</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="F32" t="n">
-        <v>7.71</v>
+        <v>5.18</v>
       </c>
       <c r="G32" t="n">
-        <v>110.2</v>
+        <v>113.5</v>
       </c>
       <c r="H32" t="n">
-        <v>81.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="I32" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-52.13</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-54.62</v>
+        <v>10.72</v>
       </c>
       <c r="L32" t="n">
-        <v>75.51000000000001</v>
+        <v>85.59999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:17:18</t>
+          <t>08:20:08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="F33" t="n">
-        <v>7.4</v>
+        <v>5.64</v>
       </c>
       <c r="G33" t="n">
-        <v>117</v>
+        <v>113.2</v>
       </c>
       <c r="H33" t="n">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="I33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-66.33</v>
+        <v>-12.84</v>
       </c>
       <c r="K33" t="n">
-        <v>-6.16</v>
+        <v>-56.85</v>
       </c>
       <c r="L33" t="n">
-        <v>66.62</v>
+        <v>58.28</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:18:23</t>
+          <t>08:22:08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.46</v>
+        <v>2.99</v>
       </c>
       <c r="F34" t="n">
         <v>7.44</v>
       </c>
       <c r="G34" t="n">
-        <v>113.5</v>
+        <v>127.2</v>
       </c>
       <c r="H34" t="n">
-        <v>87.7</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I34" t="n">
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-78.84</v>
+        <v>-33.88</v>
       </c>
       <c r="K34" t="n">
-        <v>-11.72</v>
+        <v>-90.88</v>
       </c>
       <c r="L34" t="n">
-        <v>79.7</v>
+        <v>96.98999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:23:26</t>
+          <t>08:28:08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.55</v>
+        <v>3.01</v>
       </c>
       <c r="F35" t="n">
-        <v>7.8</v>
+        <v>8.74</v>
       </c>
       <c r="G35" t="n">
-        <v>100</v>
+        <v>110.6</v>
       </c>
       <c r="H35" t="n">
-        <v>83.40000000000001</v>
+        <v>89</v>
       </c>
       <c r="I35" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>128.37</v>
+        <v>84.64</v>
       </c>
       <c r="K35" t="n">
-        <v>77.44</v>
+        <v>51.6</v>
       </c>
       <c r="L35" t="n">
-        <v>149.92</v>
+        <v>99.13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:25:03</t>
+          <t>08:30:16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.04</v>
+        <v>2.73</v>
       </c>
       <c r="F36" t="n">
-        <v>7.74</v>
+        <v>8.74</v>
       </c>
       <c r="G36" t="n">
-        <v>117.2</v>
+        <v>118.2</v>
       </c>
       <c r="H36" t="n">
-        <v>85.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I36" t="n">
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-82.90000000000001</v>
+        <v>114.84</v>
       </c>
       <c r="K36" t="n">
-        <v>121.01</v>
+        <v>72.86</v>
       </c>
       <c r="L36" t="n">
-        <v>146.69</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:25:55</t>
+          <t>08:32:37</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="F37" t="n">
-        <v>7.62</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>123.1</v>
+        <v>117.8</v>
       </c>
       <c r="H37" t="n">
-        <v>92</v>
+        <v>88.7</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>69.93000000000001</v>
+        <v>-106.58</v>
       </c>
       <c r="K37" t="n">
-        <v>12.04</v>
+        <v>-11.52</v>
       </c>
       <c r="L37" t="n">
-        <v>70.95999999999999</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:30:13</t>
+          <t>08:37:28</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.53</v>
+        <v>3.11</v>
       </c>
       <c r="F38" t="n">
-        <v>7.9</v>
+        <v>8.74</v>
       </c>
       <c r="G38" t="n">
-        <v>114.6</v>
+        <v>120.4</v>
       </c>
       <c r="H38" t="n">
-        <v>81.8</v>
+        <v>92.2</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>143.34</v>
+        <v>103.75</v>
       </c>
       <c r="K38" t="n">
-        <v>136.64</v>
+        <v>-122.94</v>
       </c>
       <c r="L38" t="n">
-        <v>198.03</v>
+        <v>160.87</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:32:03</t>
+          <t>08:39:55</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.58</v>
+        <v>3.13</v>
       </c>
       <c r="F39" t="n">
-        <v>8.02</v>
+        <v>8.74</v>
       </c>
       <c r="G39" t="n">
-        <v>125.4</v>
+        <v>112</v>
       </c>
       <c r="H39" t="n">
-        <v>89.7</v>
+        <v>85.5</v>
       </c>
       <c r="I39" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-31.41</v>
+        <v>-121</v>
       </c>
       <c r="K39" t="n">
-        <v>-102.22</v>
+        <v>43.14</v>
       </c>
       <c r="L39" t="n">
-        <v>106.93</v>
+        <v>128.46</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:33:13</t>
+          <t>08:41:46</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="F40" t="n">
-        <v>7.38</v>
+        <v>8.74</v>
       </c>
       <c r="G40" t="n">
-        <v>92.40000000000001</v>
+        <v>115.1</v>
       </c>
       <c r="H40" t="n">
-        <v>87.59999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>198.55</v>
+        <v>188.79</v>
       </c>
       <c r="K40" t="n">
-        <v>-0</v>
+        <v>-89.18000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>198.55</v>
+        <v>208.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:37:28</t>
+          <t>08:47:23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.94</v>
+        <v>3.45</v>
       </c>
       <c r="F41" t="n">
-        <v>7.3</v>
+        <v>8.74</v>
       </c>
       <c r="G41" t="n">
-        <v>131.1</v>
+        <v>122.9</v>
       </c>
       <c r="H41" t="n">
-        <v>83.2</v>
+        <v>84.3</v>
       </c>
       <c r="I41" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>12.58</v>
+        <v>85.47</v>
       </c>
       <c r="K41" t="n">
-        <v>-157.89</v>
+        <v>-137.3</v>
       </c>
       <c r="L41" t="n">
-        <v>158.39</v>
+        <v>161.73</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:39:24</t>
+          <t>08:49:47</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.18</v>
+        <v>3.42</v>
       </c>
       <c r="F42" t="n">
-        <v>7.43</v>
+        <v>4.79</v>
       </c>
       <c r="G42" t="n">
-        <v>114.6</v>
+        <v>113</v>
       </c>
       <c r="H42" t="n">
-        <v>85.8</v>
+        <v>79</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-100.53</v>
+        <v>60.88</v>
       </c>
       <c r="K42" t="n">
-        <v>-291.2</v>
+        <v>-162.47</v>
       </c>
       <c r="L42" t="n">
-        <v>308.06</v>
+        <v>173.51</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:42:00</t>
+          <t>08:51:54</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.49</v>
+        <v>2.8</v>
       </c>
       <c r="F43" t="n">
-        <v>7.32</v>
+        <v>8.74</v>
       </c>
       <c r="G43" t="n">
-        <v>110.7</v>
+        <v>115.6</v>
       </c>
       <c r="H43" t="n">
-        <v>86</v>
+        <v>92.8</v>
       </c>
       <c r="I43" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>165.52</v>
+        <v>-199.45</v>
       </c>
       <c r="K43" t="n">
-        <v>29.37</v>
+        <v>-16.85</v>
       </c>
       <c r="L43" t="n">
-        <v>168.1</v>
+        <v>200.16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:53:42</t>
+          <t>09:02:21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.36</v>
+        <v>3.07</v>
       </c>
       <c r="F44" t="n">
-        <v>7.65</v>
+        <v>6.91</v>
       </c>
       <c r="G44" t="n">
-        <v>106.4</v>
+        <v>113.6</v>
       </c>
       <c r="H44" t="n">
-        <v>78.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J44" t="n">
-        <v>-31.33</v>
+        <v>-70.39</v>
       </c>
       <c r="K44" t="n">
-        <v>-44.73</v>
+        <v>15.28</v>
       </c>
       <c r="L44" t="n">
-        <v>54.61</v>
+        <v>72.03</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:55:49</t>
+          <t>09:03:38</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.84</v>
+        <v>3.07</v>
       </c>
       <c r="F45" t="n">
-        <v>7.16</v>
+        <v>7.08</v>
       </c>
       <c r="G45" t="n">
-        <v>114.4</v>
+        <v>111.2</v>
       </c>
       <c r="H45" t="n">
-        <v>85.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="I45" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>32.86</v>
+        <v>29.81</v>
       </c>
       <c r="K45" t="n">
-        <v>-15.22</v>
+        <v>-70.25</v>
       </c>
       <c r="L45" t="n">
-        <v>36.21</v>
+        <v>76.31</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:56:39</t>
+          <t>09:05:46</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
       <c r="F46" t="n">
-        <v>7.35</v>
+        <v>7.7</v>
       </c>
       <c r="G46" t="n">
-        <v>111.2</v>
+        <v>114.6</v>
       </c>
       <c r="H46" t="n">
-        <v>91.8</v>
+        <v>83</v>
       </c>
       <c r="I46" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>-41.61</v>
+        <v>32.48</v>
       </c>
       <c r="K46" t="n">
-        <v>-46.41</v>
+        <v>71.42</v>
       </c>
       <c r="L46" t="n">
-        <v>62.33</v>
+        <v>78.45999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:00:55</t>
+          <t>09:11:14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="F47" t="n">
-        <v>7.85</v>
+        <v>7.21</v>
       </c>
       <c r="G47" t="n">
-        <v>98.7</v>
+        <v>112.4</v>
       </c>
       <c r="H47" t="n">
-        <v>86.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="I47" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-60.11</v>
+        <v>-65.18000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>30.14</v>
+        <v>68.02</v>
       </c>
       <c r="L47" t="n">
-        <v>67.23999999999999</v>
+        <v>94.20999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:02:34</t>
+          <t>09:12:55</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.96</v>
+        <v>2.63</v>
       </c>
       <c r="F48" t="n">
-        <v>7.27</v>
+        <v>6.79</v>
       </c>
       <c r="G48" t="n">
-        <v>112.4</v>
+        <v>114.4</v>
       </c>
       <c r="H48" t="n">
-        <v>85.5</v>
+        <v>86.2</v>
       </c>
       <c r="I48" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>48.61</v>
+        <v>-32.71</v>
       </c>
       <c r="K48" t="n">
-        <v>-72.62</v>
+        <v>65.84</v>
       </c>
       <c r="L48" t="n">
-        <v>87.39</v>
+        <v>73.52</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:04:02</t>
+          <t>09:15:08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.01</v>
+        <v>3.53</v>
       </c>
       <c r="F49" t="n">
-        <v>7.86</v>
+        <v>6.29</v>
       </c>
       <c r="G49" t="n">
-        <v>111.8</v>
+        <v>118</v>
       </c>
       <c r="H49" t="n">
-        <v>89.2</v>
+        <v>85.5</v>
       </c>
       <c r="I49" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.1</v>
+        <v>46.93</v>
       </c>
       <c r="K49" t="n">
-        <v>-88.48999999999999</v>
+        <v>-53.98</v>
       </c>
       <c r="L49" t="n">
-        <v>88.64</v>
+        <v>71.53</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:10:02</t>
+          <t>09:20:21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="F50" t="n">
-        <v>7.73</v>
+        <v>8.74</v>
       </c>
       <c r="G50" t="n">
-        <v>98.8</v>
+        <v>114.9</v>
       </c>
       <c r="H50" t="n">
-        <v>88.09999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="I50" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>83.28</v>
+        <v>-21.53</v>
       </c>
       <c r="K50" t="n">
-        <v>-50.38</v>
+        <v>185.38</v>
       </c>
       <c r="L50" t="n">
-        <v>97.34</v>
+        <v>186.63</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:11:33</t>
+          <t>09:22:24</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="F51" t="n">
-        <v>8.69</v>
+        <v>5.86</v>
       </c>
       <c r="G51" t="n">
-        <v>110.9</v>
+        <v>108.9</v>
       </c>
       <c r="H51" t="n">
-        <v>82.59999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-23.03</v>
+        <v>95.86</v>
       </c>
       <c r="K51" t="n">
-        <v>-90.65000000000001</v>
+        <v>-72.84</v>
       </c>
       <c r="L51" t="n">
-        <v>93.53</v>
+        <v>120.39</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:12:51</t>
+          <t>09:23:33</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.97</v>
+        <v>3.27</v>
       </c>
       <c r="F52" t="n">
-        <v>8.06</v>
+        <v>6.89</v>
       </c>
       <c r="G52" t="n">
-        <v>127.4</v>
+        <v>104.8</v>
       </c>
       <c r="H52" t="n">
         <v>83.59999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>76.27</v>
+        <v>-59.14</v>
       </c>
       <c r="K52" t="n">
-        <v>-45.73</v>
+        <v>107.27</v>
       </c>
       <c r="L52" t="n">
-        <v>88.93000000000001</v>
+        <v>122.49</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:17:44</t>
+          <t>09:27:57</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.76</v>
+        <v>3.12</v>
       </c>
       <c r="F53" t="n">
-        <v>8.119999999999999</v>
+        <v>7.65</v>
       </c>
       <c r="G53" t="n">
-        <v>107.8</v>
+        <v>110.8</v>
       </c>
       <c r="H53" t="n">
-        <v>90.3</v>
+        <v>86.5</v>
       </c>
       <c r="I53" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>-53.33</v>
+        <v>110.02</v>
       </c>
       <c r="K53" t="n">
-        <v>-92.78</v>
+        <v>-136.48</v>
       </c>
       <c r="L53" t="n">
-        <v>107.01</v>
+        <v>175.3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:18:36</t>
+          <t>09:29:12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.49</v>
+        <v>3.09</v>
       </c>
       <c r="F54" t="n">
-        <v>7.83</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>121.6</v>
+        <v>118.4</v>
       </c>
       <c r="H54" t="n">
-        <v>84.5</v>
+        <v>87.8</v>
       </c>
       <c r="I54" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>11.24</v>
+        <v>-132.84</v>
       </c>
       <c r="K54" t="n">
-        <v>-183.32</v>
+        <v>27.49</v>
       </c>
       <c r="L54" t="n">
-        <v>183.66</v>
+        <v>135.66</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:19:37</t>
+          <t>09:30:31</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="F55" t="n">
-        <v>7.7</v>
+        <v>8.33</v>
       </c>
       <c r="G55" t="n">
-        <v>108.9</v>
+        <v>116.2</v>
       </c>
       <c r="H55" t="n">
-        <v>82.5</v>
+        <v>87</v>
       </c>
       <c r="I55" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>34.62</v>
+        <v>33.64</v>
       </c>
       <c r="K55" t="n">
-        <v>-103.65</v>
+        <v>-165.34</v>
       </c>
       <c r="L55" t="n">
-        <v>109.28</v>
+        <v>168.73</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:23:22</t>
+          <t>09:33:40</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.18</v>
+        <v>3.07</v>
       </c>
       <c r="F56" t="n">
-        <v>7.23</v>
+        <v>8.74</v>
       </c>
       <c r="G56" t="n">
-        <v>114</v>
+        <v>127.9</v>
       </c>
       <c r="H56" t="n">
-        <v>89.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>180.29</v>
+        <v>53.02</v>
       </c>
       <c r="K56" t="n">
-        <v>250.85</v>
+        <v>229.41</v>
       </c>
       <c r="L56" t="n">
-        <v>308.91</v>
+        <v>235.45</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:24:55</t>
+          <t>09:35:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.78</v>
+        <v>3.01</v>
       </c>
       <c r="F57" t="n">
-        <v>7.44</v>
+        <v>7.17</v>
       </c>
       <c r="G57" t="n">
-        <v>128.4</v>
+        <v>109.3</v>
       </c>
       <c r="H57" t="n">
-        <v>86.59999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="I57" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>-133.06</v>
+        <v>-132.07</v>
       </c>
       <c r="K57" t="n">
-        <v>-11.71</v>
+        <v>130.78</v>
       </c>
       <c r="L57" t="n">
-        <v>133.57</v>
+        <v>185.86</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:27:07</t>
+          <t>09:36:14</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="F58" t="n">
-        <v>7.8</v>
+        <v>7.22</v>
       </c>
       <c r="G58" t="n">
-        <v>108.8</v>
+        <v>134.2</v>
       </c>
       <c r="H58" t="n">
-        <v>92.3</v>
+        <v>88.8</v>
       </c>
       <c r="I58" t="n">
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>193.09</v>
+        <v>-84.81</v>
       </c>
       <c r="K58" t="n">
-        <v>-118.56</v>
+        <v>249.4</v>
       </c>
       <c r="L58" t="n">
-        <v>226.58</v>
+        <v>263.42</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:35:01</t>
+          <t>09:47:24</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.25</v>
+        <v>3.61</v>
       </c>
       <c r="F59" t="n">
-        <v>7.55</v>
+        <v>8.74</v>
       </c>
       <c r="G59" t="n">
-        <v>131.5</v>
+        <v>103</v>
       </c>
       <c r="H59" t="n">
-        <v>82.90000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-14.74</v>
+        <v>-73.53</v>
       </c>
       <c r="K59" t="n">
-        <v>76.84999999999999</v>
+        <v>-9.76</v>
       </c>
       <c r="L59" t="n">
-        <v>78.25</v>
+        <v>74.17</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:36:14</t>
+          <t>09:49:01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.72</v>
+        <v>2.97</v>
       </c>
       <c r="F60" t="n">
-        <v>7.17</v>
+        <v>6.68</v>
       </c>
       <c r="G60" t="n">
-        <v>102.3</v>
+        <v>107.3</v>
       </c>
       <c r="H60" t="n">
-        <v>80.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-33.72</v>
+        <v>-21.86</v>
       </c>
       <c r="K60" t="n">
-        <v>-37.76</v>
+        <v>-97.61</v>
       </c>
       <c r="L60" t="n">
-        <v>50.63</v>
+        <v>100.03</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:37:55</t>
+          <t>09:50:52</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.89</v>
+        <v>3.14</v>
       </c>
       <c r="F61" t="n">
-        <v>6.53</v>
+        <v>8.17</v>
       </c>
       <c r="G61" t="n">
-        <v>109.7</v>
+        <v>103.8</v>
       </c>
       <c r="H61" t="n">
-        <v>87.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="I61" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>47.95</v>
+        <v>1.18</v>
       </c>
       <c r="K61" t="n">
-        <v>-17.82</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>51.15</v>
+        <v>72.58</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:43:42</t>
+          <t>09:55:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.83</v>
+        <v>3.3</v>
       </c>
       <c r="F62" t="n">
-        <v>7.59</v>
+        <v>8.74</v>
       </c>
       <c r="G62" t="n">
-        <v>112.2</v>
+        <v>127.4</v>
       </c>
       <c r="H62" t="n">
-        <v>81</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J62" t="n">
-        <v>53.35</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>19.7</v>
+        <v>-53.52</v>
       </c>
       <c r="L62" t="n">
-        <v>56.87</v>
+        <v>104.41</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:44:44</t>
+          <t>09:55:56</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.36</v>
+        <v>3.26</v>
       </c>
       <c r="F63" t="n">
-        <v>7.26</v>
+        <v>8.74</v>
       </c>
       <c r="G63" t="n">
-        <v>126.2</v>
+        <v>103</v>
       </c>
       <c r="H63" t="n">
-        <v>74.2</v>
+        <v>90</v>
       </c>
       <c r="I63" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>84.59999999999999</v>
+        <v>61.26</v>
       </c>
       <c r="K63" t="n">
-        <v>30.63</v>
+        <v>-37.72</v>
       </c>
       <c r="L63" t="n">
-        <v>89.98</v>
+        <v>71.94</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:46:51</t>
+          <t>09:58:18</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.23</v>
+        <v>3.09</v>
       </c>
       <c r="F64" t="n">
-        <v>7.71</v>
+        <v>8.74</v>
       </c>
       <c r="G64" t="n">
-        <v>104.2</v>
+        <v>118.3</v>
       </c>
       <c r="H64" t="n">
-        <v>80.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="I64" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-15.65</v>
+        <v>-92.88</v>
       </c>
       <c r="K64" t="n">
-        <v>70.09999999999999</v>
+        <v>-56.78</v>
       </c>
       <c r="L64" t="n">
-        <v>71.81999999999999</v>
+        <v>108.86</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:51:21</t>
+          <t>10:04:17</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.43</v>
+        <v>3.17</v>
       </c>
       <c r="F65" t="n">
-        <v>7.24</v>
+        <v>8.74</v>
       </c>
       <c r="G65" t="n">
-        <v>102.1</v>
+        <v>119.2</v>
       </c>
       <c r="H65" t="n">
-        <v>80.2</v>
+        <v>91</v>
       </c>
       <c r="I65" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-71.39</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>54.25</v>
+        <v>-86.56</v>
       </c>
       <c r="L65" t="n">
-        <v>89.67</v>
+        <v>129.89</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:53:02</t>
+          <t>10:05:43</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.15</v>
+        <v>3.29</v>
       </c>
       <c r="F66" t="n">
-        <v>7.96</v>
+        <v>8.74</v>
       </c>
       <c r="G66" t="n">
-        <v>106.5</v>
+        <v>109.3</v>
       </c>
       <c r="H66" t="n">
-        <v>88.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>59.64</v>
+        <v>202.88</v>
       </c>
       <c r="K66" t="n">
-        <v>-63.14</v>
+        <v>-77.84999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>86.84999999999999</v>
+        <v>217.31</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:55:33</t>
+          <t>10:07:39</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.48</v>
+        <v>3.02</v>
       </c>
       <c r="F67" t="n">
-        <v>7.1</v>
+        <v>6.54</v>
       </c>
       <c r="G67" t="n">
-        <v>141</v>
+        <v>118.6</v>
       </c>
       <c r="H67" t="n">
-        <v>85</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>-51.88</v>
+        <v>-39.76</v>
       </c>
       <c r="K67" t="n">
-        <v>-103.02</v>
+        <v>-104.96</v>
       </c>
       <c r="L67" t="n">
-        <v>115.35</v>
+        <v>112.24</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:00:34</t>
+          <t>10:11:18</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2896,31 +2896,31 @@
         <v>2.92</v>
       </c>
       <c r="F68" t="n">
-        <v>7.4</v>
+        <v>6.89</v>
       </c>
       <c r="G68" t="n">
-        <v>102.1</v>
+        <v>121.8</v>
       </c>
       <c r="H68" t="n">
-        <v>88.40000000000001</v>
+        <v>81</v>
       </c>
       <c r="I68" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-117.5</v>
+        <v>67.95</v>
       </c>
       <c r="K68" t="n">
-        <v>107.37</v>
+        <v>-150.75</v>
       </c>
       <c r="L68" t="n">
-        <v>159.17</v>
+        <v>165.36</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:01:42</t>
+          <t>10:12:08</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.99</v>
+        <v>3.14</v>
       </c>
       <c r="F69" t="n">
-        <v>7.22</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>116.7</v>
+        <v>114.8</v>
       </c>
       <c r="H69" t="n">
-        <v>91.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>134.41</v>
+        <v>159.33</v>
       </c>
       <c r="K69" t="n">
-        <v>-36.82</v>
+        <v>38.25</v>
       </c>
       <c r="L69" t="n">
-        <v>139.36</v>
+        <v>163.85</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:03:38</t>
+          <t>10:14:33</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.02</v>
+        <v>2.76</v>
       </c>
       <c r="F70" t="n">
-        <v>7.6</v>
+        <v>7.14</v>
       </c>
       <c r="G70" t="n">
-        <v>114.6</v>
+        <v>124.1</v>
       </c>
       <c r="H70" t="n">
-        <v>89.40000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>120.52</v>
+        <v>11.5</v>
       </c>
       <c r="K70" t="n">
-        <v>50.63</v>
+        <v>171.1</v>
       </c>
       <c r="L70" t="n">
-        <v>130.73</v>
+        <v>171.49</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:08:54</t>
+          <t>10:19:18</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="F71" t="n">
-        <v>7.91</v>
+        <v>6.23</v>
       </c>
       <c r="G71" t="n">
-        <v>124.1</v>
+        <v>127.1</v>
       </c>
       <c r="H71" t="n">
-        <v>90.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>202.36</v>
+        <v>146.49</v>
       </c>
       <c r="K71" t="n">
-        <v>-102.45</v>
+        <v>86.47</v>
       </c>
       <c r="L71" t="n">
-        <v>226.82</v>
+        <v>170.1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:10:36</t>
+          <t>10:20:21</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="F72" t="n">
-        <v>8.220000000000001</v>
+        <v>7.35</v>
       </c>
       <c r="G72" t="n">
-        <v>107.9</v>
+        <v>118.3</v>
       </c>
       <c r="H72" t="n">
-        <v>85.09999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="I72" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>67.51000000000001</v>
+        <v>193.61</v>
       </c>
       <c r="K72" t="n">
-        <v>135.3</v>
+        <v>-117.13</v>
       </c>
       <c r="L72" t="n">
-        <v>151.2</v>
+        <v>226.28</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:11:58</t>
+          <t>10:22:12</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="F73" t="n">
-        <v>7.44</v>
+        <v>7.26</v>
       </c>
       <c r="G73" t="n">
-        <v>118.3</v>
+        <v>110.2</v>
       </c>
       <c r="H73" t="n">
-        <v>89.5</v>
+        <v>78.5</v>
       </c>
       <c r="I73" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>-55.29</v>
+        <v>188.92</v>
       </c>
       <c r="K73" t="n">
-        <v>-198.31</v>
+        <v>-78.08</v>
       </c>
       <c r="L73" t="n">
-        <v>205.88</v>
+        <v>204.42</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:19:37</t>
+          <t>10:30:57</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="F74" t="n">
-        <v>7.37</v>
+        <v>6.93</v>
       </c>
       <c r="G74" t="n">
-        <v>98.8</v>
+        <v>116.6</v>
       </c>
       <c r="H74" t="n">
-        <v>90.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="I74" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>43.46</v>
+        <v>-2.62</v>
       </c>
       <c r="K74" t="n">
-        <v>-18.85</v>
+        <v>-55.38</v>
       </c>
       <c r="L74" t="n">
-        <v>47.38</v>
+        <v>55.44</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:21:28</t>
+          <t>10:31:53</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.29</v>
+        <v>2.92</v>
       </c>
       <c r="F75" t="n">
-        <v>7.8</v>
+        <v>8.74</v>
       </c>
       <c r="G75" t="n">
-        <v>116.6</v>
+        <v>115.8</v>
       </c>
       <c r="H75" t="n">
-        <v>85</v>
+        <v>82.2</v>
       </c>
       <c r="I75" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>-26.58</v>
+        <v>3.02</v>
       </c>
       <c r="K75" t="n">
-        <v>-67.45</v>
+        <v>108.59</v>
       </c>
       <c r="L75" t="n">
-        <v>72.5</v>
+        <v>108.63</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:22:59</t>
+          <t>10:34:47</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.41</v>
+        <v>3.47</v>
       </c>
       <c r="F76" t="n">
-        <v>7.65</v>
+        <v>8.74</v>
       </c>
       <c r="G76" t="n">
-        <v>106.2</v>
+        <v>115.8</v>
       </c>
       <c r="H76" t="n">
-        <v>90.40000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>2.43</v>
+        <v>15.51</v>
       </c>
       <c r="K76" t="n">
-        <v>99.62</v>
+        <v>-91.06999999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>99.65000000000001</v>
+        <v>92.38</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:27:27</t>
+          <t>10:38:16</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.46</v>
+        <v>2.85</v>
       </c>
       <c r="F77" t="n">
-        <v>6.99</v>
+        <v>7.43</v>
       </c>
       <c r="G77" t="n">
-        <v>115.8</v>
+        <v>98</v>
       </c>
       <c r="H77" t="n">
-        <v>85.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>-87.48</v>
+        <v>116.5</v>
       </c>
       <c r="K77" t="n">
-        <v>-71.15000000000001</v>
+        <v>-59.99</v>
       </c>
       <c r="L77" t="n">
-        <v>112.76</v>
+        <v>131.04</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:28:41</t>
+          <t>10:39:58</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="F78" t="n">
-        <v>6.76</v>
+        <v>8.74</v>
       </c>
       <c r="G78" t="n">
-        <v>108.3</v>
+        <v>107.6</v>
       </c>
       <c r="H78" t="n">
-        <v>92.2</v>
+        <v>83.5</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>114.49</v>
+        <v>83.59</v>
       </c>
       <c r="K78" t="n">
-        <v>-59.73</v>
+        <v>10</v>
       </c>
       <c r="L78" t="n">
-        <v>129.13</v>
+        <v>84.18000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:30:43</t>
+          <t>10:41:08</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.67</v>
+        <v>3.44</v>
       </c>
       <c r="F79" t="n">
-        <v>7.83</v>
+        <v>8.74</v>
       </c>
       <c r="G79" t="n">
-        <v>107.6</v>
+        <v>107.1</v>
       </c>
       <c r="H79" t="n">
-        <v>83.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>21.04</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>63.82</v>
+        <v>7.96</v>
       </c>
       <c r="L79" t="n">
-        <v>67.2</v>
+        <v>79.05</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:35:13</t>
+          <t>10:45:16</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="F80" t="n">
-        <v>7.21</v>
+        <v>8.74</v>
       </c>
       <c r="G80" t="n">
-        <v>131.1</v>
+        <v>114.1</v>
       </c>
       <c r="H80" t="n">
-        <v>87.5</v>
+        <v>83</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>101.02</v>
+        <v>-53.38</v>
       </c>
       <c r="K80" t="n">
-        <v>8.140000000000001</v>
+        <v>86.36</v>
       </c>
       <c r="L80" t="n">
-        <v>101.35</v>
+        <v>101.52</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:37:32</t>
+          <t>10:47:18</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.38</v>
+        <v>3.01</v>
       </c>
       <c r="F81" t="n">
-        <v>7.52</v>
+        <v>7.57</v>
       </c>
       <c r="G81" t="n">
-        <v>114.1</v>
+        <v>108</v>
       </c>
       <c r="H81" t="n">
-        <v>83</v>
+        <v>88.5</v>
       </c>
       <c r="I81" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>56.22</v>
+        <v>10.67</v>
       </c>
       <c r="K81" t="n">
-        <v>-87.23999999999999</v>
+        <v>83.88</v>
       </c>
       <c r="L81" t="n">
-        <v>103.78</v>
+        <v>84.55</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:38:39</t>
+          <t>10:48:29</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.74</v>
+        <v>3.49</v>
       </c>
       <c r="F82" t="n">
-        <v>7.26</v>
+        <v>8.74</v>
       </c>
       <c r="G82" t="n">
-        <v>118.9</v>
+        <v>119.1</v>
       </c>
       <c r="H82" t="n">
-        <v>95.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-13.4</v>
+        <v>32.55</v>
       </c>
       <c r="K82" t="n">
-        <v>63.37</v>
+        <v>-94.92</v>
       </c>
       <c r="L82" t="n">
-        <v>64.77</v>
+        <v>100.35</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:42:35</t>
+          <t>10:52:54</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.48</v>
+        <v>2.98</v>
       </c>
       <c r="F83" t="n">
-        <v>7.68</v>
+        <v>8.74</v>
       </c>
       <c r="G83" t="n">
-        <v>119.1</v>
+        <v>107.7</v>
       </c>
       <c r="H83" t="n">
-        <v>92.40000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="I83" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-47.6</v>
+        <v>-145.21</v>
       </c>
       <c r="K83" t="n">
-        <v>-137.25</v>
+        <v>-50.66</v>
       </c>
       <c r="L83" t="n">
-        <v>145.27</v>
+        <v>153.8</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:44:51</t>
+          <t>10:54:01</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.43</v>
+        <v>3.52</v>
       </c>
       <c r="F84" t="n">
-        <v>7.25</v>
+        <v>8.74</v>
       </c>
       <c r="G84" t="n">
-        <v>119.3</v>
+        <v>124.5</v>
       </c>
       <c r="H84" t="n">
-        <v>88.2</v>
+        <v>89.3</v>
       </c>
       <c r="I84" t="n">
         <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-145.64</v>
+        <v>-26.76</v>
       </c>
       <c r="K84" t="n">
-        <v>-38.73</v>
+        <v>-145.26</v>
       </c>
       <c r="L84" t="n">
-        <v>150.7</v>
+        <v>147.71</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:46:37</t>
+          <t>10:56:08</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.51</v>
+        <v>3.08</v>
       </c>
       <c r="F85" t="n">
-        <v>6.94</v>
+        <v>5.65</v>
       </c>
       <c r="G85" t="n">
-        <v>124.5</v>
+        <v>106.5</v>
       </c>
       <c r="H85" t="n">
-        <v>89.3</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>-80.43000000000001</v>
+        <v>112.81</v>
       </c>
       <c r="K85" t="n">
-        <v>-121.01</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>145.3</v>
+        <v>113.24</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:51:39</t>
+          <t>11:00:58</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.19</v>
+        <v>2.9</v>
       </c>
       <c r="F86" t="n">
-        <v>7.18</v>
+        <v>8.74</v>
       </c>
       <c r="G86" t="n">
-        <v>115.1</v>
+        <v>128.2</v>
       </c>
       <c r="H86" t="n">
-        <v>85</v>
+        <v>83.5</v>
       </c>
       <c r="I86" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>57.6</v>
+        <v>154.46</v>
       </c>
       <c r="K86" t="n">
-        <v>18.94</v>
+        <v>107.57</v>
       </c>
       <c r="L86" t="n">
-        <v>60.63</v>
+        <v>188.23</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:52:56</t>
+          <t>11:03:11</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="F87" t="n">
-        <v>7.78</v>
+        <v>8.74</v>
       </c>
       <c r="G87" t="n">
-        <v>128.2</v>
+        <v>119.6</v>
       </c>
       <c r="H87" t="n">
-        <v>83.5</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>115.91</v>
+        <v>162.83</v>
       </c>
       <c r="K87" t="n">
-        <v>-163.47</v>
+        <v>-59.62</v>
       </c>
       <c r="L87" t="n">
-        <v>200.39</v>
+        <v>173.41</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:53:47</t>
+          <t>11:05:06</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="F88" t="n">
-        <v>7.84</v>
+        <v>8.74</v>
       </c>
       <c r="G88" t="n">
-        <v>112</v>
+        <v>125.1</v>
       </c>
       <c r="H88" t="n">
-        <v>83.3</v>
+        <v>87.7</v>
       </c>
       <c r="I88" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>56.35</v>
+        <v>-72.67</v>
       </c>
       <c r="K88" t="n">
-        <v>1.2</v>
+        <v>-208.84</v>
       </c>
       <c r="L88" t="n">
-        <v>56.36</v>
+        <v>221.12</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-03.xlsx
+++ b/output/2025-10-03.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>10.06</v>
+        <v>10.8</v>
       </c>
       <c r="K14" t="n">
-        <v>-42.38</v>
+        <v>-45.52</v>
       </c>
       <c r="L14" t="n">
-        <v>43.55</v>
+        <v>46.78</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-25.38</v>
+        <v>-25.83</v>
       </c>
       <c r="K15" t="n">
-        <v>18.45</v>
+        <v>18.78</v>
       </c>
       <c r="L15" t="n">
-        <v>31.38</v>
+        <v>31.94</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>-56.39</v>
+        <v>-59.59</v>
       </c>
       <c r="K16" t="n">
-        <v>48</v>
+        <v>50.71</v>
       </c>
       <c r="L16" t="n">
-        <v>74.05</v>
+        <v>78.25</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>27.19</v>
+        <v>28.24</v>
       </c>
       <c r="K17" t="n">
-        <v>63.05</v>
+        <v>65.48</v>
       </c>
       <c r="L17" t="n">
-        <v>68.67</v>
+        <v>71.31</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>49.91</v>
+        <v>53.61</v>
       </c>
       <c r="K18" t="n">
-        <v>-30.86</v>
+        <v>-33.14</v>
       </c>
       <c r="L18" t="n">
-        <v>58.68</v>
+        <v>63.03</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-42.69</v>
+        <v>-45.85</v>
       </c>
       <c r="K19" t="n">
-        <v>34.14</v>
+        <v>36.66</v>
       </c>
       <c r="L19" t="n">
-        <v>54.66</v>
+        <v>58.71</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>-94.91</v>
+        <v>-100.28</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.4</v>
+        <v>-4.65</v>
       </c>
       <c r="L20" t="n">
-        <v>95.01000000000001</v>
+        <v>100.39</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>16.85</v>
+        <v>18.66</v>
       </c>
       <c r="K21" t="n">
-        <v>-34.04</v>
+        <v>-37.69</v>
       </c>
       <c r="L21" t="n">
-        <v>37.99</v>
+        <v>42.06</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-131.34</v>
+        <v>-145.41</v>
       </c>
       <c r="K22" t="n">
-        <v>22.52</v>
+        <v>24.93</v>
       </c>
       <c r="L22" t="n">
-        <v>133.25</v>
+        <v>147.53</v>
       </c>
     </row>
     <row r="23">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-39.95</v>
+        <v>-42.21</v>
       </c>
       <c r="K24" t="n">
-        <v>137.26</v>
+        <v>145.03</v>
       </c>
       <c r="L24" t="n">
-        <v>142.95</v>
+        <v>151.04</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>-178.99</v>
+        <v>-198.17</v>
       </c>
       <c r="K25" t="n">
-        <v>73.01000000000001</v>
+        <v>80.83</v>
       </c>
       <c r="L25" t="n">
-        <v>193.31</v>
+        <v>214.02</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>189.4</v>
+        <v>206.62</v>
       </c>
       <c r="K26" t="n">
-        <v>-122.94</v>
+        <v>-134.12</v>
       </c>
       <c r="L26" t="n">
-        <v>225.81</v>
+        <v>246.33</v>
       </c>
     </row>
     <row r="27">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-125.21</v>
+        <v>-134.49</v>
       </c>
       <c r="K28" t="n">
-        <v>-165.25</v>
+        <v>-177.5</v>
       </c>
       <c r="L28" t="n">
-        <v>207.33</v>
+        <v>222.69</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-34.79</v>
+        <v>-37.35</v>
       </c>
       <c r="K29" t="n">
-        <v>-50.8</v>
+        <v>-54.54</v>
       </c>
       <c r="L29" t="n">
-        <v>61.57</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>-33.1</v>
+        <v>-34.98</v>
       </c>
       <c r="K30" t="n">
-        <v>43.08</v>
+        <v>45.52</v>
       </c>
       <c r="L30" t="n">
-        <v>54.33</v>
+        <v>57.41</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-51.49</v>
+        <v>-54.4</v>
       </c>
       <c r="K31" t="n">
-        <v>24.7</v>
+        <v>26.1</v>
       </c>
       <c r="L31" t="n">
-        <v>57.1</v>
+        <v>60.34</v>
       </c>
     </row>
     <row r="32">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-12.84</v>
+        <v>-13.33</v>
       </c>
       <c r="K33" t="n">
-        <v>-56.85</v>
+        <v>-59.03</v>
       </c>
       <c r="L33" t="n">
-        <v>58.28</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-33.88</v>
+        <v>-34.54</v>
       </c>
       <c r="K34" t="n">
-        <v>-90.88</v>
+        <v>-92.66</v>
       </c>
       <c r="L34" t="n">
-        <v>96.98999999999999</v>
+        <v>98.89</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>84.64</v>
+        <v>92.34</v>
       </c>
       <c r="K35" t="n">
-        <v>51.6</v>
+        <v>56.29</v>
       </c>
       <c r="L35" t="n">
-        <v>99.13</v>
+        <v>108.14</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>114.84</v>
+        <v>119.26</v>
       </c>
       <c r="K36" t="n">
-        <v>72.86</v>
+        <v>75.66</v>
       </c>
       <c r="L36" t="n">
-        <v>136</v>
+        <v>141.23</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-106.58</v>
+        <v>-110.68</v>
       </c>
       <c r="K37" t="n">
-        <v>-11.52</v>
+        <v>-11.97</v>
       </c>
       <c r="L37" t="n">
-        <v>107.2</v>
+        <v>111.33</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>103.75</v>
+        <v>113.18</v>
       </c>
       <c r="K38" t="n">
-        <v>-122.94</v>
+        <v>-134.12</v>
       </c>
       <c r="L38" t="n">
-        <v>160.87</v>
+        <v>175.49</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-121</v>
+        <v>-127.85</v>
       </c>
       <c r="K39" t="n">
-        <v>43.14</v>
+        <v>45.58</v>
       </c>
       <c r="L39" t="n">
-        <v>128.46</v>
+        <v>135.73</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>188.79</v>
+        <v>196.05</v>
       </c>
       <c r="K40" t="n">
-        <v>-89.18000000000001</v>
+        <v>-92.61</v>
       </c>
       <c r="L40" t="n">
-        <v>208.8</v>
+        <v>216.83</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>85.47</v>
+        <v>88.92</v>
       </c>
       <c r="K41" t="n">
-        <v>-137.3</v>
+        <v>-142.82</v>
       </c>
       <c r="L41" t="n">
-        <v>161.73</v>
+        <v>168.24</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>60.88</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>-162.47</v>
+        <v>-171.92</v>
       </c>
       <c r="L42" t="n">
-        <v>173.51</v>
+        <v>183.6</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>-199.45</v>
+        <v>-220.81</v>
       </c>
       <c r="K43" t="n">
-        <v>-16.85</v>
+        <v>-18.65</v>
       </c>
       <c r="L43" t="n">
-        <v>200.16</v>
+        <v>221.6</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>18</v>
       </c>
       <c r="J44" t="n">
-        <v>-70.39</v>
+        <v>-77.93000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>15.28</v>
+        <v>16.91</v>
       </c>
       <c r="L44" t="n">
-        <v>72.03</v>
+        <v>79.73999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>29.81</v>
+        <v>32.52</v>
       </c>
       <c r="K45" t="n">
-        <v>-70.25</v>
+        <v>-76.64</v>
       </c>
       <c r="L45" t="n">
-        <v>76.31</v>
+        <v>83.25</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>32.48</v>
+        <v>35.43</v>
       </c>
       <c r="K46" t="n">
-        <v>71.42</v>
+        <v>77.91</v>
       </c>
       <c r="L46" t="n">
-        <v>78.45999999999999</v>
+        <v>85.59</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-65.18000000000001</v>
+        <v>-71.09999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>68.02</v>
+        <v>74.2</v>
       </c>
       <c r="L47" t="n">
-        <v>94.20999999999999</v>
+        <v>102.77</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-32.71</v>
+        <v>-36.21</v>
       </c>
       <c r="K48" t="n">
-        <v>65.84</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>73.52</v>
+        <v>81.39</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>46.93</v>
+        <v>51.13</v>
       </c>
       <c r="K49" t="n">
-        <v>-53.98</v>
+        <v>-58.81</v>
       </c>
       <c r="L49" t="n">
-        <v>71.53</v>
+        <v>77.92</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>18</v>
       </c>
       <c r="J50" t="n">
-        <v>-21.53</v>
+        <v>-23.84</v>
       </c>
       <c r="K50" t="n">
-        <v>185.38</v>
+        <v>205.24</v>
       </c>
       <c r="L50" t="n">
-        <v>186.63</v>
+        <v>206.62</v>
       </c>
     </row>
     <row r="51">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-59.14</v>
+        <v>-61.41</v>
       </c>
       <c r="K52" t="n">
-        <v>107.27</v>
+        <v>111.39</v>
       </c>
       <c r="L52" t="n">
-        <v>122.49</v>
+        <v>127.2</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>110.02</v>
+        <v>114.25</v>
       </c>
       <c r="K53" t="n">
-        <v>-136.48</v>
+        <v>-141.73</v>
       </c>
       <c r="L53" t="n">
-        <v>175.3</v>
+        <v>182.04</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-132.84</v>
+        <v>-142.68</v>
       </c>
       <c r="K54" t="n">
-        <v>27.49</v>
+        <v>29.52</v>
       </c>
       <c r="L54" t="n">
-        <v>135.66</v>
+        <v>145.7</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>33.64</v>
+        <v>35.55</v>
       </c>
       <c r="K55" t="n">
-        <v>-165.34</v>
+        <v>-174.74</v>
       </c>
       <c r="L55" t="n">
-        <v>168.73</v>
+        <v>178.31</v>
       </c>
     </row>
     <row r="56">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>-132.07</v>
+        <v>-146.22</v>
       </c>
       <c r="K57" t="n">
-        <v>130.78</v>
+        <v>144.79</v>
       </c>
       <c r="L57" t="n">
-        <v>185.86</v>
+        <v>205.78</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-84.81</v>
+        <v>-88.06999999999999</v>
       </c>
       <c r="K58" t="n">
-        <v>249.4</v>
+        <v>258.99</v>
       </c>
       <c r="L58" t="n">
-        <v>263.42</v>
+        <v>273.55</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-73.53</v>
+        <v>-78.84</v>
       </c>
       <c r="K59" t="n">
-        <v>-9.76</v>
+        <v>-10.47</v>
       </c>
       <c r="L59" t="n">
-        <v>74.17</v>
+        <v>79.53</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-21.86</v>
+        <v>-23.1</v>
       </c>
       <c r="K60" t="n">
-        <v>-97.61</v>
+        <v>-103.14</v>
       </c>
       <c r="L60" t="n">
-        <v>100.03</v>
+        <v>105.69</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="K61" t="n">
-        <v>72.56999999999999</v>
+        <v>77.95</v>
       </c>
       <c r="L61" t="n">
-        <v>72.58</v>
+        <v>77.95999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>20</v>
       </c>
       <c r="J62" t="n">
-        <v>89.65000000000001</v>
+        <v>96.27</v>
       </c>
       <c r="K62" t="n">
-        <v>-53.52</v>
+        <v>-57.46</v>
       </c>
       <c r="L62" t="n">
-        <v>104.41</v>
+        <v>112.12</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>61.26</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-37.72</v>
+        <v>-41.76</v>
       </c>
       <c r="L63" t="n">
-        <v>71.94</v>
+        <v>79.65000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-92.88</v>
+        <v>-102.83</v>
       </c>
       <c r="K64" t="n">
-        <v>-56.78</v>
+        <v>-62.86</v>
       </c>
       <c r="L64" t="n">
-        <v>108.86</v>
+        <v>120.52</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>96.84999999999999</v>
+        <v>100.57</v>
       </c>
       <c r="K65" t="n">
-        <v>-86.56</v>
+        <v>-89.89</v>
       </c>
       <c r="L65" t="n">
-        <v>129.89</v>
+        <v>134.89</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>202.88</v>
+        <v>214.35</v>
       </c>
       <c r="K66" t="n">
-        <v>-77.84999999999999</v>
+        <v>-82.25</v>
       </c>
       <c r="L66" t="n">
-        <v>217.31</v>
+        <v>229.59</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>-39.76</v>
+        <v>-44.02</v>
       </c>
       <c r="K67" t="n">
-        <v>-104.96</v>
+        <v>-116.21</v>
       </c>
       <c r="L67" t="n">
-        <v>112.24</v>
+        <v>124.27</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>67.95</v>
+        <v>74.12</v>
       </c>
       <c r="K68" t="n">
-        <v>-150.75</v>
+        <v>-164.46</v>
       </c>
       <c r="L68" t="n">
-        <v>165.36</v>
+        <v>180.39</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>159.33</v>
+        <v>171.13</v>
       </c>
       <c r="K69" t="n">
-        <v>38.25</v>
+        <v>41.09</v>
       </c>
       <c r="L69" t="n">
-        <v>163.85</v>
+        <v>175.99</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>11.5</v>
+        <v>12.54</v>
       </c>
       <c r="K70" t="n">
-        <v>171.1</v>
+        <v>186.65</v>
       </c>
       <c r="L70" t="n">
-        <v>171.49</v>
+        <v>187.08</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>146.49</v>
+        <v>159.81</v>
       </c>
       <c r="K71" t="n">
-        <v>86.47</v>
+        <v>94.33</v>
       </c>
       <c r="L71" t="n">
-        <v>170.1</v>
+        <v>185.57</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>193.61</v>
+        <v>204.56</v>
       </c>
       <c r="K72" t="n">
-        <v>-117.13</v>
+        <v>-123.76</v>
       </c>
       <c r="L72" t="n">
-        <v>226.28</v>
+        <v>239.09</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>188.92</v>
+        <v>202.92</v>
       </c>
       <c r="K73" t="n">
-        <v>-78.08</v>
+        <v>-83.86</v>
       </c>
       <c r="L73" t="n">
-        <v>204.42</v>
+        <v>219.57</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-2.62</v>
+        <v>-2.77</v>
       </c>
       <c r="K74" t="n">
-        <v>-55.38</v>
+        <v>-58.5</v>
       </c>
       <c r="L74" t="n">
-        <v>55.44</v>
+        <v>58.56</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>3.02</v>
+        <v>3.34</v>
       </c>
       <c r="K75" t="n">
-        <v>108.59</v>
+        <v>120.23</v>
       </c>
       <c r="L75" t="n">
-        <v>108.63</v>
+        <v>120.27</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>15.51</v>
+        <v>16.37</v>
       </c>
       <c r="K76" t="n">
-        <v>-91.06999999999999</v>
+        <v>-96.12</v>
       </c>
       <c r="L76" t="n">
-        <v>92.38</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>116.5</v>
+        <v>128.98</v>
       </c>
       <c r="K77" t="n">
-        <v>-59.99</v>
+        <v>-66.42</v>
       </c>
       <c r="L77" t="n">
-        <v>131.04</v>
+        <v>145.08</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>83.59</v>
+        <v>83.41</v>
       </c>
       <c r="K78" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="L78" t="n">
-        <v>84.18000000000001</v>
+        <v>84</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>78.65000000000001</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>7.96</v>
+        <v>7.95</v>
       </c>
       <c r="L79" t="n">
-        <v>79.05</v>
+        <v>78.97</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>-53.38</v>
+        <v>-58.21</v>
       </c>
       <c r="K80" t="n">
-        <v>86.36</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>101.52</v>
+        <v>110.72</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>10.67</v>
+        <v>11.46</v>
       </c>
       <c r="K81" t="n">
-        <v>83.88</v>
+        <v>90.09</v>
       </c>
       <c r="L81" t="n">
-        <v>84.55</v>
+        <v>90.81</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>32.55</v>
+        <v>33.79</v>
       </c>
       <c r="K82" t="n">
-        <v>-94.92</v>
+        <v>-98.53</v>
       </c>
       <c r="L82" t="n">
-        <v>100.35</v>
+        <v>104.16</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-145.21</v>
+        <v>-153.43</v>
       </c>
       <c r="K83" t="n">
-        <v>-50.66</v>
+        <v>-53.53</v>
       </c>
       <c r="L83" t="n">
-        <v>153.8</v>
+        <v>162.5</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-26.76</v>
+        <v>-27.29</v>
       </c>
       <c r="K84" t="n">
-        <v>-145.26</v>
+        <v>-148.16</v>
       </c>
       <c r="L84" t="n">
-        <v>147.71</v>
+        <v>150.65</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>112.81</v>
+        <v>123.06</v>
       </c>
       <c r="K85" t="n">
-        <v>9.859999999999999</v>
+        <v>10.76</v>
       </c>
       <c r="L85" t="n">
-        <v>113.24</v>
+        <v>123.53</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>154.46</v>
+        <v>163.21</v>
       </c>
       <c r="K86" t="n">
-        <v>107.57</v>
+        <v>113.66</v>
       </c>
       <c r="L86" t="n">
-        <v>188.23</v>
+        <v>198.89</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>18</v>
       </c>
       <c r="J87" t="n">
-        <v>162.83</v>
+        <v>180.28</v>
       </c>
       <c r="K87" t="n">
-        <v>-59.62</v>
+        <v>-66.01000000000001</v>
       </c>
       <c r="L87" t="n">
-        <v>173.41</v>
+        <v>191.98</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>-72.67</v>
+        <v>-80.47</v>
       </c>
       <c r="K88" t="n">
-        <v>-208.84</v>
+        <v>-231.24</v>
       </c>
       <c r="L88" t="n">
-        <v>221.12</v>
+        <v>244.84</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-03.xlsx
+++ b/output/2025-10-03.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="F14" t="n">
-        <v>6.79</v>
+        <v>3.05</v>
       </c>
       <c r="G14" t="n">
-        <v>120.8</v>
+        <v>123.7</v>
       </c>
       <c r="H14" t="n">
-        <v>85.8</v>
+        <v>32.4</v>
       </c>
       <c r="I14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>10.8</v>
+        <v>13.69</v>
       </c>
       <c r="K14" t="n">
-        <v>-45.52</v>
+        <v>39.78</v>
       </c>
       <c r="L14" t="n">
-        <v>46.78</v>
+        <v>42.07</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:23:34</t>
+          <t>07:22:53</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.59</v>
+        <v>2.36</v>
       </c>
       <c r="F15" t="n">
-        <v>7.01</v>
+        <v>7.18</v>
       </c>
       <c r="G15" t="n">
-        <v>113.5</v>
+        <v>114.2</v>
       </c>
       <c r="H15" t="n">
-        <v>83.09999999999999</v>
+        <v>51.7</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J15" t="n">
-        <v>-25.83</v>
+        <v>30.63</v>
       </c>
       <c r="K15" t="n">
-        <v>18.78</v>
+        <v>-4.92</v>
       </c>
       <c r="L15" t="n">
-        <v>31.94</v>
+        <v>31.03</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:25:02</t>
+          <t>07:23:46</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="F16" t="n">
-        <v>8.74</v>
+        <v>5.04</v>
       </c>
       <c r="G16" t="n">
-        <v>120.6</v>
+        <v>113.9</v>
       </c>
       <c r="H16" t="n">
-        <v>84.59999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-59.59</v>
+        <v>45.79</v>
       </c>
       <c r="K16" t="n">
-        <v>50.71</v>
+        <v>5.89</v>
       </c>
       <c r="L16" t="n">
-        <v>78.25</v>
+        <v>46.16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:30:47</t>
+          <t>07:28:02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="F17" t="n">
-        <v>5.31</v>
+        <v>6.11</v>
       </c>
       <c r="G17" t="n">
-        <v>116</v>
+        <v>110.7</v>
       </c>
       <c r="H17" t="n">
-        <v>90.90000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J17" t="n">
-        <v>28.24</v>
+        <v>-56.87</v>
       </c>
       <c r="K17" t="n">
-        <v>65.48</v>
+        <v>-22.18</v>
       </c>
       <c r="L17" t="n">
-        <v>71.31</v>
+        <v>61.04</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:32:49</t>
+          <t>07:29:55</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="F18" t="n">
-        <v>5.48</v>
+        <v>6.19</v>
       </c>
       <c r="G18" t="n">
-        <v>125.5</v>
+        <v>120</v>
       </c>
       <c r="H18" t="n">
-        <v>83.40000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I18" t="n">
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>53.61</v>
+        <v>-10.1</v>
       </c>
       <c r="K18" t="n">
-        <v>-33.14</v>
+        <v>-66.81</v>
       </c>
       <c r="L18" t="n">
-        <v>63.03</v>
+        <v>67.56</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:34:10</t>
+          <t>07:31:56</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.31</v>
+        <v>2.46</v>
       </c>
       <c r="F19" t="n">
-        <v>3.63</v>
+        <v>6.08</v>
       </c>
       <c r="G19" t="n">
-        <v>105.3</v>
+        <v>132.6</v>
       </c>
       <c r="H19" t="n">
-        <v>82.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J19" t="n">
-        <v>-45.85</v>
+        <v>50.37</v>
       </c>
       <c r="K19" t="n">
-        <v>36.66</v>
+        <v>27.4</v>
       </c>
       <c r="L19" t="n">
-        <v>58.71</v>
+        <v>57.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:40:37</t>
+          <t>07:37:09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="F20" t="n">
-        <v>5.03</v>
+        <v>4.87</v>
       </c>
       <c r="G20" t="n">
-        <v>116.8</v>
+        <v>96.3</v>
       </c>
       <c r="H20" t="n">
-        <v>87.3</v>
+        <v>55</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>-100.28</v>
+        <v>135.67</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.65</v>
+        <v>12.2</v>
       </c>
       <c r="L20" t="n">
-        <v>100.39</v>
+        <v>136.22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:42:28</t>
+          <t>07:39:04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="F21" t="n">
-        <v>6.63</v>
+        <v>5.18</v>
       </c>
       <c r="G21" t="n">
-        <v>110.1</v>
+        <v>111.4</v>
       </c>
       <c r="H21" t="n">
-        <v>81.40000000000001</v>
+        <v>32.4</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>18.66</v>
+        <v>68.78</v>
       </c>
       <c r="K21" t="n">
-        <v>-37.69</v>
+        <v>-86.25</v>
       </c>
       <c r="L21" t="n">
-        <v>42.06</v>
+        <v>110.31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:43:20</t>
+          <t>07:41:01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.3</v>
+        <v>2.92</v>
       </c>
       <c r="F22" t="n">
-        <v>5.29</v>
+        <v>7.78</v>
       </c>
       <c r="G22" t="n">
-        <v>99.7</v>
+        <v>115.1</v>
       </c>
       <c r="H22" t="n">
-        <v>91.3</v>
+        <v>40.4</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>-145.41</v>
+        <v>-23.07</v>
       </c>
       <c r="K22" t="n">
-        <v>24.93</v>
+        <v>113.24</v>
       </c>
       <c r="L22" t="n">
-        <v>147.53</v>
+        <v>115.57</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:48:28</t>
+          <t>07:46:14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.03</v>
+        <v>2.45</v>
       </c>
       <c r="F23" t="n">
-        <v>8.470000000000001</v>
+        <v>5.23</v>
       </c>
       <c r="G23" t="n">
-        <v>108.6</v>
+        <v>109</v>
       </c>
       <c r="H23" t="n">
-        <v>88</v>
+        <v>23.1</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>129.18</v>
+        <v>-68.73999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-63.26</v>
+        <v>113.43</v>
       </c>
       <c r="L23" t="n">
-        <v>143.84</v>
+        <v>132.63</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:49:49</t>
+          <t>07:47:23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.95</v>
+        <v>3.11</v>
       </c>
       <c r="F24" t="n">
-        <v>7.81</v>
+        <v>6.11</v>
       </c>
       <c r="G24" t="n">
-        <v>118.8</v>
+        <v>117.7</v>
       </c>
       <c r="H24" t="n">
-        <v>94.09999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>-42.21</v>
+        <v>-23.27</v>
       </c>
       <c r="K24" t="n">
-        <v>145.03</v>
+        <v>-133.94</v>
       </c>
       <c r="L24" t="n">
-        <v>151.04</v>
+        <v>135.94</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:52:18</t>
+          <t>07:48:45</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.01</v>
+        <v>3.16</v>
       </c>
       <c r="F25" t="n">
-        <v>5.16</v>
+        <v>7.63</v>
       </c>
       <c r="G25" t="n">
-        <v>119.4</v>
+        <v>110.7</v>
       </c>
       <c r="H25" t="n">
-        <v>87.2</v>
+        <v>25.1</v>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J25" t="n">
-        <v>-198.17</v>
+        <v>130.02</v>
       </c>
       <c r="K25" t="n">
-        <v>80.83</v>
+        <v>-114.37</v>
       </c>
       <c r="L25" t="n">
-        <v>214.02</v>
+        <v>173.17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:57:08</t>
+          <t>07:53:57</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.13</v>
+        <v>2.79</v>
       </c>
       <c r="F26" t="n">
-        <v>7.88</v>
+        <v>8.74</v>
       </c>
       <c r="G26" t="n">
-        <v>103.5</v>
+        <v>123.6</v>
       </c>
       <c r="H26" t="n">
-        <v>89.5</v>
+        <v>56.4</v>
       </c>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>206.62</v>
+        <v>159.4</v>
       </c>
       <c r="K26" t="n">
-        <v>-134.12</v>
+        <v>80.81</v>
       </c>
       <c r="L26" t="n">
-        <v>246.33</v>
+        <v>178.71</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:58:47</t>
+          <t>07:54:50</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="F27" t="n">
-        <v>4.98</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>122.4</v>
+        <v>116.1</v>
       </c>
       <c r="H27" t="n">
-        <v>88.40000000000001</v>
+        <v>32.5</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>218.44</v>
+        <v>-237.02</v>
       </c>
       <c r="K27" t="n">
-        <v>26.4</v>
+        <v>19.97</v>
       </c>
       <c r="L27" t="n">
-        <v>220.03</v>
+        <v>237.85</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08:00:22</t>
+          <t>07:57:03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.24</v>
+        <v>2.75</v>
       </c>
       <c r="F28" t="n">
-        <v>8.58</v>
+        <v>6.38</v>
       </c>
       <c r="G28" t="n">
-        <v>109.8</v>
+        <v>106.8</v>
       </c>
       <c r="H28" t="n">
-        <v>88.09999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>-134.49</v>
+        <v>168.01</v>
       </c>
       <c r="K28" t="n">
-        <v>-177.5</v>
+        <v>-223.99</v>
       </c>
       <c r="L28" t="n">
-        <v>222.69</v>
+        <v>280</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:09:14</t>
+          <t>08:10:12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.33</v>
+        <v>2.96</v>
       </c>
       <c r="F29" t="n">
-        <v>7.97</v>
+        <v>7.16</v>
       </c>
       <c r="G29" t="n">
-        <v>106.8</v>
+        <v>101.1</v>
       </c>
       <c r="H29" t="n">
-        <v>77.90000000000001</v>
+        <v>55.4</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-37.35</v>
+        <v>57.2</v>
       </c>
       <c r="K29" t="n">
-        <v>-54.54</v>
+        <v>18.98</v>
       </c>
       <c r="L29" t="n">
-        <v>66.09999999999999</v>
+        <v>60.27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:11:04</t>
+          <t>08:12:12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="F30" t="n">
-        <v>6.21</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>117.6</v>
+        <v>110.8</v>
       </c>
       <c r="H30" t="n">
-        <v>92.2</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I30" t="n">
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>-34.98</v>
+        <v>31.83</v>
       </c>
       <c r="K30" t="n">
-        <v>45.52</v>
+        <v>-26.29</v>
       </c>
       <c r="L30" t="n">
-        <v>57.41</v>
+        <v>41.28</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:13:07</t>
+          <t>08:13:03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="F31" t="n">
-        <v>8.550000000000001</v>
+        <v>6.99</v>
       </c>
       <c r="G31" t="n">
-        <v>124.4</v>
+        <v>114.4</v>
       </c>
       <c r="H31" t="n">
-        <v>84.40000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="I31" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-54.4</v>
+        <v>48.22</v>
       </c>
       <c r="K31" t="n">
-        <v>26.1</v>
+        <v>19.3</v>
       </c>
       <c r="L31" t="n">
-        <v>60.34</v>
+        <v>51.94</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:17:56</t>
+          <t>08:17:48</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="F32" t="n">
-        <v>5.18</v>
+        <v>6.06</v>
       </c>
       <c r="G32" t="n">
-        <v>113.5</v>
+        <v>121.1</v>
       </c>
       <c r="H32" t="n">
-        <v>88</v>
+        <v>60.3</v>
       </c>
       <c r="I32" t="n">
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>84.93000000000001</v>
+        <v>-12.26</v>
       </c>
       <c r="K32" t="n">
-        <v>10.72</v>
+        <v>-60.15</v>
       </c>
       <c r="L32" t="n">
-        <v>85.59999999999999</v>
+        <v>61.39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:20:08</t>
+          <t>08:20:05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.74</v>
+        <v>2.98</v>
       </c>
       <c r="F33" t="n">
-        <v>5.64</v>
+        <v>7.52</v>
       </c>
       <c r="G33" t="n">
-        <v>113.2</v>
+        <v>122.5</v>
       </c>
       <c r="H33" t="n">
-        <v>96.3</v>
+        <v>56.5</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>-13.33</v>
+        <v>81.12</v>
       </c>
       <c r="K33" t="n">
-        <v>-59.03</v>
+        <v>-8.94</v>
       </c>
       <c r="L33" t="n">
-        <v>60.52</v>
+        <v>81.62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:22:08</t>
+          <t>08:21:06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="F34" t="n">
-        <v>7.44</v>
+        <v>7.23</v>
       </c>
       <c r="G34" t="n">
-        <v>127.2</v>
+        <v>114.3</v>
       </c>
       <c r="H34" t="n">
-        <v>81.09999999999999</v>
+        <v>45.8</v>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-34.54</v>
+        <v>-16.15</v>
       </c>
       <c r="K34" t="n">
-        <v>-92.66</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>98.89</v>
+        <v>79.69</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:28:08</t>
+          <t>08:26:04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.01</v>
+        <v>2.68</v>
       </c>
       <c r="F35" t="n">
-        <v>8.74</v>
+        <v>4.13</v>
       </c>
       <c r="G35" t="n">
-        <v>110.6</v>
+        <v>113.2</v>
       </c>
       <c r="H35" t="n">
-        <v>89</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>92.34</v>
+        <v>-62.81</v>
       </c>
       <c r="K35" t="n">
-        <v>56.29</v>
+        <v>-118.73</v>
       </c>
       <c r="L35" t="n">
-        <v>108.14</v>
+        <v>134.32</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:30:16</t>
+          <t>08:27:36</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.73</v>
+        <v>3.31</v>
       </c>
       <c r="F36" t="n">
-        <v>8.74</v>
+        <v>7.32</v>
       </c>
       <c r="G36" t="n">
-        <v>118.2</v>
+        <v>114.5</v>
       </c>
       <c r="H36" t="n">
-        <v>86.59999999999999</v>
+        <v>43.2</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>119.26</v>
+        <v>44.82</v>
       </c>
       <c r="K36" t="n">
-        <v>75.66</v>
+        <v>-103.9</v>
       </c>
       <c r="L36" t="n">
-        <v>141.23</v>
+        <v>113.15</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:32:37</t>
+          <t>08:28:51</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.92</v>
+        <v>3.03</v>
       </c>
       <c r="F37" t="n">
-        <v>8.029999999999999</v>
+        <v>7.38</v>
       </c>
       <c r="G37" t="n">
-        <v>117.8</v>
+        <v>120.9</v>
       </c>
       <c r="H37" t="n">
-        <v>88.7</v>
+        <v>15</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J37" t="n">
-        <v>-110.68</v>
+        <v>184.73</v>
       </c>
       <c r="K37" t="n">
-        <v>-11.97</v>
+        <v>-64.16</v>
       </c>
       <c r="L37" t="n">
-        <v>111.33</v>
+        <v>195.56</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:37:28</t>
+          <t>08:32:22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.11</v>
+        <v>2.25</v>
       </c>
       <c r="F38" t="n">
-        <v>8.74</v>
+        <v>5.86</v>
       </c>
       <c r="G38" t="n">
-        <v>120.4</v>
+        <v>111.7</v>
       </c>
       <c r="H38" t="n">
-        <v>92.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>113.18</v>
+        <v>-6.45</v>
       </c>
       <c r="K38" t="n">
-        <v>-134.12</v>
+        <v>125.71</v>
       </c>
       <c r="L38" t="n">
-        <v>175.49</v>
+        <v>125.88</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:39:55</t>
+          <t>08:34:33</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.13</v>
+        <v>2.71</v>
       </c>
       <c r="F39" t="n">
-        <v>8.74</v>
+        <v>6.01</v>
       </c>
       <c r="G39" t="n">
-        <v>112</v>
+        <v>103.2</v>
       </c>
       <c r="H39" t="n">
-        <v>85.5</v>
+        <v>59.4</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>-127.85</v>
+        <v>-14.55</v>
       </c>
       <c r="K39" t="n">
-        <v>45.58</v>
+        <v>124.18</v>
       </c>
       <c r="L39" t="n">
-        <v>135.73</v>
+        <v>125.03</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:41:46</t>
+          <t>08:35:33</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="F40" t="n">
-        <v>8.74</v>
+        <v>7.02</v>
       </c>
       <c r="G40" t="n">
-        <v>115.1</v>
+        <v>105.2</v>
       </c>
       <c r="H40" t="n">
-        <v>86.5</v>
+        <v>14.9</v>
       </c>
       <c r="I40" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J40" t="n">
-        <v>196.05</v>
+        <v>-53.75</v>
       </c>
       <c r="K40" t="n">
-        <v>-92.61</v>
+        <v>-112.57</v>
       </c>
       <c r="L40" t="n">
-        <v>216.83</v>
+        <v>124.75</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:47:23</t>
+          <t>08:40:44</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.45</v>
+        <v>2.92</v>
       </c>
       <c r="F41" t="n">
-        <v>8.74</v>
+        <v>7.47</v>
       </c>
       <c r="G41" t="n">
-        <v>122.9</v>
+        <v>126.4</v>
       </c>
       <c r="H41" t="n">
-        <v>84.3</v>
+        <v>40.6</v>
       </c>
       <c r="I41" t="n">
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>88.92</v>
+        <v>-137.55</v>
       </c>
       <c r="K41" t="n">
-        <v>-142.82</v>
+        <v>-122.98</v>
       </c>
       <c r="L41" t="n">
-        <v>168.24</v>
+        <v>184.51</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:49:47</t>
+          <t>08:42:23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="F42" t="n">
-        <v>4.79</v>
+        <v>7.46</v>
       </c>
       <c r="G42" t="n">
-        <v>113</v>
+        <v>115.1</v>
       </c>
       <c r="H42" t="n">
-        <v>79</v>
+        <v>46.7</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>64.43000000000001</v>
+        <v>32.91</v>
       </c>
       <c r="K42" t="n">
-        <v>-171.92</v>
+        <v>244.42</v>
       </c>
       <c r="L42" t="n">
-        <v>183.6</v>
+        <v>246.62</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:51:54</t>
+          <t>08:44:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.8</v>
+        <v>3.22</v>
       </c>
       <c r="F43" t="n">
         <v>8.74</v>
       </c>
       <c r="G43" t="n">
-        <v>115.6</v>
+        <v>115.2</v>
       </c>
       <c r="H43" t="n">
-        <v>92.8</v>
+        <v>83.2</v>
       </c>
       <c r="I43" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>-220.81</v>
+        <v>96.59</v>
       </c>
       <c r="K43" t="n">
-        <v>-18.65</v>
+        <v>-203.8</v>
       </c>
       <c r="L43" t="n">
-        <v>221.6</v>
+        <v>225.53</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09:02:21</t>
+          <t>08:53:13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="F44" t="n">
-        <v>6.91</v>
+        <v>7.31</v>
       </c>
       <c r="G44" t="n">
-        <v>113.6</v>
+        <v>127.3</v>
       </c>
       <c r="H44" t="n">
-        <v>84.09999999999999</v>
+        <v>34.7</v>
       </c>
       <c r="I44" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-77.93000000000001</v>
+        <v>-13.13</v>
       </c>
       <c r="K44" t="n">
-        <v>16.91</v>
+        <v>-40.38</v>
       </c>
       <c r="L44" t="n">
-        <v>79.73999999999999</v>
+        <v>42.46</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09:03:38</t>
+          <t>08:55:15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.07</v>
+        <v>3.45</v>
       </c>
       <c r="F45" t="n">
-        <v>7.08</v>
+        <v>7.65</v>
       </c>
       <c r="G45" t="n">
-        <v>111.2</v>
+        <v>112.2</v>
       </c>
       <c r="H45" t="n">
-        <v>91.8</v>
+        <v>15.5</v>
       </c>
       <c r="I45" t="n">
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>32.52</v>
+        <v>-41</v>
       </c>
       <c r="K45" t="n">
-        <v>-76.64</v>
+        <v>-48.98</v>
       </c>
       <c r="L45" t="n">
-        <v>83.25</v>
+        <v>63.87</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09:05:46</t>
+          <t>08:57:51</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.71</v>
+        <v>2.77</v>
       </c>
       <c r="F46" t="n">
-        <v>7.7</v>
+        <v>6.27</v>
       </c>
       <c r="G46" t="n">
-        <v>114.6</v>
+        <v>110.5</v>
       </c>
       <c r="H46" t="n">
-        <v>83</v>
+        <v>39.1</v>
       </c>
       <c r="I46" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>35.43</v>
+        <v>-30.95</v>
       </c>
       <c r="K46" t="n">
-        <v>77.91</v>
+        <v>-40.25</v>
       </c>
       <c r="L46" t="n">
-        <v>85.59</v>
+        <v>50.77</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:11:14</t>
+          <t>09:02:53</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.82</v>
+        <v>3.22</v>
       </c>
       <c r="F47" t="n">
-        <v>7.21</v>
+        <v>7.07</v>
       </c>
       <c r="G47" t="n">
-        <v>112.4</v>
+        <v>111.8</v>
       </c>
       <c r="H47" t="n">
-        <v>85.5</v>
+        <v>61.3</v>
       </c>
       <c r="I47" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>-71.09999999999999</v>
+        <v>25.8</v>
       </c>
       <c r="K47" t="n">
-        <v>74.2</v>
+        <v>-65.94</v>
       </c>
       <c r="L47" t="n">
-        <v>102.77</v>
+        <v>70.81</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:12:55</t>
+          <t>09:05:09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.63</v>
+        <v>3.13</v>
       </c>
       <c r="F48" t="n">
-        <v>6.79</v>
+        <v>7.79</v>
       </c>
       <c r="G48" t="n">
-        <v>114.4</v>
+        <v>109.7</v>
       </c>
       <c r="H48" t="n">
-        <v>86.2</v>
+        <v>52.4</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>-36.21</v>
+        <v>-51.07</v>
       </c>
       <c r="K48" t="n">
-        <v>72.90000000000001</v>
+        <v>63.13</v>
       </c>
       <c r="L48" t="n">
-        <v>81.39</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:15:08</t>
+          <t>09:07:04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.53</v>
+        <v>3.09</v>
       </c>
       <c r="F49" t="n">
-        <v>6.29</v>
+        <v>8.74</v>
       </c>
       <c r="G49" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H49" t="n">
-        <v>85.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>51.13</v>
+        <v>40.16</v>
       </c>
       <c r="K49" t="n">
-        <v>-58.81</v>
+        <v>-94.64</v>
       </c>
       <c r="L49" t="n">
-        <v>77.92</v>
+        <v>102.81</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:20:21</t>
+          <t>09:11:05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.26</v>
+        <v>3.09</v>
       </c>
       <c r="F50" t="n">
-        <v>8.74</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>114.9</v>
+        <v>108.4</v>
       </c>
       <c r="H50" t="n">
-        <v>80.5</v>
+        <v>63.6</v>
       </c>
       <c r="I50" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-23.84</v>
+        <v>107.28</v>
       </c>
       <c r="K50" t="n">
-        <v>205.24</v>
+        <v>39.86</v>
       </c>
       <c r="L50" t="n">
-        <v>206.62</v>
+        <v>114.45</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:22:24</t>
+          <t>09:13:09</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="F51" t="n">
-        <v>5.86</v>
+        <v>7.15</v>
       </c>
       <c r="G51" t="n">
-        <v>108.9</v>
+        <v>105</v>
       </c>
       <c r="H51" t="n">
-        <v>85.90000000000001</v>
+        <v>54.1</v>
       </c>
       <c r="I51" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>95.86</v>
+        <v>-68.16</v>
       </c>
       <c r="K51" t="n">
-        <v>-72.84</v>
+        <v>-89.3</v>
       </c>
       <c r="L51" t="n">
-        <v>120.39</v>
+        <v>112.34</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:23:33</t>
+          <t>09:14:35</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.27</v>
+        <v>3.39</v>
       </c>
       <c r="F52" t="n">
-        <v>6.89</v>
+        <v>7.49</v>
       </c>
       <c r="G52" t="n">
-        <v>104.8</v>
+        <v>120.4</v>
       </c>
       <c r="H52" t="n">
-        <v>83.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I52" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>-61.41</v>
+        <v>-107.85</v>
       </c>
       <c r="K52" t="n">
-        <v>111.39</v>
+        <v>23.59</v>
       </c>
       <c r="L52" t="n">
-        <v>127.2</v>
+        <v>110.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:27:57</t>
+          <t>09:19:35</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.12</v>
+        <v>3.32</v>
       </c>
       <c r="F53" t="n">
-        <v>7.65</v>
+        <v>8.74</v>
       </c>
       <c r="G53" t="n">
-        <v>110.8</v>
+        <v>112.5</v>
       </c>
       <c r="H53" t="n">
-        <v>86.5</v>
+        <v>52</v>
       </c>
       <c r="I53" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>114.25</v>
+        <v>-204.97</v>
       </c>
       <c r="K53" t="n">
-        <v>-141.73</v>
+        <v>-26.93</v>
       </c>
       <c r="L53" t="n">
-        <v>182.04</v>
+        <v>206.73</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:29:12</t>
+          <t>09:21:11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.09</v>
+        <v>3.13</v>
       </c>
       <c r="F54" t="n">
-        <v>8.300000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="G54" t="n">
-        <v>118.4</v>
+        <v>122.7</v>
       </c>
       <c r="H54" t="n">
-        <v>87.8</v>
+        <v>67.8</v>
       </c>
       <c r="I54" t="n">
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-142.68</v>
+        <v>-95.8</v>
       </c>
       <c r="K54" t="n">
-        <v>29.52</v>
+        <v>102.67</v>
       </c>
       <c r="L54" t="n">
-        <v>145.7</v>
+        <v>140.43</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:30:31</t>
+          <t>09:23:05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="F55" t="n">
-        <v>8.33</v>
+        <v>8.41</v>
       </c>
       <c r="G55" t="n">
-        <v>116.2</v>
+        <v>117.9</v>
       </c>
       <c r="H55" t="n">
-        <v>87</v>
+        <v>58.5</v>
       </c>
       <c r="I55" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>35.55</v>
+        <v>131.29</v>
       </c>
       <c r="K55" t="n">
-        <v>-174.74</v>
+        <v>-97.84</v>
       </c>
       <c r="L55" t="n">
-        <v>178.31</v>
+        <v>163.73</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:33:40</t>
+          <t>09:28:35</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.07</v>
+        <v>3.15</v>
       </c>
       <c r="F56" t="n">
-        <v>8.74</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>127.9</v>
+        <v>111.5</v>
       </c>
       <c r="H56" t="n">
-        <v>81.59999999999999</v>
+        <v>32</v>
       </c>
       <c r="I56" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>53.02</v>
+        <v>42.07</v>
       </c>
       <c r="K56" t="n">
-        <v>229.41</v>
+        <v>231.2</v>
       </c>
       <c r="L56" t="n">
-        <v>235.45</v>
+        <v>235</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:35:00</t>
+          <t>09:30:51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.01</v>
+        <v>3.49</v>
       </c>
       <c r="F57" t="n">
-        <v>7.17</v>
+        <v>8.74</v>
       </c>
       <c r="G57" t="n">
-        <v>109.3</v>
+        <v>119.9</v>
       </c>
       <c r="H57" t="n">
-        <v>87.7</v>
+        <v>61.7</v>
       </c>
       <c r="I57" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J57" t="n">
-        <v>-146.22</v>
+        <v>-216.56</v>
       </c>
       <c r="K57" t="n">
-        <v>144.79</v>
+        <v>-23.49</v>
       </c>
       <c r="L57" t="n">
-        <v>205.78</v>
+        <v>217.83</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:36:14</t>
+          <t>09:32:14</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.12</v>
+        <v>3.23</v>
       </c>
       <c r="F58" t="n">
-        <v>7.22</v>
+        <v>8.74</v>
       </c>
       <c r="G58" t="n">
-        <v>134.2</v>
+        <v>100.1</v>
       </c>
       <c r="H58" t="n">
-        <v>88.8</v>
+        <v>54.7</v>
       </c>
       <c r="I58" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-88.06999999999999</v>
+        <v>186.33</v>
       </c>
       <c r="K58" t="n">
-        <v>258.99</v>
+        <v>-30.85</v>
       </c>
       <c r="L58" t="n">
-        <v>273.55</v>
+        <v>188.87</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:47:24</t>
+          <t>09:43:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.61</v>
+        <v>3.21</v>
       </c>
       <c r="F59" t="n">
-        <v>8.74</v>
+        <v>8.73</v>
       </c>
       <c r="G59" t="n">
-        <v>103</v>
+        <v>112.6</v>
       </c>
       <c r="H59" t="n">
-        <v>91.40000000000001</v>
+        <v>36</v>
       </c>
       <c r="I59" t="n">
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-78.84</v>
+        <v>0.75</v>
       </c>
       <c r="K59" t="n">
-        <v>-10.47</v>
+        <v>37.76</v>
       </c>
       <c r="L59" t="n">
-        <v>79.53</v>
+        <v>37.77</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:49:01</t>
+          <t>09:45:11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.97</v>
+        <v>3.07</v>
       </c>
       <c r="F60" t="n">
-        <v>6.68</v>
+        <v>8.6</v>
       </c>
       <c r="G60" t="n">
-        <v>107.3</v>
+        <v>113.6</v>
       </c>
       <c r="H60" t="n">
-        <v>82.90000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="I60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-23.1</v>
+        <v>20.35</v>
       </c>
       <c r="K60" t="n">
-        <v>-103.14</v>
+        <v>47.9</v>
       </c>
       <c r="L60" t="n">
-        <v>105.69</v>
+        <v>52.05</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:50:52</t>
+          <t>09:46:58</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="F61" t="n">
-        <v>8.17</v>
+        <v>6.12</v>
       </c>
       <c r="G61" t="n">
-        <v>103.8</v>
+        <v>105.1</v>
       </c>
       <c r="H61" t="n">
-        <v>89.5</v>
+        <v>35.6</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J61" t="n">
-        <v>1.27</v>
+        <v>43.94</v>
       </c>
       <c r="K61" t="n">
-        <v>77.95</v>
+        <v>23.27</v>
       </c>
       <c r="L61" t="n">
-        <v>77.95999999999999</v>
+        <v>49.72</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:55:00</t>
+          <t>09:51:06</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="F62" t="n">
         <v>8.74</v>
       </c>
       <c r="G62" t="n">
-        <v>127.4</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>81.90000000000001</v>
+        <v>61.9</v>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J62" t="n">
-        <v>96.27</v>
+        <v>-67.83</v>
       </c>
       <c r="K62" t="n">
-        <v>-57.46</v>
+        <v>-77.38</v>
       </c>
       <c r="L62" t="n">
-        <v>112.12</v>
+        <v>102.9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:55:56</t>
+          <t>09:52:22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.26</v>
+        <v>2.79</v>
       </c>
       <c r="F63" t="n">
-        <v>8.74</v>
+        <v>4.56</v>
       </c>
       <c r="G63" t="n">
-        <v>103</v>
+        <v>126.5</v>
       </c>
       <c r="H63" t="n">
-        <v>90</v>
+        <v>49.9</v>
       </c>
       <c r="I63" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>67.81999999999999</v>
+        <v>65.12</v>
       </c>
       <c r="K63" t="n">
-        <v>-41.76</v>
+        <v>-34.33</v>
       </c>
       <c r="L63" t="n">
-        <v>79.65000000000001</v>
+        <v>73.62</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:58:18</t>
+          <t>09:53:28</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="F64" t="n">
-        <v>8.74</v>
+        <v>8.43</v>
       </c>
       <c r="G64" t="n">
-        <v>118.3</v>
+        <v>120.5</v>
       </c>
       <c r="H64" t="n">
-        <v>82.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-102.83</v>
+        <v>101.03</v>
       </c>
       <c r="K64" t="n">
-        <v>-62.86</v>
+        <v>11.51</v>
       </c>
       <c r="L64" t="n">
-        <v>120.52</v>
+        <v>101.68</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10:04:17</t>
+          <t>09:58:57</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.17</v>
+        <v>3.73</v>
       </c>
       <c r="F65" t="n">
         <v>8.74</v>
       </c>
       <c r="G65" t="n">
-        <v>119.2</v>
+        <v>109.6</v>
       </c>
       <c r="H65" t="n">
-        <v>91</v>
+        <v>58.8</v>
       </c>
       <c r="I65" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>100.57</v>
+        <v>-149.03</v>
       </c>
       <c r="K65" t="n">
-        <v>-89.89</v>
+        <v>-58.17</v>
       </c>
       <c r="L65" t="n">
-        <v>134.89</v>
+        <v>159.98</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10:05:43</t>
+          <t>09:59:56</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.29</v>
+        <v>3.24</v>
       </c>
       <c r="F66" t="n">
-        <v>8.74</v>
+        <v>8.51</v>
       </c>
       <c r="G66" t="n">
-        <v>109.3</v>
+        <v>116.5</v>
       </c>
       <c r="H66" t="n">
-        <v>89.40000000000001</v>
+        <v>58.3</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>214.35</v>
+        <v>121.25</v>
       </c>
       <c r="K66" t="n">
-        <v>-82.25</v>
+        <v>-3.25</v>
       </c>
       <c r="L66" t="n">
-        <v>229.59</v>
+        <v>121.3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:07:39</t>
+          <t>10:00:44</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.02</v>
+        <v>2.73</v>
       </c>
       <c r="F67" t="n">
-        <v>6.54</v>
+        <v>8.24</v>
       </c>
       <c r="G67" t="n">
-        <v>118.6</v>
+        <v>114.3</v>
       </c>
       <c r="H67" t="n">
-        <v>86.09999999999999</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J67" t="n">
-        <v>-44.02</v>
+        <v>132.86</v>
       </c>
       <c r="K67" t="n">
-        <v>-116.21</v>
+        <v>-16.01</v>
       </c>
       <c r="L67" t="n">
-        <v>124.27</v>
+        <v>133.82</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:11:18</t>
+          <t>10:05:38</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="F68" t="n">
-        <v>6.89</v>
+        <v>8.74</v>
       </c>
       <c r="G68" t="n">
-        <v>121.8</v>
+        <v>109</v>
       </c>
       <c r="H68" t="n">
-        <v>81</v>
+        <v>14.1</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>74.12</v>
+        <v>-63.64</v>
       </c>
       <c r="K68" t="n">
-        <v>-164.46</v>
+        <v>152.55</v>
       </c>
       <c r="L68" t="n">
-        <v>180.39</v>
+        <v>165.29</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:12:08</t>
+          <t>10:07:48</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.14</v>
+        <v>2.76</v>
       </c>
       <c r="F69" t="n">
-        <v>8.619999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="G69" t="n">
-        <v>114.8</v>
+        <v>122</v>
       </c>
       <c r="H69" t="n">
-        <v>86.40000000000001</v>
+        <v>22.3</v>
       </c>
       <c r="I69" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>171.13</v>
+        <v>136.82</v>
       </c>
       <c r="K69" t="n">
-        <v>41.09</v>
+        <v>33.81</v>
       </c>
       <c r="L69" t="n">
-        <v>175.99</v>
+        <v>140.94</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:14:33</t>
+          <t>10:08:53</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.76</v>
+        <v>3.22</v>
       </c>
       <c r="F70" t="n">
-        <v>7.14</v>
+        <v>7.74</v>
       </c>
       <c r="G70" t="n">
-        <v>124.1</v>
+        <v>116.3</v>
       </c>
       <c r="H70" t="n">
-        <v>90.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="I70" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>12.54</v>
+        <v>-184.34</v>
       </c>
       <c r="K70" t="n">
-        <v>186.65</v>
+        <v>14.59</v>
       </c>
       <c r="L70" t="n">
-        <v>187.08</v>
+        <v>184.92</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:19:18</t>
+          <t>10:13:50</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.04</v>
+        <v>2.87</v>
       </c>
       <c r="F71" t="n">
-        <v>6.23</v>
+        <v>5.37</v>
       </c>
       <c r="G71" t="n">
-        <v>127.1</v>
+        <v>112</v>
       </c>
       <c r="H71" t="n">
-        <v>83.09999999999999</v>
+        <v>27</v>
       </c>
       <c r="I71" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>159.81</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>94.33</v>
+        <v>-182.64</v>
       </c>
       <c r="L71" t="n">
-        <v>185.57</v>
+        <v>205.62</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:20:21</t>
+          <t>10:15:06</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.07</v>
+        <v>2.73</v>
       </c>
       <c r="F72" t="n">
-        <v>7.35</v>
+        <v>8.74</v>
       </c>
       <c r="G72" t="n">
-        <v>118.3</v>
+        <v>122.6</v>
       </c>
       <c r="H72" t="n">
-        <v>89.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>204.56</v>
+        <v>171.39</v>
       </c>
       <c r="K72" t="n">
-        <v>-123.76</v>
+        <v>-134.82</v>
       </c>
       <c r="L72" t="n">
-        <v>239.09</v>
+        <v>218.06</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:22:12</t>
+          <t>10:16:11</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="F73" t="n">
-        <v>7.26</v>
+        <v>8.74</v>
       </c>
       <c r="G73" t="n">
-        <v>110.2</v>
+        <v>109.4</v>
       </c>
       <c r="H73" t="n">
-        <v>78.5</v>
+        <v>55.2</v>
       </c>
       <c r="I73" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>202.92</v>
+        <v>2.7</v>
       </c>
       <c r="K73" t="n">
-        <v>-83.86</v>
+        <v>-249.94</v>
       </c>
       <c r="L73" t="n">
-        <v>219.57</v>
+        <v>249.95</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:30:57</t>
+          <t>10:27:46</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.31</v>
+        <v>3.55</v>
       </c>
       <c r="F74" t="n">
-        <v>6.93</v>
+        <v>8.74</v>
       </c>
       <c r="G74" t="n">
-        <v>116.6</v>
+        <v>119.6</v>
       </c>
       <c r="H74" t="n">
-        <v>85</v>
+        <v>46.6</v>
       </c>
       <c r="I74" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>-2.77</v>
+        <v>-50.86</v>
       </c>
       <c r="K74" t="n">
-        <v>-58.5</v>
+        <v>-20.2</v>
       </c>
       <c r="L74" t="n">
-        <v>58.56</v>
+        <v>54.72</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:31:53</t>
+          <t>10:30:07</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.92</v>
+        <v>3.46</v>
       </c>
       <c r="F75" t="n">
-        <v>8.74</v>
+        <v>6.81</v>
       </c>
       <c r="G75" t="n">
         <v>115.8</v>
       </c>
       <c r="H75" t="n">
-        <v>82.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>3.34</v>
+        <v>-6.43</v>
       </c>
       <c r="K75" t="n">
-        <v>120.23</v>
+        <v>-72.28</v>
       </c>
       <c r="L75" t="n">
-        <v>120.27</v>
+        <v>72.56999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:34:47</t>
+          <t>10:31:41</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.47</v>
+        <v>2.87</v>
       </c>
       <c r="F76" t="n">
-        <v>8.74</v>
+        <v>7.12</v>
       </c>
       <c r="G76" t="n">
-        <v>115.8</v>
+        <v>123.9</v>
       </c>
       <c r="H76" t="n">
-        <v>85.09999999999999</v>
+        <v>61.2</v>
       </c>
       <c r="I76" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>16.37</v>
+        <v>-21.79</v>
       </c>
       <c r="K76" t="n">
-        <v>-96.12</v>
+        <v>-33.98</v>
       </c>
       <c r="L76" t="n">
-        <v>97.5</v>
+        <v>40.37</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:38:16</t>
+          <t>10:36:37</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.85</v>
+        <v>3.24</v>
       </c>
       <c r="F77" t="n">
-        <v>7.43</v>
+        <v>7.79</v>
       </c>
       <c r="G77" t="n">
-        <v>98</v>
+        <v>114.2</v>
       </c>
       <c r="H77" t="n">
-        <v>83.3</v>
+        <v>88.2</v>
       </c>
       <c r="I77" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>128.98</v>
+        <v>66.55</v>
       </c>
       <c r="K77" t="n">
-        <v>-66.42</v>
+        <v>-38.44</v>
       </c>
       <c r="L77" t="n">
-        <v>145.08</v>
+        <v>76.84999999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:39:58</t>
+          <t>10:37:54</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.69</v>
+        <v>3.16</v>
       </c>
       <c r="F78" t="n">
-        <v>8.74</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G78" t="n">
-        <v>107.6</v>
+        <v>120.1</v>
       </c>
       <c r="H78" t="n">
-        <v>83.5</v>
+        <v>37.2</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>83.41</v>
+        <v>69.34</v>
       </c>
       <c r="K78" t="n">
-        <v>9.98</v>
+        <v>-33.9</v>
       </c>
       <c r="L78" t="n">
-        <v>84</v>
+        <v>77.18000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:41:08</t>
+          <t>10:40:23</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.44</v>
+        <v>3.59</v>
       </c>
       <c r="F79" t="n">
         <v>8.74</v>
       </c>
       <c r="G79" t="n">
-        <v>107.1</v>
+        <v>115.4</v>
       </c>
       <c r="H79" t="n">
-        <v>94.59999999999999</v>
+        <v>24.8</v>
       </c>
       <c r="I79" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>78.56999999999999</v>
+        <v>-79.20999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>7.95</v>
+        <v>-47.14</v>
       </c>
       <c r="L79" t="n">
-        <v>78.97</v>
+        <v>92.18000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:45:16</t>
+          <t>10:45:37</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="F80" t="n">
         <v>8.74</v>
       </c>
       <c r="G80" t="n">
-        <v>114.1</v>
+        <v>114.9</v>
       </c>
       <c r="H80" t="n">
-        <v>83</v>
+        <v>36.8</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-58.21</v>
+        <v>121.01</v>
       </c>
       <c r="K80" t="n">
-        <v>94.18000000000001</v>
+        <v>-21.51</v>
       </c>
       <c r="L80" t="n">
-        <v>110.72</v>
+        <v>122.9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:47:18</t>
+          <t>10:47:45</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.01</v>
+        <v>3.28</v>
       </c>
       <c r="F81" t="n">
-        <v>7.57</v>
+        <v>8.74</v>
       </c>
       <c r="G81" t="n">
-        <v>108</v>
+        <v>109.3</v>
       </c>
       <c r="H81" t="n">
-        <v>88.5</v>
+        <v>56.3</v>
       </c>
       <c r="I81" t="n">
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>11.46</v>
+        <v>100.91</v>
       </c>
       <c r="K81" t="n">
-        <v>90.09</v>
+        <v>-60.71</v>
       </c>
       <c r="L81" t="n">
-        <v>90.81</v>
+        <v>117.76</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:48:29</t>
+          <t>10:48:44</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.49</v>
+        <v>3.18</v>
       </c>
       <c r="F82" t="n">
         <v>8.74</v>
       </c>
       <c r="G82" t="n">
-        <v>119.1</v>
+        <v>104.9</v>
       </c>
       <c r="H82" t="n">
-        <v>92.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="I82" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>33.79</v>
+        <v>17.81</v>
       </c>
       <c r="K82" t="n">
-        <v>-98.53</v>
+        <v>115.55</v>
       </c>
       <c r="L82" t="n">
-        <v>104.16</v>
+        <v>116.92</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:52:54</t>
+          <t>10:53:20</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.98</v>
+        <v>3.47</v>
       </c>
       <c r="F83" t="n">
         <v>8.74</v>
       </c>
       <c r="G83" t="n">
-        <v>107.7</v>
+        <v>119.9</v>
       </c>
       <c r="H83" t="n">
-        <v>88.8</v>
+        <v>11.5</v>
       </c>
       <c r="I83" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-153.43</v>
+        <v>17.91</v>
       </c>
       <c r="K83" t="n">
-        <v>-53.53</v>
+        <v>223.86</v>
       </c>
       <c r="L83" t="n">
-        <v>162.5</v>
+        <v>224.58</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:54:01</t>
+          <t>10:54:25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.52</v>
+        <v>3.33</v>
       </c>
       <c r="F84" t="n">
-        <v>8.74</v>
+        <v>6.37</v>
       </c>
       <c r="G84" t="n">
-        <v>124.5</v>
+        <v>107</v>
       </c>
       <c r="H84" t="n">
-        <v>89.3</v>
+        <v>53.1</v>
       </c>
       <c r="I84" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>-27.29</v>
+        <v>-150.41</v>
       </c>
       <c r="K84" t="n">
-        <v>-148.16</v>
+        <v>27.93</v>
       </c>
       <c r="L84" t="n">
-        <v>150.65</v>
+        <v>152.98</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:56:08</t>
+          <t>10:55:37</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.08</v>
+        <v>3.65</v>
       </c>
       <c r="F85" t="n">
-        <v>5.65</v>
+        <v>8.74</v>
       </c>
       <c r="G85" t="n">
-        <v>106.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>86.59999999999999</v>
+        <v>51.4</v>
       </c>
       <c r="I85" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>123.06</v>
+        <v>65.23</v>
       </c>
       <c r="K85" t="n">
-        <v>10.76</v>
+        <v>177.99</v>
       </c>
       <c r="L85" t="n">
-        <v>123.53</v>
+        <v>189.56</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11:00:58</t>
+          <t>10:59:41</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="F86" t="n">
         <v>8.74</v>
       </c>
       <c r="G86" t="n">
-        <v>128.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="H86" t="n">
-        <v>83.5</v>
+        <v>54.5</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>163.21</v>
+        <v>182.26</v>
       </c>
       <c r="K86" t="n">
-        <v>113.66</v>
+        <v>-40.53</v>
       </c>
       <c r="L86" t="n">
-        <v>198.89</v>
+        <v>186.71</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11:03:11</t>
+          <t>11:01:31</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="F87" t="n">
-        <v>8.74</v>
+        <v>6.41</v>
       </c>
       <c r="G87" t="n">
-        <v>119.6</v>
+        <v>108.4</v>
       </c>
       <c r="H87" t="n">
-        <v>85.09999999999999</v>
+        <v>37.2</v>
       </c>
       <c r="I87" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J87" t="n">
-        <v>180.28</v>
+        <v>168.91</v>
       </c>
       <c r="K87" t="n">
-        <v>-66.01000000000001</v>
+        <v>16.27</v>
       </c>
       <c r="L87" t="n">
-        <v>191.98</v>
+        <v>169.69</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:05:06</t>
+          <t>11:03:09</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.26</v>
+        <v>3.19</v>
       </c>
       <c r="F88" t="n">
-        <v>8.74</v>
+        <v>7.3</v>
       </c>
       <c r="G88" t="n">
-        <v>125.1</v>
+        <v>101.3</v>
       </c>
       <c r="H88" t="n">
-        <v>87.7</v>
+        <v>30.2</v>
       </c>
       <c r="I88" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-80.47</v>
+        <v>-1.64</v>
       </c>
       <c r="K88" t="n">
-        <v>-231.24</v>
+        <v>-248.36</v>
       </c>
       <c r="L88" t="n">
-        <v>244.84</v>
+        <v>248.36</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-03.xlsx
+++ b/output/2025-10-03.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="F14" t="n">
-        <v>3.05</v>
+        <v>5.79</v>
       </c>
       <c r="G14" t="n">
-        <v>123.7</v>
+        <v>113.3</v>
       </c>
       <c r="H14" t="n">
-        <v>32.4</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>13.69</v>
+        <v>38.31</v>
       </c>
       <c r="K14" t="n">
-        <v>39.78</v>
+        <v>-20.45</v>
       </c>
       <c r="L14" t="n">
-        <v>42.07</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:22:53</t>
+          <t>07:23:20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.36</v>
+        <v>2.8</v>
       </c>
       <c r="F15" t="n">
-        <v>7.18</v>
+        <v>7.69</v>
       </c>
       <c r="G15" t="n">
-        <v>114.2</v>
+        <v>110.9</v>
       </c>
       <c r="H15" t="n">
-        <v>51.7</v>
+        <v>84.2</v>
       </c>
       <c r="I15" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>30.63</v>
+        <v>22.75</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.92</v>
+        <v>12.2</v>
       </c>
       <c r="L15" t="n">
-        <v>31.03</v>
+        <v>25.82</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:23:46</t>
+          <t>07:24:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="F16" t="n">
-        <v>5.04</v>
+        <v>5.76</v>
       </c>
       <c r="G16" t="n">
-        <v>113.9</v>
+        <v>118.3</v>
       </c>
       <c r="H16" t="n">
-        <v>85.2</v>
+        <v>85.5</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>45.79</v>
+        <v>-18.72</v>
       </c>
       <c r="K16" t="n">
-        <v>5.89</v>
+        <v>31.46</v>
       </c>
       <c r="L16" t="n">
-        <v>46.16</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:28:02</t>
+          <t>07:29:41</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.51</v>
+        <v>2.34</v>
       </c>
       <c r="F17" t="n">
-        <v>6.11</v>
+        <v>3.77</v>
       </c>
       <c r="G17" t="n">
-        <v>110.7</v>
+        <v>124.3</v>
       </c>
       <c r="H17" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-56.87</v>
+        <v>-45.22</v>
       </c>
       <c r="K17" t="n">
-        <v>-22.18</v>
+        <v>-7.92</v>
       </c>
       <c r="L17" t="n">
-        <v>61.04</v>
+        <v>45.91</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:29:55</t>
+          <t>07:31:03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="F18" t="n">
-        <v>6.19</v>
+        <v>5.35</v>
       </c>
       <c r="G18" t="n">
-        <v>120</v>
+        <v>101.5</v>
       </c>
       <c r="H18" t="n">
-        <v>70.09999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>-10.1</v>
+        <v>-57.45</v>
       </c>
       <c r="K18" t="n">
-        <v>-66.81</v>
+        <v>38.59</v>
       </c>
       <c r="L18" t="n">
-        <v>67.56</v>
+        <v>69.20999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:31:56</t>
+          <t>07:32:15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.46</v>
+        <v>2.83</v>
       </c>
       <c r="F19" t="n">
-        <v>6.08</v>
+        <v>7.13</v>
       </c>
       <c r="G19" t="n">
-        <v>132.6</v>
+        <v>121.5</v>
       </c>
       <c r="H19" t="n">
-        <v>73.2</v>
+        <v>84</v>
       </c>
       <c r="I19" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>50.37</v>
+        <v>2.39</v>
       </c>
       <c r="K19" t="n">
-        <v>27.4</v>
+        <v>-69.98999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>57.33</v>
+        <v>70.03</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:37:09</t>
+          <t>07:36:32</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.62</v>
+        <v>2.12</v>
       </c>
       <c r="F20" t="n">
-        <v>4.87</v>
+        <v>4.72</v>
       </c>
       <c r="G20" t="n">
-        <v>96.3</v>
+        <v>109.6</v>
       </c>
       <c r="H20" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>135.67</v>
+        <v>16.36</v>
       </c>
       <c r="K20" t="n">
-        <v>12.2</v>
+        <v>86.89</v>
       </c>
       <c r="L20" t="n">
-        <v>136.22</v>
+        <v>88.41</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:39:04</t>
+          <t>07:37:50</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="F21" t="n">
-        <v>5.18</v>
+        <v>5.31</v>
       </c>
       <c r="G21" t="n">
-        <v>111.4</v>
+        <v>127.6</v>
       </c>
       <c r="H21" t="n">
-        <v>32.4</v>
+        <v>48.8</v>
       </c>
       <c r="I21" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>68.78</v>
+        <v>38.11</v>
       </c>
       <c r="K21" t="n">
-        <v>-86.25</v>
+        <v>-92.18000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>110.31</v>
+        <v>99.75</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:41:01</t>
+          <t>07:40:13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.92</v>
+        <v>2.54</v>
       </c>
       <c r="F22" t="n">
-        <v>7.78</v>
+        <v>3.3</v>
       </c>
       <c r="G22" t="n">
-        <v>115.1</v>
+        <v>109.6</v>
       </c>
       <c r="H22" t="n">
-        <v>40.4</v>
+        <v>74.5</v>
       </c>
       <c r="I22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-23.07</v>
+        <v>-66.18000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>113.24</v>
+        <v>-18.12</v>
       </c>
       <c r="L22" t="n">
-        <v>115.57</v>
+        <v>68.62</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:46:14</t>
+          <t>07:44:37</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="F23" t="n">
-        <v>5.23</v>
+        <v>4.7</v>
       </c>
       <c r="G23" t="n">
-        <v>109</v>
+        <v>111.3</v>
       </c>
       <c r="H23" t="n">
-        <v>23.1</v>
+        <v>33</v>
       </c>
       <c r="I23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-68.73999999999999</v>
+        <v>-105.6</v>
       </c>
       <c r="K23" t="n">
-        <v>113.43</v>
+        <v>73</v>
       </c>
       <c r="L23" t="n">
-        <v>132.63</v>
+        <v>128.38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:47:23</t>
+          <t>07:46:29</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.11</v>
+        <v>3.43</v>
       </c>
       <c r="F24" t="n">
-        <v>6.11</v>
+        <v>6.9</v>
       </c>
       <c r="G24" t="n">
-        <v>117.7</v>
+        <v>115.1</v>
       </c>
       <c r="H24" t="n">
-        <v>68.8</v>
+        <v>58.2</v>
       </c>
       <c r="I24" t="n">
         <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>-23.27</v>
+        <v>127.65</v>
       </c>
       <c r="K24" t="n">
-        <v>-133.94</v>
+        <v>158.04</v>
       </c>
       <c r="L24" t="n">
-        <v>135.94</v>
+        <v>203.16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:48:45</t>
+          <t>07:47:49</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.16</v>
+        <v>2.4</v>
       </c>
       <c r="F25" t="n">
-        <v>7.63</v>
+        <v>6.09</v>
       </c>
       <c r="G25" t="n">
-        <v>110.7</v>
+        <v>113.1</v>
       </c>
       <c r="H25" t="n">
-        <v>25.1</v>
+        <v>45</v>
       </c>
       <c r="I25" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J25" t="n">
-        <v>130.02</v>
+        <v>-127.4</v>
       </c>
       <c r="K25" t="n">
-        <v>-114.37</v>
+        <v>-7.54</v>
       </c>
       <c r="L25" t="n">
-        <v>173.17</v>
+        <v>127.62</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:53:57</t>
+          <t>07:52:34</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.79</v>
+        <v>2.29</v>
       </c>
       <c r="F26" t="n">
-        <v>8.74</v>
+        <v>4.66</v>
       </c>
       <c r="G26" t="n">
         <v>123.6</v>
       </c>
       <c r="H26" t="n">
-        <v>56.4</v>
+        <v>56.3</v>
       </c>
       <c r="I26" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>159.4</v>
+        <v>-44.21</v>
       </c>
       <c r="K26" t="n">
-        <v>80.81</v>
+        <v>211.89</v>
       </c>
       <c r="L26" t="n">
-        <v>178.71</v>
+        <v>216.45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:54:50</t>
+          <t>07:54:51</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.93</v>
+        <v>2.5</v>
       </c>
       <c r="F27" t="n">
-        <v>8.289999999999999</v>
+        <v>4.03</v>
       </c>
       <c r="G27" t="n">
-        <v>116.1</v>
+        <v>120.8</v>
       </c>
       <c r="H27" t="n">
-        <v>32.5</v>
+        <v>90.8</v>
       </c>
       <c r="I27" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-237.02</v>
+        <v>132.55</v>
       </c>
       <c r="K27" t="n">
-        <v>19.97</v>
+        <v>120.95</v>
       </c>
       <c r="L27" t="n">
-        <v>237.85</v>
+        <v>179.44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:57:03</t>
+          <t>07:56:01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="F28" t="n">
-        <v>6.38</v>
+        <v>7.97</v>
       </c>
       <c r="G28" t="n">
-        <v>106.8</v>
+        <v>114.9</v>
       </c>
       <c r="H28" t="n">
-        <v>80.59999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>168.01</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>-223.99</v>
+        <v>-143.14</v>
       </c>
       <c r="L28" t="n">
-        <v>280</v>
+        <v>163.86</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:10:12</t>
+          <t>08:09:33</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="F29" t="n">
-        <v>7.16</v>
+        <v>7.44</v>
       </c>
       <c r="G29" t="n">
-        <v>101.1</v>
+        <v>113.3</v>
       </c>
       <c r="H29" t="n">
-        <v>55.4</v>
+        <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>57.2</v>
+        <v>25.25</v>
       </c>
       <c r="K29" t="n">
-        <v>18.98</v>
+        <v>-130.64</v>
       </c>
       <c r="L29" t="n">
-        <v>60.27</v>
+        <v>133.06</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:12:12</t>
+          <t>08:10:31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="F30" t="n">
-        <v>8.199999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="G30" t="n">
-        <v>110.8</v>
+        <v>108.4</v>
       </c>
       <c r="H30" t="n">
-        <v>68.90000000000001</v>
+        <v>24.6</v>
       </c>
       <c r="I30" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>31.83</v>
+        <v>-41.26</v>
       </c>
       <c r="K30" t="n">
-        <v>-26.29</v>
+        <v>14.39</v>
       </c>
       <c r="L30" t="n">
-        <v>41.28</v>
+        <v>43.69</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:13:03</t>
+          <t>08:11:47</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.93</v>
+        <v>2.49</v>
       </c>
       <c r="F31" t="n">
-        <v>6.99</v>
+        <v>8.49</v>
       </c>
       <c r="G31" t="n">
-        <v>114.4</v>
+        <v>117.6</v>
       </c>
       <c r="H31" t="n">
-        <v>96.2</v>
+        <v>51.7</v>
       </c>
       <c r="I31" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>48.22</v>
+        <v>33.41</v>
       </c>
       <c r="K31" t="n">
-        <v>19.3</v>
+        <v>2.21</v>
       </c>
       <c r="L31" t="n">
-        <v>51.94</v>
+        <v>33.48</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:17:48</t>
+          <t>08:17:11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="F32" t="n">
-        <v>6.06</v>
+        <v>5.87</v>
       </c>
       <c r="G32" t="n">
-        <v>121.1</v>
+        <v>121.6</v>
       </c>
       <c r="H32" t="n">
-        <v>60.3</v>
+        <v>57</v>
       </c>
       <c r="I32" t="n">
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-12.26</v>
+        <v>-59.11</v>
       </c>
       <c r="K32" t="n">
-        <v>-60.15</v>
+        <v>-47.24</v>
       </c>
       <c r="L32" t="n">
-        <v>61.39</v>
+        <v>75.67</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:20:05</t>
+          <t>08:18:05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.98</v>
+        <v>3.18</v>
       </c>
       <c r="F33" t="n">
-        <v>7.52</v>
+        <v>8.74</v>
       </c>
       <c r="G33" t="n">
-        <v>122.5</v>
+        <v>117.4</v>
       </c>
       <c r="H33" t="n">
-        <v>56.5</v>
+        <v>63.4</v>
       </c>
       <c r="I33" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>81.12</v>
+        <v>-86.5</v>
       </c>
       <c r="K33" t="n">
-        <v>-8.94</v>
+        <v>-3.5</v>
       </c>
       <c r="L33" t="n">
-        <v>81.62</v>
+        <v>86.56999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:21:06</t>
+          <t>08:19:43</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.05</v>
+        <v>2.46</v>
       </c>
       <c r="F34" t="n">
-        <v>7.23</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>114.3</v>
+        <v>129.2</v>
       </c>
       <c r="H34" t="n">
-        <v>45.8</v>
+        <v>40.8</v>
       </c>
       <c r="I34" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-16.15</v>
+        <v>33.17</v>
       </c>
       <c r="K34" t="n">
-        <v>78.04000000000001</v>
+        <v>32.73</v>
       </c>
       <c r="L34" t="n">
-        <v>79.69</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:26:04</t>
+          <t>08:24:32</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="F35" t="n">
-        <v>4.13</v>
+        <v>8.74</v>
       </c>
       <c r="G35" t="n">
-        <v>113.2</v>
+        <v>114</v>
       </c>
       <c r="H35" t="n">
-        <v>69.90000000000001</v>
+        <v>34.5</v>
       </c>
       <c r="I35" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J35" t="n">
-        <v>-62.81</v>
+        <v>-20.97</v>
       </c>
       <c r="K35" t="n">
-        <v>-118.73</v>
+        <v>-82.17</v>
       </c>
       <c r="L35" t="n">
-        <v>134.32</v>
+        <v>84.81</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:27:36</t>
+          <t>08:26:09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.31</v>
+        <v>2.76</v>
       </c>
       <c r="F36" t="n">
-        <v>7.32</v>
+        <v>5.86</v>
       </c>
       <c r="G36" t="n">
-        <v>114.5</v>
+        <v>117.6</v>
       </c>
       <c r="H36" t="n">
-        <v>43.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I36" t="n">
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>44.82</v>
+        <v>-87.18000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-103.9</v>
+        <v>-12.03</v>
       </c>
       <c r="L36" t="n">
-        <v>113.15</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:28:51</t>
+          <t>08:28:53</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.03</v>
+        <v>3.12</v>
       </c>
       <c r="F37" t="n">
-        <v>7.38</v>
+        <v>6.64</v>
       </c>
       <c r="G37" t="n">
-        <v>120.9</v>
+        <v>119.8</v>
       </c>
       <c r="H37" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="I37" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J37" t="n">
-        <v>184.73</v>
+        <v>49.46</v>
       </c>
       <c r="K37" t="n">
-        <v>-64.16</v>
+        <v>-176.36</v>
       </c>
       <c r="L37" t="n">
-        <v>195.56</v>
+        <v>183.16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:32:22</t>
+          <t>08:32:44</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.25</v>
+        <v>2.61</v>
       </c>
       <c r="F38" t="n">
-        <v>5.86</v>
+        <v>5.36</v>
       </c>
       <c r="G38" t="n">
-        <v>111.7</v>
+        <v>122.1</v>
       </c>
       <c r="H38" t="n">
-        <v>92.09999999999999</v>
+        <v>56.2</v>
       </c>
       <c r="I38" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-6.45</v>
+        <v>163.75</v>
       </c>
       <c r="K38" t="n">
-        <v>125.71</v>
+        <v>10.52</v>
       </c>
       <c r="L38" t="n">
-        <v>125.88</v>
+        <v>164.08</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:34:33</t>
+          <t>08:34:32</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="F39" t="n">
-        <v>6.01</v>
+        <v>7.85</v>
       </c>
       <c r="G39" t="n">
-        <v>103.2</v>
+        <v>105.8</v>
       </c>
       <c r="H39" t="n">
-        <v>59.4</v>
+        <v>54.7</v>
       </c>
       <c r="I39" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-14.55</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>124.18</v>
+        <v>-112.77</v>
       </c>
       <c r="L39" t="n">
-        <v>125.03</v>
+        <v>136.21</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:35:33</t>
+          <t>08:36:12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>7.02</v>
+        <v>7.78</v>
       </c>
       <c r="G40" t="n">
-        <v>105.2</v>
+        <v>117</v>
       </c>
       <c r="H40" t="n">
-        <v>14.9</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-53.75</v>
+        <v>-71.73999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>-112.57</v>
+        <v>191.7</v>
       </c>
       <c r="L40" t="n">
-        <v>124.75</v>
+        <v>204.69</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:40:44</t>
+          <t>08:40:52</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.92</v>
+        <v>3.11</v>
       </c>
       <c r="F41" t="n">
-        <v>7.47</v>
+        <v>7.52</v>
       </c>
       <c r="G41" t="n">
-        <v>126.4</v>
+        <v>110.2</v>
       </c>
       <c r="H41" t="n">
-        <v>40.6</v>
+        <v>49.2</v>
       </c>
       <c r="I41" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-137.55</v>
+        <v>-183.04</v>
       </c>
       <c r="K41" t="n">
-        <v>-122.98</v>
+        <v>-16.48</v>
       </c>
       <c r="L41" t="n">
-        <v>184.51</v>
+        <v>183.78</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:42:23</t>
+          <t>08:42:04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="F42" t="n">
-        <v>7.46</v>
+        <v>8.74</v>
       </c>
       <c r="G42" t="n">
-        <v>115.1</v>
+        <v>107.9</v>
       </c>
       <c r="H42" t="n">
-        <v>46.7</v>
+        <v>81.5</v>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>32.91</v>
+        <v>-166.56</v>
       </c>
       <c r="K42" t="n">
-        <v>244.42</v>
+        <v>81.87</v>
       </c>
       <c r="L42" t="n">
-        <v>246.62</v>
+        <v>185.59</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:44:00</t>
+          <t>08:43:34</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.22</v>
+        <v>3.49</v>
       </c>
       <c r="F43" t="n">
-        <v>8.74</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>115.2</v>
+        <v>120.2</v>
       </c>
       <c r="H43" t="n">
-        <v>83.2</v>
+        <v>55.9</v>
       </c>
       <c r="I43" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>96.59</v>
+        <v>-123.85</v>
       </c>
       <c r="K43" t="n">
-        <v>-203.8</v>
+        <v>-190.02</v>
       </c>
       <c r="L43" t="n">
-        <v>225.53</v>
+        <v>226.82</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:53:13</t>
+          <t>08:52:59</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.08</v>
+        <v>2.71</v>
       </c>
       <c r="F44" t="n">
-        <v>7.31</v>
+        <v>7.42</v>
       </c>
       <c r="G44" t="n">
-        <v>127.3</v>
+        <v>111.3</v>
       </c>
       <c r="H44" t="n">
-        <v>34.7</v>
+        <v>82.8</v>
       </c>
       <c r="I44" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>-13.13</v>
+        <v>-22.32</v>
       </c>
       <c r="K44" t="n">
-        <v>-40.38</v>
+        <v>33.49</v>
       </c>
       <c r="L44" t="n">
-        <v>42.46</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:55:15</t>
+          <t>08:54:06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.45</v>
+        <v>3.13</v>
       </c>
       <c r="F45" t="n">
-        <v>7.65</v>
+        <v>7.01</v>
       </c>
       <c r="G45" t="n">
-        <v>112.2</v>
+        <v>111.5</v>
       </c>
       <c r="H45" t="n">
-        <v>15.5</v>
+        <v>22.3</v>
       </c>
       <c r="I45" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-41</v>
+        <v>-37.94</v>
       </c>
       <c r="K45" t="n">
-        <v>-48.98</v>
+        <v>26.91</v>
       </c>
       <c r="L45" t="n">
-        <v>63.87</v>
+        <v>46.51</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:57:51</t>
+          <t>08:56:20</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.77</v>
+        <v>3.4</v>
       </c>
       <c r="F46" t="n">
-        <v>6.27</v>
+        <v>8.74</v>
       </c>
       <c r="G46" t="n">
-        <v>110.5</v>
+        <v>104.8</v>
       </c>
       <c r="H46" t="n">
-        <v>39.1</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-30.95</v>
+        <v>38.66</v>
       </c>
       <c r="K46" t="n">
-        <v>-40.25</v>
+        <v>-30.73</v>
       </c>
       <c r="L46" t="n">
-        <v>50.77</v>
+        <v>49.39</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:02:53</t>
+          <t>09:02:13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.22</v>
+        <v>3.01</v>
       </c>
       <c r="F47" t="n">
-        <v>7.07</v>
+        <v>7.16</v>
       </c>
       <c r="G47" t="n">
-        <v>111.8</v>
+        <v>104.6</v>
       </c>
       <c r="H47" t="n">
-        <v>61.3</v>
+        <v>56.1</v>
       </c>
       <c r="I47" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J47" t="n">
-        <v>25.8</v>
+        <v>27.37</v>
       </c>
       <c r="K47" t="n">
-        <v>-65.94</v>
+        <v>58.17</v>
       </c>
       <c r="L47" t="n">
-        <v>70.81</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:05:09</t>
+          <t>09:03:18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.13</v>
+        <v>3.26</v>
       </c>
       <c r="F48" t="n">
-        <v>7.79</v>
+        <v>8.74</v>
       </c>
       <c r="G48" t="n">
-        <v>109.7</v>
+        <v>116.1</v>
       </c>
       <c r="H48" t="n">
-        <v>52.4</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-51.07</v>
+        <v>23.86</v>
       </c>
       <c r="K48" t="n">
-        <v>63.13</v>
+        <v>-54.85</v>
       </c>
       <c r="L48" t="n">
-        <v>81.2</v>
+        <v>59.82</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:07:04</t>
+          <t>09:05:09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.09</v>
+        <v>2.88</v>
       </c>
       <c r="F49" t="n">
-        <v>8.74</v>
+        <v>7.12</v>
       </c>
       <c r="G49" t="n">
-        <v>115</v>
+        <v>107.4</v>
       </c>
       <c r="H49" t="n">
-        <v>69.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>40.16</v>
+        <v>31.3</v>
       </c>
       <c r="K49" t="n">
-        <v>-94.64</v>
+        <v>49.94</v>
       </c>
       <c r="L49" t="n">
-        <v>102.81</v>
+        <v>58.94</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:11:05</t>
+          <t>09:09:25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.09</v>
+        <v>2.72</v>
       </c>
       <c r="F50" t="n">
-        <v>8.050000000000001</v>
+        <v>7.08</v>
       </c>
       <c r="G50" t="n">
-        <v>108.4</v>
+        <v>110.7</v>
       </c>
       <c r="H50" t="n">
-        <v>63.6</v>
+        <v>51.3</v>
       </c>
       <c r="I50" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>107.28</v>
+        <v>-60.96</v>
       </c>
       <c r="K50" t="n">
-        <v>39.86</v>
+        <v>-200.85</v>
       </c>
       <c r="L50" t="n">
-        <v>114.45</v>
+        <v>209.9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:13:09</t>
+          <t>09:10:52</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.95</v>
+        <v>3.34</v>
       </c>
       <c r="F51" t="n">
-        <v>7.15</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>105</v>
+        <v>111.6</v>
       </c>
       <c r="H51" t="n">
-        <v>54.1</v>
+        <v>32.6</v>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J51" t="n">
-        <v>-68.16</v>
+        <v>-85.45999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-89.3</v>
+        <v>-53.95</v>
       </c>
       <c r="L51" t="n">
-        <v>112.34</v>
+        <v>101.07</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:14:35</t>
+          <t>09:12:53</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.39</v>
+        <v>2.84</v>
       </c>
       <c r="F52" t="n">
-        <v>7.49</v>
+        <v>6.48</v>
       </c>
       <c r="G52" t="n">
-        <v>120.4</v>
+        <v>115.6</v>
       </c>
       <c r="H52" t="n">
-        <v>100</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-107.85</v>
+        <v>67.11</v>
       </c>
       <c r="K52" t="n">
-        <v>23.59</v>
+        <v>37.07</v>
       </c>
       <c r="L52" t="n">
-        <v>110.4</v>
+        <v>76.67</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:19:35</t>
+          <t>09:18:19</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.32</v>
+        <v>3.04</v>
       </c>
       <c r="F53" t="n">
-        <v>8.74</v>
+        <v>7.44</v>
       </c>
       <c r="G53" t="n">
-        <v>112.5</v>
+        <v>106.4</v>
       </c>
       <c r="H53" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-204.97</v>
+        <v>-94.23</v>
       </c>
       <c r="K53" t="n">
-        <v>-26.93</v>
+        <v>149.62</v>
       </c>
       <c r="L53" t="n">
-        <v>206.73</v>
+        <v>176.82</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:21:11</t>
+          <t>09:20:13</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.13</v>
+        <v>3.27</v>
       </c>
       <c r="F54" t="n">
-        <v>8.74</v>
+        <v>8.58</v>
       </c>
       <c r="G54" t="n">
-        <v>122.7</v>
+        <v>116.4</v>
       </c>
       <c r="H54" t="n">
-        <v>67.8</v>
+        <v>18.5</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>-95.8</v>
+        <v>178.44</v>
       </c>
       <c r="K54" t="n">
-        <v>102.67</v>
+        <v>-22.86</v>
       </c>
       <c r="L54" t="n">
-        <v>140.43</v>
+        <v>179.89</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:23:05</t>
+          <t>09:22:39</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.23</v>
+        <v>2.95</v>
       </c>
       <c r="F55" t="n">
-        <v>8.41</v>
+        <v>7.02</v>
       </c>
       <c r="G55" t="n">
-        <v>117.9</v>
+        <v>132.5</v>
       </c>
       <c r="H55" t="n">
-        <v>58.5</v>
+        <v>26.4</v>
       </c>
       <c r="I55" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>131.29</v>
+        <v>176.79</v>
       </c>
       <c r="K55" t="n">
-        <v>-97.84</v>
+        <v>-5.36</v>
       </c>
       <c r="L55" t="n">
-        <v>163.73</v>
+        <v>176.87</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:28:35</t>
+          <t>09:26:46</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="F56" t="n">
-        <v>8.449999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="G56" t="n">
-        <v>111.5</v>
+        <v>112.3</v>
       </c>
       <c r="H56" t="n">
-        <v>32</v>
+        <v>27.5</v>
       </c>
       <c r="I56" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>42.07</v>
+        <v>278.79</v>
       </c>
       <c r="K56" t="n">
-        <v>231.2</v>
+        <v>-113.22</v>
       </c>
       <c r="L56" t="n">
-        <v>235</v>
+        <v>300.9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:30:51</t>
+          <t>09:29:06</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.49</v>
+        <v>3.63</v>
       </c>
       <c r="F57" t="n">
         <v>8.74</v>
       </c>
       <c r="G57" t="n">
-        <v>119.9</v>
+        <v>104.3</v>
       </c>
       <c r="H57" t="n">
-        <v>61.7</v>
+        <v>58</v>
       </c>
       <c r="I57" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-216.56</v>
+        <v>-202.01</v>
       </c>
       <c r="K57" t="n">
-        <v>-23.49</v>
+        <v>-210.62</v>
       </c>
       <c r="L57" t="n">
-        <v>217.83</v>
+        <v>291.83</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:32:14</t>
+          <t>09:30:41</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.23</v>
+        <v>3.73</v>
       </c>
       <c r="F58" t="n">
         <v>8.74</v>
       </c>
       <c r="G58" t="n">
-        <v>100.1</v>
+        <v>110.1</v>
       </c>
       <c r="H58" t="n">
-        <v>54.7</v>
+        <v>89.8</v>
       </c>
       <c r="I58" t="n">
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>186.33</v>
+        <v>326.97</v>
       </c>
       <c r="K58" t="n">
-        <v>-30.85</v>
+        <v>-199</v>
       </c>
       <c r="L58" t="n">
-        <v>188.87</v>
+        <v>382.77</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:43:00</t>
+          <t>09:42:15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.21</v>
+        <v>3.02</v>
       </c>
       <c r="F59" t="n">
-        <v>8.73</v>
+        <v>7.53</v>
       </c>
       <c r="G59" t="n">
-        <v>112.6</v>
+        <v>108</v>
       </c>
       <c r="H59" t="n">
-        <v>36</v>
+        <v>31.5</v>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J59" t="n">
-        <v>0.75</v>
+        <v>36.56</v>
       </c>
       <c r="K59" t="n">
-        <v>37.76</v>
+        <v>-30.96</v>
       </c>
       <c r="L59" t="n">
-        <v>37.77</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:45:11</t>
+          <t>09:43:18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.07</v>
+        <v>2.94</v>
       </c>
       <c r="F60" t="n">
         <v>8.6</v>
       </c>
       <c r="G60" t="n">
-        <v>113.6</v>
+        <v>114</v>
       </c>
       <c r="H60" t="n">
-        <v>85.3</v>
+        <v>46.2</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>20.35</v>
+        <v>-14.81</v>
       </c>
       <c r="K60" t="n">
-        <v>47.9</v>
+        <v>-22.82</v>
       </c>
       <c r="L60" t="n">
-        <v>52.05</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:46:58</t>
+          <t>09:45:12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="F61" t="n">
-        <v>6.12</v>
+        <v>7.16</v>
       </c>
       <c r="G61" t="n">
-        <v>105.1</v>
+        <v>111.6</v>
       </c>
       <c r="H61" t="n">
-        <v>35.6</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>43.94</v>
+        <v>53.66</v>
       </c>
       <c r="K61" t="n">
-        <v>23.27</v>
+        <v>9.59</v>
       </c>
       <c r="L61" t="n">
-        <v>49.72</v>
+        <v>54.51</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:51:06</t>
+          <t>09:49:19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="F62" t="n">
         <v>8.74</v>
       </c>
       <c r="G62" t="n">
-        <v>97.90000000000001</v>
+        <v>104.3</v>
       </c>
       <c r="H62" t="n">
-        <v>61.9</v>
+        <v>46.4</v>
       </c>
       <c r="I62" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-67.83</v>
+        <v>-67</v>
       </c>
       <c r="K62" t="n">
-        <v>-77.38</v>
+        <v>-24.33</v>
       </c>
       <c r="L62" t="n">
-        <v>102.9</v>
+        <v>71.28</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:52:22</t>
+          <t>09:51:53</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="F63" t="n">
-        <v>4.56</v>
+        <v>7.07</v>
       </c>
       <c r="G63" t="n">
-        <v>126.5</v>
+        <v>115.3</v>
       </c>
       <c r="H63" t="n">
-        <v>49.9</v>
+        <v>100</v>
       </c>
       <c r="I63" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>65.12</v>
+        <v>-20.11</v>
       </c>
       <c r="K63" t="n">
-        <v>-34.33</v>
+        <v>-67.23999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>73.62</v>
+        <v>70.18000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:53:28</t>
+          <t>09:52:47</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="F64" t="n">
-        <v>8.43</v>
+        <v>8.57</v>
       </c>
       <c r="G64" t="n">
-        <v>120.5</v>
+        <v>108.5</v>
       </c>
       <c r="H64" t="n">
-        <v>87.90000000000001</v>
+        <v>52.5</v>
       </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>101.03</v>
+        <v>-17.66</v>
       </c>
       <c r="K64" t="n">
-        <v>11.51</v>
+        <v>-59.71</v>
       </c>
       <c r="L64" t="n">
-        <v>101.68</v>
+        <v>62.27</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:58:57</t>
+          <t>09:57:28</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.73</v>
+        <v>3.22</v>
       </c>
       <c r="F65" t="n">
         <v>8.74</v>
       </c>
       <c r="G65" t="n">
-        <v>109.6</v>
+        <v>122.2</v>
       </c>
       <c r="H65" t="n">
-        <v>58.8</v>
+        <v>65.3</v>
       </c>
       <c r="I65" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>-149.03</v>
+        <v>-91.38</v>
       </c>
       <c r="K65" t="n">
-        <v>-58.17</v>
+        <v>10.14</v>
       </c>
       <c r="L65" t="n">
-        <v>159.98</v>
+        <v>91.94</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:59:56</t>
+          <t>09:58:51</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.24</v>
+        <v>3.43</v>
       </c>
       <c r="F66" t="n">
-        <v>8.51</v>
+        <v>8.74</v>
       </c>
       <c r="G66" t="n">
-        <v>116.5</v>
+        <v>135.9</v>
       </c>
       <c r="H66" t="n">
-        <v>58.3</v>
+        <v>53.9</v>
       </c>
       <c r="I66" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>121.25</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.25</v>
+        <v>11.43</v>
       </c>
       <c r="L66" t="n">
-        <v>121.3</v>
+        <v>76.62</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:00:44</t>
+          <t>10:00:50</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.73</v>
+        <v>3.12</v>
       </c>
       <c r="F67" t="n">
-        <v>8.24</v>
+        <v>8.31</v>
       </c>
       <c r="G67" t="n">
-        <v>114.3</v>
+        <v>113</v>
       </c>
       <c r="H67" t="n">
-        <v>64.40000000000001</v>
+        <v>57.4</v>
       </c>
       <c r="I67" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>132.86</v>
+        <v>-4.48</v>
       </c>
       <c r="K67" t="n">
-        <v>-16.01</v>
+        <v>57.4</v>
       </c>
       <c r="L67" t="n">
-        <v>133.82</v>
+        <v>57.57</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:05:38</t>
+          <t>10:05:35</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.93</v>
+        <v>3.31</v>
       </c>
       <c r="F68" t="n">
         <v>8.74</v>
       </c>
       <c r="G68" t="n">
-        <v>109</v>
+        <v>110.3</v>
       </c>
       <c r="H68" t="n">
-        <v>14.1</v>
+        <v>28.8</v>
       </c>
       <c r="I68" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>-63.64</v>
+        <v>136.43</v>
       </c>
       <c r="K68" t="n">
-        <v>152.55</v>
+        <v>113.08</v>
       </c>
       <c r="L68" t="n">
-        <v>165.29</v>
+        <v>177.2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:07:48</t>
+          <t>10:07:21</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.76</v>
+        <v>3.52</v>
       </c>
       <c r="F69" t="n">
         <v>8.74</v>
       </c>
       <c r="G69" t="n">
-        <v>122</v>
+        <v>115.5</v>
       </c>
       <c r="H69" t="n">
-        <v>22.3</v>
+        <v>54.4</v>
       </c>
       <c r="I69" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>136.82</v>
+        <v>-170.19</v>
       </c>
       <c r="K69" t="n">
-        <v>33.81</v>
+        <v>-28.18</v>
       </c>
       <c r="L69" t="n">
-        <v>140.94</v>
+        <v>172.51</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:08:53</t>
+          <t>10:08:12</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="F70" t="n">
-        <v>7.74</v>
+        <v>8.74</v>
       </c>
       <c r="G70" t="n">
-        <v>116.3</v>
+        <v>107.3</v>
       </c>
       <c r="H70" t="n">
-        <v>88.5</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-184.34</v>
+        <v>66.05</v>
       </c>
       <c r="K70" t="n">
-        <v>14.59</v>
+        <v>57.35</v>
       </c>
       <c r="L70" t="n">
-        <v>184.92</v>
+        <v>87.47</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:13:50</t>
+          <t>10:12:45</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.87</v>
+        <v>3.22</v>
       </c>
       <c r="F71" t="n">
-        <v>5.37</v>
+        <v>8.74</v>
       </c>
       <c r="G71" t="n">
-        <v>112</v>
+        <v>121.3</v>
       </c>
       <c r="H71" t="n">
-        <v>27</v>
+        <v>78.3</v>
       </c>
       <c r="I71" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>94.45999999999999</v>
+        <v>156.41</v>
       </c>
       <c r="K71" t="n">
-        <v>-182.64</v>
+        <v>197.5</v>
       </c>
       <c r="L71" t="n">
-        <v>205.62</v>
+        <v>251.93</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:15:06</t>
+          <t>10:15:01</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.73</v>
+        <v>2.96</v>
       </c>
       <c r="F72" t="n">
-        <v>8.74</v>
+        <v>7.17</v>
       </c>
       <c r="G72" t="n">
-        <v>122.6</v>
+        <v>110.5</v>
       </c>
       <c r="H72" t="n">
-        <v>72.09999999999999</v>
+        <v>58</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>171.39</v>
+        <v>-60.85</v>
       </c>
       <c r="K72" t="n">
-        <v>-134.82</v>
+        <v>48.66</v>
       </c>
       <c r="L72" t="n">
-        <v>218.06</v>
+        <v>77.91</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:16:11</t>
+          <t>10:17:14</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="F73" t="n">
-        <v>8.74</v>
+        <v>6.61</v>
       </c>
       <c r="G73" t="n">
-        <v>109.4</v>
+        <v>119.1</v>
       </c>
       <c r="H73" t="n">
-        <v>55.2</v>
+        <v>45.5</v>
       </c>
       <c r="I73" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>2.7</v>
+        <v>64.13</v>
       </c>
       <c r="K73" t="n">
-        <v>-249.94</v>
+        <v>175.79</v>
       </c>
       <c r="L73" t="n">
-        <v>249.95</v>
+        <v>187.12</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:27:46</t>
+          <t>10:29:00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.55</v>
+        <v>2.98</v>
       </c>
       <c r="F74" t="n">
-        <v>8.74</v>
+        <v>6.13</v>
       </c>
       <c r="G74" t="n">
-        <v>119.6</v>
+        <v>108.4</v>
       </c>
       <c r="H74" t="n">
-        <v>46.6</v>
+        <v>43.2</v>
       </c>
       <c r="I74" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>-50.86</v>
+        <v>1.49</v>
       </c>
       <c r="K74" t="n">
-        <v>-20.2</v>
+        <v>47.02</v>
       </c>
       <c r="L74" t="n">
-        <v>54.72</v>
+        <v>47.04</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:30:07</t>
+          <t>10:31:16</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.46</v>
+        <v>3.31</v>
       </c>
       <c r="F75" t="n">
-        <v>6.81</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G75" t="n">
-        <v>115.8</v>
+        <v>97.2</v>
       </c>
       <c r="H75" t="n">
-        <v>83.90000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.43</v>
+        <v>28.68</v>
       </c>
       <c r="K75" t="n">
-        <v>-72.28</v>
+        <v>-49.05</v>
       </c>
       <c r="L75" t="n">
-        <v>72.56999999999999</v>
+        <v>56.82</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:31:41</t>
+          <t>10:32:29</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.87</v>
+        <v>2.98</v>
       </c>
       <c r="F76" t="n">
-        <v>7.12</v>
+        <v>8.74</v>
       </c>
       <c r="G76" t="n">
-        <v>123.9</v>
+        <v>127.2</v>
       </c>
       <c r="H76" t="n">
-        <v>61.2</v>
+        <v>51.4</v>
       </c>
       <c r="I76" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J76" t="n">
-        <v>-21.79</v>
+        <v>44.04</v>
       </c>
       <c r="K76" t="n">
-        <v>-33.98</v>
+        <v>30.98</v>
       </c>
       <c r="L76" t="n">
-        <v>40.37</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:36:37</t>
+          <t>10:38:06</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.24</v>
+        <v>2.78</v>
       </c>
       <c r="F77" t="n">
-        <v>7.79</v>
+        <v>7.58</v>
       </c>
       <c r="G77" t="n">
-        <v>114.2</v>
+        <v>114.9</v>
       </c>
       <c r="H77" t="n">
-        <v>88.2</v>
+        <v>82.5</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>66.55</v>
+        <v>39.12</v>
       </c>
       <c r="K77" t="n">
-        <v>-38.44</v>
+        <v>-60.31</v>
       </c>
       <c r="L77" t="n">
-        <v>76.84999999999999</v>
+        <v>71.89</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:37:54</t>
+          <t>10:40:13</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="F78" t="n">
-        <v>8.710000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="G78" t="n">
-        <v>120.1</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>37.2</v>
+        <v>57.4</v>
       </c>
       <c r="I78" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>69.34</v>
+        <v>11.48</v>
       </c>
       <c r="K78" t="n">
-        <v>-33.9</v>
+        <v>-66.20999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>77.18000000000001</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:40:23</t>
+          <t>10:41:53</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.59</v>
+        <v>3.79</v>
       </c>
       <c r="F79" t="n">
         <v>8.74</v>
       </c>
       <c r="G79" t="n">
-        <v>115.4</v>
+        <v>107.4</v>
       </c>
       <c r="H79" t="n">
-        <v>24.8</v>
+        <v>63.5</v>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-79.20999999999999</v>
+        <v>-60.83</v>
       </c>
       <c r="K79" t="n">
-        <v>-47.14</v>
+        <v>-58.19</v>
       </c>
       <c r="L79" t="n">
-        <v>92.18000000000001</v>
+        <v>84.18000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:45:37</t>
+          <t>10:47:04</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="F80" t="n">
         <v>8.74</v>
       </c>
       <c r="G80" t="n">
-        <v>114.9</v>
+        <v>121.7</v>
       </c>
       <c r="H80" t="n">
-        <v>36.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>121.01</v>
+        <v>107.84</v>
       </c>
       <c r="K80" t="n">
-        <v>-21.51</v>
+        <v>35.68</v>
       </c>
       <c r="L80" t="n">
-        <v>122.9</v>
+        <v>113.58</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:47:45</t>
+          <t>10:49:12</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.28</v>
+        <v>3.11</v>
       </c>
       <c r="F81" t="n">
         <v>8.74</v>
       </c>
       <c r="G81" t="n">
-        <v>109.3</v>
+        <v>121.1</v>
       </c>
       <c r="H81" t="n">
-        <v>56.3</v>
+        <v>92</v>
       </c>
       <c r="I81" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>100.91</v>
+        <v>102.45</v>
       </c>
       <c r="K81" t="n">
-        <v>-60.71</v>
+        <v>-13.28</v>
       </c>
       <c r="L81" t="n">
-        <v>117.76</v>
+        <v>103.31</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:48:44</t>
+          <t>10:51:05</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.18</v>
+        <v>3.52</v>
       </c>
       <c r="F82" t="n">
-        <v>8.74</v>
+        <v>7.98</v>
       </c>
       <c r="G82" t="n">
-        <v>104.9</v>
+        <v>123</v>
       </c>
       <c r="H82" t="n">
-        <v>85.2</v>
+        <v>34.7</v>
       </c>
       <c r="I82" t="n">
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>17.81</v>
+        <v>-31.82</v>
       </c>
       <c r="K82" t="n">
-        <v>115.55</v>
+        <v>-101.66</v>
       </c>
       <c r="L82" t="n">
-        <v>116.92</v>
+        <v>106.52</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:53:20</t>
+          <t>10:55:55</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="F83" t="n">
         <v>8.74</v>
       </c>
       <c r="G83" t="n">
-        <v>119.9</v>
+        <v>129.9</v>
       </c>
       <c r="H83" t="n">
-        <v>11.5</v>
+        <v>30.6</v>
       </c>
       <c r="I83" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J83" t="n">
-        <v>17.91</v>
+        <v>14.31</v>
       </c>
       <c r="K83" t="n">
-        <v>223.86</v>
+        <v>166.3</v>
       </c>
       <c r="L83" t="n">
-        <v>224.58</v>
+        <v>166.92</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:54:25</t>
+          <t>10:58:26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.33</v>
+        <v>4.37</v>
       </c>
       <c r="F84" t="n">
-        <v>6.37</v>
+        <v>8.74</v>
       </c>
       <c r="G84" t="n">
-        <v>107</v>
+        <v>107.5</v>
       </c>
       <c r="H84" t="n">
-        <v>53.1</v>
+        <v>100</v>
       </c>
       <c r="I84" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-150.41</v>
+        <v>148.4</v>
       </c>
       <c r="K84" t="n">
-        <v>27.93</v>
+        <v>148.92</v>
       </c>
       <c r="L84" t="n">
-        <v>152.98</v>
+        <v>210.24</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:55:37</t>
+          <t>10:59:39</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="F85" t="n">
         <v>8.74</v>
       </c>
       <c r="G85" t="n">
-        <v>99.90000000000001</v>
+        <v>108.3</v>
       </c>
       <c r="H85" t="n">
-        <v>51.4</v>
+        <v>76</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>65.23</v>
+        <v>189.56</v>
       </c>
       <c r="K85" t="n">
-        <v>177.99</v>
+        <v>-31.79</v>
       </c>
       <c r="L85" t="n">
-        <v>189.56</v>
+        <v>192.2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:59:41</t>
+          <t>11:04:50</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="F86" t="n">
         <v>8.74</v>
       </c>
       <c r="G86" t="n">
-        <v>93.40000000000001</v>
+        <v>118.4</v>
       </c>
       <c r="H86" t="n">
-        <v>54.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J86" t="n">
-        <v>182.26</v>
+        <v>-174.18</v>
       </c>
       <c r="K86" t="n">
-        <v>-40.53</v>
+        <v>-81.34</v>
       </c>
       <c r="L86" t="n">
-        <v>186.71</v>
+        <v>192.24</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11:01:31</t>
+          <t>11:06:54</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="F87" t="n">
-        <v>6.41</v>
+        <v>8.74</v>
       </c>
       <c r="G87" t="n">
-        <v>108.4</v>
+        <v>117</v>
       </c>
       <c r="H87" t="n">
-        <v>37.2</v>
+        <v>92.3</v>
       </c>
       <c r="I87" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>168.91</v>
+        <v>-206.23</v>
       </c>
       <c r="K87" t="n">
-        <v>16.27</v>
+        <v>49.05</v>
       </c>
       <c r="L87" t="n">
-        <v>169.69</v>
+        <v>211.98</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:03:09</t>
+          <t>11:09:01</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="F88" t="n">
-        <v>7.3</v>
+        <v>8.74</v>
       </c>
       <c r="G88" t="n">
-        <v>101.3</v>
+        <v>120.2</v>
       </c>
       <c r="H88" t="n">
-        <v>30.2</v>
+        <v>53.1</v>
       </c>
       <c r="I88" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.64</v>
+        <v>-76.54000000000001</v>
       </c>
       <c r="K88" t="n">
-        <v>-248.36</v>
+        <v>-186.08</v>
       </c>
       <c r="L88" t="n">
-        <v>248.36</v>
+        <v>201.21</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-03.xlsx
+++ b/output/2025-10-03.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>38.98</v>
+        <v>47.71</v>
       </c>
       <c r="K14" t="n">
-        <v>27.64</v>
+        <v>33.83</v>
       </c>
       <c r="L14" t="n">
-        <v>47.79</v>
+        <v>58.48</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-44.14</v>
+        <v>-47.15</v>
       </c>
       <c r="K15" t="n">
-        <v>-49.7</v>
+        <v>-53.08</v>
       </c>
       <c r="L15" t="n">
-        <v>66.47</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.01</v>
+        <v>-9.65</v>
       </c>
       <c r="K16" t="n">
-        <v>54.81</v>
+        <v>58.71</v>
       </c>
       <c r="L16" t="n">
-        <v>55.55</v>
+        <v>59.49</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>9.07</v>
+        <v>11.21</v>
       </c>
       <c r="K17" t="n">
-        <v>-20.62</v>
+        <v>-25.49</v>
       </c>
       <c r="L17" t="n">
-        <v>22.53</v>
+        <v>27.84</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-57.36</v>
+        <v>-56.36</v>
       </c>
       <c r="K18" t="n">
-        <v>-103.93</v>
+        <v>-102.11</v>
       </c>
       <c r="L18" t="n">
-        <v>118.71</v>
+        <v>116.64</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="K19" t="n">
-        <v>-74.94</v>
+        <v>-82.66</v>
       </c>
       <c r="L19" t="n">
-        <v>75.01000000000001</v>
+        <v>82.75</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-113.27</v>
+        <v>-128.14</v>
       </c>
       <c r="K20" t="n">
-        <v>-20.45</v>
+        <v>-23.14</v>
       </c>
       <c r="L20" t="n">
-        <v>115.1</v>
+        <v>130.21</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>103.7</v>
+        <v>118.91</v>
       </c>
       <c r="K21" t="n">
-        <v>6.92</v>
+        <v>7.94</v>
       </c>
       <c r="L21" t="n">
-        <v>103.93</v>
+        <v>119.17</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-104.97</v>
+        <v>-115.82</v>
       </c>
       <c r="K22" t="n">
-        <v>-52.34</v>
+        <v>-57.75</v>
       </c>
       <c r="L22" t="n">
-        <v>117.3</v>
+        <v>129.42</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>76.81</v>
+        <v>96.64</v>
       </c>
       <c r="K23" t="n">
-        <v>94.09999999999999</v>
+        <v>118.4</v>
       </c>
       <c r="L23" t="n">
-        <v>121.46</v>
+        <v>152.83</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>124.64</v>
+        <v>152.76</v>
       </c>
       <c r="K24" t="n">
-        <v>-27.99</v>
+        <v>-34.31</v>
       </c>
       <c r="L24" t="n">
-        <v>127.75</v>
+        <v>156.57</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>6.08</v>
+        <v>7.11</v>
       </c>
       <c r="K25" t="n">
-        <v>-157.4</v>
+        <v>-184.14</v>
       </c>
       <c r="L25" t="n">
-        <v>157.51</v>
+        <v>184.28</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-266.64</v>
+        <v>-315.04</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.22</v>
+        <v>-3.8</v>
       </c>
       <c r="L26" t="n">
-        <v>266.66</v>
+        <v>315.07</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-147.25</v>
+        <v>-180.88</v>
       </c>
       <c r="K27" t="n">
-        <v>-159.32</v>
+        <v>-195.72</v>
       </c>
       <c r="L27" t="n">
-        <v>216.95</v>
+        <v>266.5</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>81.44</v>
+        <v>113.15</v>
       </c>
       <c r="K28" t="n">
-        <v>76.2</v>
+        <v>105.87</v>
       </c>
       <c r="L28" t="n">
-        <v>111.53</v>
+        <v>154.96</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>-26.42</v>
+        <v>-31.13</v>
       </c>
       <c r="K29" t="n">
-        <v>-36.76</v>
+        <v>-43.3</v>
       </c>
       <c r="L29" t="n">
-        <v>45.27</v>
+        <v>53.33</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>32.99</v>
+        <v>35.28</v>
       </c>
       <c r="K30" t="n">
-        <v>-30.62</v>
+        <v>-32.75</v>
       </c>
       <c r="L30" t="n">
-        <v>45</v>
+        <v>48.14</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>36.69</v>
+        <v>41.15</v>
       </c>
       <c r="K31" t="n">
-        <v>45.9</v>
+        <v>51.49</v>
       </c>
       <c r="L31" t="n">
-        <v>58.76</v>
+        <v>65.91</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>-52.13</v>
+        <v>-57.92</v>
       </c>
       <c r="K32" t="n">
-        <v>-54.62</v>
+        <v>-60.68</v>
       </c>
       <c r="L32" t="n">
-        <v>75.51000000000001</v>
+        <v>83.88</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-66.33</v>
+        <v>-77.78</v>
       </c>
       <c r="K33" t="n">
-        <v>-6.16</v>
+        <v>-7.22</v>
       </c>
       <c r="L33" t="n">
-        <v>66.62</v>
+        <v>78.11</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-78.84</v>
+        <v>-89.52</v>
       </c>
       <c r="K34" t="n">
-        <v>-11.72</v>
+        <v>-13.31</v>
       </c>
       <c r="L34" t="n">
-        <v>79.7</v>
+        <v>90.51000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>128.37</v>
+        <v>137.32</v>
       </c>
       <c r="K35" t="n">
-        <v>77.44</v>
+        <v>82.84</v>
       </c>
       <c r="L35" t="n">
-        <v>149.92</v>
+        <v>160.37</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-82.90000000000001</v>
+        <v>-91.34</v>
       </c>
       <c r="K36" t="n">
-        <v>121.01</v>
+        <v>133.33</v>
       </c>
       <c r="L36" t="n">
-        <v>146.69</v>
+        <v>161.61</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>69.93000000000001</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>12.04</v>
+        <v>15.58</v>
       </c>
       <c r="L37" t="n">
-        <v>70.95999999999999</v>
+        <v>91.79000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>143.34</v>
+        <v>167.37</v>
       </c>
       <c r="K38" t="n">
-        <v>136.64</v>
+        <v>159.54</v>
       </c>
       <c r="L38" t="n">
-        <v>198.03</v>
+        <v>231.22</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-31.41</v>
+        <v>-41.77</v>
       </c>
       <c r="K39" t="n">
-        <v>-102.22</v>
+        <v>-135.96</v>
       </c>
       <c r="L39" t="n">
-        <v>106.93</v>
+        <v>142.23</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>198.55</v>
+        <v>220.9</v>
       </c>
       <c r="K40" t="n">
         <v>-0</v>
       </c>
       <c r="L40" t="n">
-        <v>198.55</v>
+        <v>220.9</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>12.58</v>
+        <v>16.66</v>
       </c>
       <c r="K41" t="n">
-        <v>-157.89</v>
+        <v>-209.1</v>
       </c>
       <c r="L41" t="n">
-        <v>158.39</v>
+        <v>209.76</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-100.53</v>
+        <v>-115.53</v>
       </c>
       <c r="K42" t="n">
-        <v>-291.2</v>
+        <v>-334.65</v>
       </c>
       <c r="L42" t="n">
-        <v>308.06</v>
+        <v>354.03</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>165.52</v>
+        <v>206.97</v>
       </c>
       <c r="K43" t="n">
-        <v>29.37</v>
+        <v>36.72</v>
       </c>
       <c r="L43" t="n">
-        <v>168.1</v>
+        <v>210.21</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>-31.33</v>
+        <v>-35.28</v>
       </c>
       <c r="K44" t="n">
-        <v>-44.73</v>
+        <v>-50.37</v>
       </c>
       <c r="L44" t="n">
-        <v>54.61</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>32.86</v>
+        <v>39.81</v>
       </c>
       <c r="K45" t="n">
-        <v>-15.22</v>
+        <v>-18.43</v>
       </c>
       <c r="L45" t="n">
-        <v>36.21</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>-41.61</v>
+        <v>-43.98</v>
       </c>
       <c r="K46" t="n">
-        <v>-46.41</v>
+        <v>-49.05</v>
       </c>
       <c r="L46" t="n">
-        <v>62.33</v>
+        <v>65.88</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>-60.11</v>
+        <v>-69.15000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>30.14</v>
+        <v>34.67</v>
       </c>
       <c r="L47" t="n">
-        <v>67.23999999999999</v>
+        <v>77.36</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>48.61</v>
+        <v>51.55</v>
       </c>
       <c r="K48" t="n">
-        <v>-72.62</v>
+        <v>-77.02</v>
       </c>
       <c r="L48" t="n">
-        <v>87.39</v>
+        <v>92.68000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.1</v>
+        <v>-5.43</v>
       </c>
       <c r="K49" t="n">
-        <v>-88.48999999999999</v>
+        <v>-94.26000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>88.64</v>
+        <v>94.42</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>83.28</v>
+        <v>99.94</v>
       </c>
       <c r="K50" t="n">
-        <v>-50.38</v>
+        <v>-60.45</v>
       </c>
       <c r="L50" t="n">
-        <v>97.34</v>
+        <v>116.8</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>28</v>
       </c>
       <c r="J51" t="n">
-        <v>-23.03</v>
+        <v>-26.81</v>
       </c>
       <c r="K51" t="n">
-        <v>-90.65000000000001</v>
+        <v>-105.5</v>
       </c>
       <c r="L51" t="n">
-        <v>93.53</v>
+        <v>108.86</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>76.27</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>-45.73</v>
+        <v>-54.17</v>
       </c>
       <c r="L52" t="n">
-        <v>88.93000000000001</v>
+        <v>105.34</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-53.33</v>
+        <v>-68.48</v>
       </c>
       <c r="K53" t="n">
-        <v>-92.78</v>
+        <v>-119.13</v>
       </c>
       <c r="L53" t="n">
-        <v>107.01</v>
+        <v>137.41</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>11.24</v>
+        <v>13.19</v>
       </c>
       <c r="K54" t="n">
-        <v>-183.32</v>
+        <v>-215.26</v>
       </c>
       <c r="L54" t="n">
-        <v>183.66</v>
+        <v>215.67</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>34.62</v>
+        <v>44.36</v>
       </c>
       <c r="K55" t="n">
-        <v>-103.65</v>
+        <v>-132.79</v>
       </c>
       <c r="L55" t="n">
-        <v>109.28</v>
+        <v>140</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>180.29</v>
+        <v>222</v>
       </c>
       <c r="K56" t="n">
-        <v>250.85</v>
+        <v>308.88</v>
       </c>
       <c r="L56" t="n">
-        <v>308.91</v>
+        <v>380.39</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-133.06</v>
+        <v>-177.56</v>
       </c>
       <c r="K57" t="n">
-        <v>-11.71</v>
+        <v>-15.63</v>
       </c>
       <c r="L57" t="n">
-        <v>133.57</v>
+        <v>178.25</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>193.09</v>
+        <v>238.53</v>
       </c>
       <c r="K58" t="n">
-        <v>-118.56</v>
+        <v>-146.46</v>
       </c>
       <c r="L58" t="n">
-        <v>226.58</v>
+        <v>279.9</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>-14.74</v>
+        <v>-15.93</v>
       </c>
       <c r="K59" t="n">
-        <v>76.84999999999999</v>
+        <v>83.03</v>
       </c>
       <c r="L59" t="n">
-        <v>78.25</v>
+        <v>84.55</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>-33.72</v>
+        <v>-36.89</v>
       </c>
       <c r="K60" t="n">
-        <v>-37.76</v>
+        <v>-41.31</v>
       </c>
       <c r="L60" t="n">
-        <v>50.63</v>
+        <v>55.39</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>47.95</v>
+        <v>54.66</v>
       </c>
       <c r="K61" t="n">
-        <v>-17.82</v>
+        <v>-20.32</v>
       </c>
       <c r="L61" t="n">
-        <v>51.15</v>
+        <v>58.31</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>53.35</v>
+        <v>62.65</v>
       </c>
       <c r="K62" t="n">
-        <v>19.7</v>
+        <v>23.14</v>
       </c>
       <c r="L62" t="n">
-        <v>56.87</v>
+        <v>66.79000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>84.59999999999999</v>
+        <v>92.48</v>
       </c>
       <c r="K63" t="n">
-        <v>30.63</v>
+        <v>33.48</v>
       </c>
       <c r="L63" t="n">
-        <v>89.98</v>
+        <v>98.36</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-15.65</v>
+        <v>-17.38</v>
       </c>
       <c r="K64" t="n">
-        <v>70.09999999999999</v>
+        <v>77.84</v>
       </c>
       <c r="L64" t="n">
-        <v>71.81999999999999</v>
+        <v>79.76000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-71.39</v>
+        <v>-87.90000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>54.25</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>89.67</v>
+        <v>110.39</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>59.64</v>
+        <v>73.7</v>
       </c>
       <c r="K66" t="n">
-        <v>-63.14</v>
+        <v>-78.02</v>
       </c>
       <c r="L66" t="n">
-        <v>86.84999999999999</v>
+        <v>107.33</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-51.88</v>
+        <v>-60.53</v>
       </c>
       <c r="K67" t="n">
-        <v>-103.02</v>
+        <v>-120.21</v>
       </c>
       <c r="L67" t="n">
-        <v>115.35</v>
+        <v>134.59</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>-117.5</v>
+        <v>-140.42</v>
       </c>
       <c r="K68" t="n">
-        <v>107.37</v>
+        <v>128.31</v>
       </c>
       <c r="L68" t="n">
-        <v>159.17</v>
+        <v>190.21</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>134.41</v>
+        <v>162.66</v>
       </c>
       <c r="K69" t="n">
-        <v>-36.82</v>
+        <v>-44.56</v>
       </c>
       <c r="L69" t="n">
-        <v>139.36</v>
+        <v>168.65</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>120.52</v>
+        <v>152.48</v>
       </c>
       <c r="K70" t="n">
-        <v>50.63</v>
+        <v>64.05</v>
       </c>
       <c r="L70" t="n">
-        <v>130.73</v>
+        <v>165.39</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>202.36</v>
+        <v>244.29</v>
       </c>
       <c r="K71" t="n">
-        <v>-102.45</v>
+        <v>-123.68</v>
       </c>
       <c r="L71" t="n">
-        <v>226.82</v>
+        <v>273.82</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>67.51000000000001</v>
+        <v>92.04000000000001</v>
       </c>
       <c r="K72" t="n">
-        <v>135.3</v>
+        <v>184.45</v>
       </c>
       <c r="L72" t="n">
-        <v>151.2</v>
+        <v>206.14</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-55.29</v>
+        <v>-69.7</v>
       </c>
       <c r="K73" t="n">
-        <v>-198.31</v>
+        <v>-250</v>
       </c>
       <c r="L73" t="n">
-        <v>205.88</v>
+        <v>259.54</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>43.46</v>
+        <v>51.87</v>
       </c>
       <c r="K74" t="n">
-        <v>-18.85</v>
+        <v>-22.5</v>
       </c>
       <c r="L74" t="n">
-        <v>47.38</v>
+        <v>56.54</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-26.58</v>
+        <v>-28.99</v>
       </c>
       <c r="K75" t="n">
-        <v>-67.45</v>
+        <v>-73.55</v>
       </c>
       <c r="L75" t="n">
-        <v>72.5</v>
+        <v>79.05</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="K76" t="n">
-        <v>99.62</v>
+        <v>101.99</v>
       </c>
       <c r="L76" t="n">
-        <v>99.65000000000001</v>
+        <v>102.02</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-87.48</v>
+        <v>-91.19</v>
       </c>
       <c r="K77" t="n">
-        <v>-71.15000000000001</v>
+        <v>-74.17</v>
       </c>
       <c r="L77" t="n">
-        <v>112.76</v>
+        <v>117.55</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>114.49</v>
+        <v>119.11</v>
       </c>
       <c r="K78" t="n">
-        <v>-59.73</v>
+        <v>-62.14</v>
       </c>
       <c r="L78" t="n">
-        <v>129.13</v>
+        <v>134.35</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>21.04</v>
+        <v>24.99</v>
       </c>
       <c r="K79" t="n">
-        <v>63.82</v>
+        <v>75.8</v>
       </c>
       <c r="L79" t="n">
-        <v>67.2</v>
+        <v>79.81999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>101.02</v>
+        <v>120.03</v>
       </c>
       <c r="K80" t="n">
-        <v>8.140000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="L80" t="n">
-        <v>101.35</v>
+        <v>120.42</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>26</v>
       </c>
       <c r="J81" t="n">
-        <v>56.22</v>
+        <v>65.47</v>
       </c>
       <c r="K81" t="n">
-        <v>-87.23999999999999</v>
+        <v>-101.6</v>
       </c>
       <c r="L81" t="n">
-        <v>103.78</v>
+        <v>120.86</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-13.4</v>
+        <v>-17.2</v>
       </c>
       <c r="K82" t="n">
-        <v>63.37</v>
+        <v>81.31</v>
       </c>
       <c r="L82" t="n">
-        <v>64.77</v>
+        <v>83.11</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>28</v>
       </c>
       <c r="J83" t="n">
-        <v>-47.6</v>
+        <v>-57.57</v>
       </c>
       <c r="K83" t="n">
-        <v>-137.25</v>
+        <v>-165.99</v>
       </c>
       <c r="L83" t="n">
-        <v>145.27</v>
+        <v>175.69</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-145.64</v>
+        <v>-179.5</v>
       </c>
       <c r="K84" t="n">
-        <v>-38.73</v>
+        <v>-47.73</v>
       </c>
       <c r="L84" t="n">
-        <v>150.7</v>
+        <v>185.74</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-80.43000000000001</v>
+        <v>-99.77</v>
       </c>
       <c r="K85" t="n">
-        <v>-121.01</v>
+        <v>-150.12</v>
       </c>
       <c r="L85" t="n">
-        <v>145.3</v>
+        <v>180.25</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>57.6</v>
+        <v>79.27</v>
       </c>
       <c r="K86" t="n">
-        <v>18.94</v>
+        <v>26.07</v>
       </c>
       <c r="L86" t="n">
-        <v>60.63</v>
+        <v>83.45</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>115.91</v>
+        <v>143.52</v>
       </c>
       <c r="K87" t="n">
-        <v>-163.47</v>
+        <v>-202.41</v>
       </c>
       <c r="L87" t="n">
-        <v>200.39</v>
+        <v>248.13</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>56.35</v>
+        <v>77.03</v>
       </c>
       <c r="K88" t="n">
-        <v>1.2</v>
+        <v>1.64</v>
       </c>
       <c r="L88" t="n">
-        <v>56.36</v>
+        <v>77.04000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-03.xlsx
+++ b/output/2025-10-03.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>47.71</v>
+        <v>52.09</v>
       </c>
       <c r="K14" t="n">
-        <v>33.83</v>
+        <v>36.93</v>
       </c>
       <c r="L14" t="n">
-        <v>58.48</v>
+        <v>63.85</v>
       </c>
     </row>
     <row r="15">
@@ -766,13 +766,13 @@
         <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>11.21</v>
+        <v>11.28</v>
       </c>
       <c r="K17" t="n">
-        <v>-25.49</v>
+        <v>-25.64</v>
       </c>
       <c r="L17" t="n">
-        <v>27.84</v>
+        <v>28.01</v>
       </c>
     </row>
     <row r="18">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>41.15</v>
+        <v>42.24</v>
       </c>
       <c r="K31" t="n">
-        <v>51.49</v>
+        <v>52.84</v>
       </c>
       <c r="L31" t="n">
-        <v>65.91</v>
+        <v>67.65000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-89.52</v>
+        <v>-94.70999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>-13.31</v>
+        <v>-14.08</v>
       </c>
       <c r="L34" t="n">
-        <v>90.51000000000001</v>
+        <v>95.75</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>-35.28</v>
+        <v>-37.41</v>
       </c>
       <c r="K44" t="n">
-        <v>-50.37</v>
+        <v>-53.42</v>
       </c>
       <c r="L44" t="n">
-        <v>61.5</v>
+        <v>65.20999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -2113,10 +2113,10 @@
         <v>-5.43</v>
       </c>
       <c r="K49" t="n">
-        <v>-94.26000000000001</v>
+        <v>-94.31</v>
       </c>
       <c r="L49" t="n">
-        <v>94.42</v>
+        <v>94.47</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>-15.93</v>
+        <v>-16.55</v>
       </c>
       <c r="K59" t="n">
-        <v>83.03</v>
+        <v>86.27</v>
       </c>
       <c r="L59" t="n">
-        <v>84.55</v>
+        <v>87.84</v>
       </c>
     </row>
     <row r="60">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>92.48</v>
+        <v>96.47</v>
       </c>
       <c r="K63" t="n">
-        <v>33.48</v>
+        <v>34.93</v>
       </c>
       <c r="L63" t="n">
-        <v>98.36</v>
+        <v>102.6</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-17.38</v>
+        <v>-17.82</v>
       </c>
       <c r="K64" t="n">
-        <v>77.84</v>
+        <v>79.8</v>
       </c>
       <c r="L64" t="n">
-        <v>79.76000000000001</v>
+        <v>81.77</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>51.87</v>
+        <v>55.42</v>
       </c>
       <c r="K74" t="n">
-        <v>-22.5</v>
+        <v>-24.04</v>
       </c>
       <c r="L74" t="n">
-        <v>56.54</v>
+        <v>60.41</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-28.99</v>
+        <v>-30.34</v>
       </c>
       <c r="K75" t="n">
-        <v>-73.55</v>
+        <v>-76.97</v>
       </c>
       <c r="L75" t="n">
-        <v>79.05</v>
+        <v>82.73999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="K76" t="n">
-        <v>101.99</v>
+        <v>109.19</v>
       </c>
       <c r="L76" t="n">
-        <v>102.02</v>
+        <v>109.23</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-91.19</v>
+        <v>-96.47</v>
       </c>
       <c r="K77" t="n">
-        <v>-74.17</v>
+        <v>-78.47</v>
       </c>
       <c r="L77" t="n">
-        <v>117.55</v>
+        <v>124.36</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>119.11</v>
+        <v>131.11</v>
       </c>
       <c r="K78" t="n">
-        <v>-62.14</v>
+        <v>-68.40000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>134.35</v>
+        <v>147.89</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>24.99</v>
+        <v>27.27</v>
       </c>
       <c r="K79" t="n">
-        <v>75.8</v>
+        <v>82.7</v>
       </c>
       <c r="L79" t="n">
-        <v>79.81999999999999</v>
+        <v>87.06999999999999</v>
       </c>
     </row>
     <row r="80">
